--- a/procesos/inputs/Excel CCC Empresas.xlsx
+++ b/procesos/inputs/Excel CCC Empresas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\LABORAL\00 asesorIA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonza\OneDrive\Nodus\Proyectos\Nodus-app\parche-gestoria\procesos\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08B4DB5-B707-4E8F-AFAA-71A59A6C2B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D7FB3E-ADB1-43F5-B504-10AD1CEDA0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14205" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE DE DATOS (NO TOCAR)" sheetId="14" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="827">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -2494,6 +2494,24 @@
   </si>
   <si>
     <t>011138123786122</t>
+  </si>
+  <si>
+    <t>ATC</t>
+  </si>
+  <si>
+    <t>ITA</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>AEAT</t>
+  </si>
+  <si>
+    <t>ART.42</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -2558,7 +2576,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2581,12 +2599,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2613,8 +2644,22 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2984,20 +3029,21 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:G254"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L254"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="12" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" style="8" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="119.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.85546875" style="6"/>
+    <col min="1" max="1" width="10.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.1796875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="27.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="119.1796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="10.81640625" style="21"/>
+    <col min="13" max="16384" width="10.81640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>815</v>
       </c>
@@ -3016,11 +3062,26 @@
       <c r="F1" s="9" t="s">
         <v>804</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="15" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="9" t="s">
+        <v>823</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>824</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>821</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>822</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>40</v>
       </c>
@@ -3040,11 +3101,16 @@
       <c r="F2" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="16" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
@@ -3064,11 +3130,16 @@
       <c r="F3" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="16" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
@@ -3088,11 +3159,16 @@
       <c r="F4" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="16" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>40</v>
       </c>
@@ -3112,11 +3188,16 @@
       <c r="F5" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="16" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
@@ -3136,11 +3217,16 @@
       <c r="F6" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="16" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -3160,11 +3246,22 @@
       <c r="F7" s="10" t="s">
         <v>386</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="16" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" s="19" t="s">
+        <v>826</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>826</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>826</v>
+      </c>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>215</v>
       </c>
@@ -3184,11 +3281,18 @@
       <c r="F8" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="16" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19" t="s">
+        <v>826</v>
+      </c>
+      <c r="L8" s="19"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
@@ -3208,11 +3312,16 @@
       <c r="F9" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="16" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
@@ -3232,11 +3341,16 @@
       <c r="F10" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="16" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>45</v>
       </c>
@@ -3256,11 +3370,16 @@
       <c r="F11" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="G11" s="10" t="s">
+      <c r="G11" s="16" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>47</v>
       </c>
@@ -3280,11 +3399,16 @@
       <c r="F12" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="16" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
@@ -3304,11 +3428,16 @@
       <c r="F13" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="16" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>49</v>
       </c>
@@ -3328,11 +3457,16 @@
       <c r="F14" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="16" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>50</v>
       </c>
@@ -3352,11 +3486,16 @@
       <c r="F15" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="16" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -3376,11 +3515,16 @@
       <c r="F16" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="16" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>223</v>
       </c>
@@ -3400,11 +3544,16 @@
       <c r="F17" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="16" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>223</v>
       </c>
@@ -3424,11 +3573,16 @@
       <c r="F18" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="16" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>223</v>
       </c>
@@ -3448,11 +3602,16 @@
       <c r="F19" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="16" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>51</v>
       </c>
@@ -3472,11 +3631,16 @@
       <c r="F20" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="16" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+    </row>
+    <row r="21" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>112</v>
       </c>
@@ -3496,11 +3660,16 @@
       <c r="F21" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="16" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>52</v>
       </c>
@@ -3520,11 +3689,16 @@
       <c r="F22" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="16" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>52</v>
       </c>
@@ -3544,11 +3718,16 @@
       <c r="F23" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="16" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>236</v>
       </c>
@@ -3568,11 +3747,16 @@
       <c r="F24" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="16" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>54</v>
       </c>
@@ -3592,11 +3776,16 @@
       <c r="F25" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" s="16" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>55</v>
       </c>
@@ -3616,11 +3805,16 @@
       <c r="F26" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" s="16" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>57</v>
       </c>
@@ -3640,11 +3834,16 @@
       <c r="F27" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="G27" s="16" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>59</v>
       </c>
@@ -3664,11 +3863,16 @@
       <c r="F28" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="G28" s="16" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>61</v>
       </c>
@@ -3688,11 +3892,16 @@
       <c r="F29" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G29" s="16" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="19"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>61</v>
       </c>
@@ -3712,11 +3921,16 @@
       <c r="F30" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" s="16" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>62</v>
       </c>
@@ -3736,11 +3950,16 @@
       <c r="F31" s="10" t="s">
         <v>416</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" s="16" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="19"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>63</v>
       </c>
@@ -3760,11 +3979,16 @@
       <c r="F32" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="G32" s="16" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="19"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>208</v>
       </c>
@@ -3784,11 +4008,16 @@
       <c r="F33" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="G33" s="10" t="s">
+      <c r="G33" s="16" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>65</v>
       </c>
@@ -3808,11 +4037,16 @@
       <c r="F34" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="G34" s="10" t="s">
+      <c r="G34" s="16" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>238</v>
       </c>
@@ -3832,11 +4066,16 @@
       <c r="F35" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="G35" s="10" t="s">
+      <c r="G35" s="16" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>113</v>
       </c>
@@ -3856,11 +4095,16 @@
       <c r="F36" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="G36" s="10" t="s">
+      <c r="G36" s="16" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>113</v>
       </c>
@@ -3880,11 +4124,16 @@
       <c r="F37" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="G37" s="16" t="s">
         <v>422</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="19"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>67</v>
       </c>
@@ -3904,11 +4153,16 @@
       <c r="F38" s="10" t="s">
         <v>425</v>
       </c>
-      <c r="G38" s="10" t="s">
+      <c r="G38" s="16" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="19"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>69</v>
       </c>
@@ -3928,11 +4182,16 @@
       <c r="F39" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="G39" s="10" t="s">
+      <c r="G39" s="16" t="s">
         <v>426</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>71</v>
       </c>
@@ -3952,11 +4211,16 @@
       <c r="F40" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="G40" s="10" t="s">
+      <c r="G40" s="16" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="19"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>72</v>
       </c>
@@ -3976,11 +4240,16 @@
       <c r="F41" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="G41" s="10" t="s">
+      <c r="G41" s="16" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>431</v>
       </c>
@@ -4000,11 +4269,16 @@
       <c r="F42" s="10" t="s">
         <v>433</v>
       </c>
-      <c r="G42" s="10" t="s">
+      <c r="G42" s="16" t="s">
         <v>432</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>434</v>
       </c>
@@ -4024,11 +4298,16 @@
       <c r="F43" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="G43" s="10" t="s">
+      <c r="G43" s="16" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="19"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>436</v>
       </c>
@@ -4048,11 +4327,16 @@
       <c r="F44" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="G44" s="10" t="s">
+      <c r="G44" s="16" t="s">
         <v>437</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="19"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>439</v>
       </c>
@@ -4072,11 +4356,16 @@
       <c r="F45" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="G45" s="16" t="s">
         <v>440</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>442</v>
       </c>
@@ -4096,11 +4385,16 @@
       <c r="F46" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="G46" s="10" t="s">
+      <c r="G46" s="16" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="19"/>
+      <c r="K46" s="19"/>
+      <c r="L46" s="19"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>164</v>
       </c>
@@ -4120,11 +4414,16 @@
       <c r="F47" s="10" t="s">
         <v>446</v>
       </c>
-      <c r="G47" s="10" t="s">
+      <c r="G47" s="16" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H47" s="19"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="19"/>
+      <c r="K47" s="19"/>
+      <c r="L47" s="19"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>214</v>
       </c>
@@ -4144,11 +4443,16 @@
       <c r="F48" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="G48" s="10" t="s">
+      <c r="G48" s="16" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H48" s="19"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="19"/>
+      <c r="K48" s="19"/>
+      <c r="L48" s="19"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>449</v>
       </c>
@@ -4168,11 +4472,16 @@
       <c r="F49" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="G49" s="10" t="s">
+      <c r="G49" s="16" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="19"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="19"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>262</v>
       </c>
@@ -4192,11 +4501,16 @@
       <c r="F50" s="10" t="s">
         <v>455</v>
       </c>
-      <c r="G50" s="10" t="s">
+      <c r="G50" s="16" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H50" s="19"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="19"/>
+      <c r="K50" s="19"/>
+      <c r="L50" s="19"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>262</v>
       </c>
@@ -4216,11 +4530,16 @@
       <c r="F51" s="10" t="s">
         <v>455</v>
       </c>
-      <c r="G51" s="10" t="s">
+      <c r="G51" s="16" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="19"/>
+      <c r="K51" s="19"/>
+      <c r="L51" s="19"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>451</v>
       </c>
@@ -4240,11 +4559,16 @@
       <c r="F52" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="G52" s="10" t="s">
+      <c r="G52" s="16" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="19"/>
+      <c r="L52" s="19"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>217</v>
       </c>
@@ -4264,11 +4588,16 @@
       <c r="F53" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="G53" s="10" t="s">
+      <c r="G53" s="16" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H53" s="19"/>
+      <c r="I53" s="19"/>
+      <c r="J53" s="19"/>
+      <c r="K53" s="19"/>
+      <c r="L53" s="19"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>217</v>
       </c>
@@ -4288,11 +4617,16 @@
       <c r="F54" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="G54" s="10" t="s">
+      <c r="G54" s="16" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H54" s="19"/>
+      <c r="I54" s="19"/>
+      <c r="J54" s="19"/>
+      <c r="K54" s="19"/>
+      <c r="L54" s="19"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>217</v>
       </c>
@@ -4312,11 +4646,16 @@
       <c r="F55" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="G55" s="10" t="s">
+      <c r="G55" s="16" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H55" s="19"/>
+      <c r="I55" s="19"/>
+      <c r="J55" s="19"/>
+      <c r="K55" s="19"/>
+      <c r="L55" s="19"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>217</v>
       </c>
@@ -4336,11 +4675,16 @@
       <c r="F56" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="G56" s="10" t="s">
+      <c r="G56" s="16" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H56" s="19"/>
+      <c r="I56" s="19"/>
+      <c r="J56" s="19"/>
+      <c r="K56" s="19"/>
+      <c r="L56" s="19"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>217</v>
       </c>
@@ -4360,11 +4704,16 @@
       <c r="F57" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="G57" s="10" t="s">
+      <c r="G57" s="16" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H57" s="19"/>
+      <c r="I57" s="19"/>
+      <c r="J57" s="19"/>
+      <c r="K57" s="19"/>
+      <c r="L57" s="19"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>217</v>
       </c>
@@ -4384,11 +4733,16 @@
       <c r="F58" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="G58" s="10" t="s">
+      <c r="G58" s="16" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H58" s="19"/>
+      <c r="I58" s="19"/>
+      <c r="J58" s="19"/>
+      <c r="K58" s="19"/>
+      <c r="L58" s="19"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>458</v>
       </c>
@@ -4408,11 +4762,16 @@
       <c r="F59" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="G59" s="10" t="s">
+      <c r="G59" s="16" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H59" s="19"/>
+      <c r="I59" s="19"/>
+      <c r="J59" s="19"/>
+      <c r="K59" s="19"/>
+      <c r="L59" s="19"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>461</v>
       </c>
@@ -4432,11 +4791,16 @@
       <c r="F60" s="10" t="s">
         <v>463</v>
       </c>
-      <c r="G60" s="10" t="s">
+      <c r="G60" s="16" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H60" s="19"/>
+      <c r="I60" s="19"/>
+      <c r="J60" s="19"/>
+      <c r="K60" s="19"/>
+      <c r="L60" s="19"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>464</v>
       </c>
@@ -4456,11 +4820,16 @@
       <c r="F61" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="G61" s="10" t="s">
+      <c r="G61" s="16" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="19"/>
+      <c r="K61" s="19"/>
+      <c r="L61" s="19"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>467</v>
       </c>
@@ -4480,11 +4849,16 @@
       <c r="F62" s="10" t="s">
         <v>469</v>
       </c>
-      <c r="G62" s="10" t="s">
+      <c r="G62" s="16" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H62" s="19"/>
+      <c r="I62" s="19"/>
+      <c r="J62" s="19"/>
+      <c r="K62" s="19"/>
+      <c r="L62" s="19"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>198</v>
       </c>
@@ -4504,11 +4878,16 @@
       <c r="F63" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="G63" s="10" t="s">
+      <c r="G63" s="16" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H63" s="19"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="19"/>
+      <c r="K63" s="19"/>
+      <c r="L63" s="19"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>198</v>
       </c>
@@ -4528,11 +4907,16 @@
       <c r="F64" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="G64" s="10" t="s">
+      <c r="G64" s="16" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="19"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>472</v>
       </c>
@@ -4552,11 +4936,16 @@
       <c r="F65" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="G65" s="10" t="s">
+      <c r="G65" s="16" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H65" s="19"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="19"/>
+      <c r="K65" s="19"/>
+      <c r="L65" s="19"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>474</v>
       </c>
@@ -4576,11 +4965,16 @@
       <c r="F66" s="10" t="s">
         <v>476</v>
       </c>
-      <c r="G66" s="10" t="s">
+      <c r="G66" s="16" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H66" s="19"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="19"/>
+      <c r="K66" s="19"/>
+      <c r="L66" s="19"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>196</v>
       </c>
@@ -4600,11 +4994,16 @@
       <c r="F67" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="G67" s="10" t="s">
+      <c r="G67" s="16" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H67" s="19"/>
+      <c r="I67" s="19"/>
+      <c r="J67" s="19"/>
+      <c r="K67" s="19"/>
+      <c r="L67" s="19"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>478</v>
       </c>
@@ -4624,11 +5023,16 @@
       <c r="F68" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="G68" s="10" t="s">
+      <c r="G68" s="16" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H68" s="19"/>
+      <c r="I68" s="19"/>
+      <c r="J68" s="19"/>
+      <c r="K68" s="19"/>
+      <c r="L68" s="19"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>480</v>
       </c>
@@ -4648,11 +5052,16 @@
       <c r="F69" s="10" t="s">
         <v>482</v>
       </c>
-      <c r="G69" s="10" t="s">
+      <c r="G69" s="16" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="19"/>
+      <c r="K69" s="19"/>
+      <c r="L69" s="19"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>480</v>
       </c>
@@ -4672,11 +5081,16 @@
       <c r="F70" s="10" t="s">
         <v>482</v>
       </c>
-      <c r="G70" s="10" t="s">
+      <c r="G70" s="16" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H70" s="19"/>
+      <c r="I70" s="19"/>
+      <c r="J70" s="19"/>
+      <c r="K70" s="19"/>
+      <c r="L70" s="19"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>115</v>
       </c>
@@ -4696,11 +5110,16 @@
       <c r="F71" s="10" t="s">
         <v>484</v>
       </c>
-      <c r="G71" s="10" t="s">
+      <c r="G71" s="16" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H71" s="19"/>
+      <c r="I71" s="19"/>
+      <c r="J71" s="19"/>
+      <c r="K71" s="19"/>
+      <c r="L71" s="19"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>485</v>
       </c>
@@ -4720,11 +5139,16 @@
       <c r="F72" s="10" t="s">
         <v>487</v>
       </c>
-      <c r="G72" s="10" t="s">
+      <c r="G72" s="16" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H72" s="19"/>
+      <c r="I72" s="19"/>
+      <c r="J72" s="19"/>
+      <c r="K72" s="19"/>
+      <c r="L72" s="19"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>488</v>
       </c>
@@ -4744,11 +5168,16 @@
       <c r="F73" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="G73" s="10" t="s">
+      <c r="G73" s="16" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="19"/>
+      <c r="K73" s="19"/>
+      <c r="L73" s="19"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>491</v>
       </c>
@@ -4768,11 +5197,16 @@
       <c r="F74" s="10" t="s">
         <v>493</v>
       </c>
-      <c r="G74" s="10" t="s">
+      <c r="G74" s="16" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H74" s="19"/>
+      <c r="I74" s="19"/>
+      <c r="J74" s="19"/>
+      <c r="K74" s="19"/>
+      <c r="L74" s="19"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>494</v>
       </c>
@@ -4792,11 +5226,16 @@
       <c r="F75" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="G75" s="10" t="s">
+      <c r="G75" s="16" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H75" s="19"/>
+      <c r="I75" s="19"/>
+      <c r="J75" s="19"/>
+      <c r="K75" s="19"/>
+      <c r="L75" s="19"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>494</v>
       </c>
@@ -4816,11 +5255,16 @@
       <c r="F76" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="G76" s="10" t="s">
+      <c r="G76" s="16" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H76" s="19"/>
+      <c r="I76" s="19"/>
+      <c r="J76" s="19"/>
+      <c r="K76" s="19"/>
+      <c r="L76" s="19"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>170</v>
       </c>
@@ -4840,11 +5284,16 @@
       <c r="F77" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="G77" s="10" t="s">
+      <c r="G77" s="16" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="19"/>
+      <c r="K77" s="19"/>
+      <c r="L77" s="19"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>130</v>
       </c>
@@ -4864,11 +5313,16 @@
       <c r="F78" s="10" t="s">
         <v>498</v>
       </c>
-      <c r="G78" s="10" t="s">
+      <c r="G78" s="16" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H78" s="19"/>
+      <c r="I78" s="19"/>
+      <c r="J78" s="19"/>
+      <c r="K78" s="19"/>
+      <c r="L78" s="19"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>161</v>
       </c>
@@ -4888,11 +5342,16 @@
       <c r="F79" s="10" t="s">
         <v>500</v>
       </c>
-      <c r="G79" s="10" t="s">
+      <c r="G79" s="16" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H79" s="19"/>
+      <c r="I79" s="19"/>
+      <c r="J79" s="19"/>
+      <c r="K79" s="19"/>
+      <c r="L79" s="19"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>137</v>
       </c>
@@ -4912,11 +5371,16 @@
       <c r="F80" s="10" t="s">
         <v>502</v>
       </c>
-      <c r="G80" s="10" t="s">
+      <c r="G80" s="16" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H80" s="19"/>
+      <c r="I80" s="19"/>
+      <c r="J80" s="19"/>
+      <c r="K80" s="19"/>
+      <c r="L80" s="19"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>503</v>
       </c>
@@ -4936,11 +5400,16 @@
       <c r="F81" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="G81" s="10" t="s">
+      <c r="G81" s="16" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H81" s="19"/>
+      <c r="I81" s="19"/>
+      <c r="J81" s="19"/>
+      <c r="K81" s="19"/>
+      <c r="L81" s="19"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>506</v>
       </c>
@@ -4960,11 +5429,16 @@
       <c r="F82" s="10" t="s">
         <v>508</v>
       </c>
-      <c r="G82" s="10" t="s">
+      <c r="G82" s="16" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H82" s="19"/>
+      <c r="I82" s="19"/>
+      <c r="J82" s="19"/>
+      <c r="K82" s="19"/>
+      <c r="L82" s="19"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>509</v>
       </c>
@@ -4984,11 +5458,16 @@
       <c r="F83" s="10" t="s">
         <v>511</v>
       </c>
-      <c r="G83" s="10" t="s">
+      <c r="G83" s="16" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H83" s="19"/>
+      <c r="I83" s="19"/>
+      <c r="J83" s="19"/>
+      <c r="K83" s="19"/>
+      <c r="L83" s="19"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>512</v>
       </c>
@@ -5008,11 +5487,16 @@
       <c r="F84" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="G84" s="10" t="s">
+      <c r="G84" s="16" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H84" s="19"/>
+      <c r="I84" s="19"/>
+      <c r="J84" s="19"/>
+      <c r="K84" s="19"/>
+      <c r="L84" s="19"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>116</v>
       </c>
@@ -5032,11 +5516,16 @@
       <c r="F85" s="10" t="s">
         <v>515</v>
       </c>
-      <c r="G85" s="10" t="s">
+      <c r="G85" s="16" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H85" s="19"/>
+      <c r="I85" s="19"/>
+      <c r="J85" s="19"/>
+      <c r="K85" s="19"/>
+      <c r="L85" s="19"/>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>516</v>
       </c>
@@ -5056,11 +5545,16 @@
       <c r="F86" s="10" t="s">
         <v>518</v>
       </c>
-      <c r="G86" s="10" t="s">
+      <c r="G86" s="16" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H86" s="19"/>
+      <c r="I86" s="19"/>
+      <c r="J86" s="19"/>
+      <c r="K86" s="19"/>
+      <c r="L86" s="19"/>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>519</v>
       </c>
@@ -5080,11 +5574,16 @@
       <c r="F87" s="10" t="s">
         <v>521</v>
       </c>
-      <c r="G87" s="10" t="s">
+      <c r="G87" s="16" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H87" s="19"/>
+      <c r="I87" s="19"/>
+      <c r="J87" s="19"/>
+      <c r="K87" s="19"/>
+      <c r="L87" s="19"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>519</v>
       </c>
@@ -5104,11 +5603,16 @@
       <c r="F88" s="10" t="s">
         <v>521</v>
       </c>
-      <c r="G88" s="10" t="s">
+      <c r="G88" s="16" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H88" s="19"/>
+      <c r="I88" s="19"/>
+      <c r="J88" s="19"/>
+      <c r="K88" s="19"/>
+      <c r="L88" s="19"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>519</v>
       </c>
@@ -5128,11 +5632,16 @@
       <c r="F89" s="10" t="s">
         <v>521</v>
       </c>
-      <c r="G89" s="10" t="s">
+      <c r="G89" s="16" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H89" s="19"/>
+      <c r="I89" s="19"/>
+      <c r="J89" s="19"/>
+      <c r="K89" s="19"/>
+      <c r="L89" s="19"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>522</v>
       </c>
@@ -5152,11 +5661,16 @@
       <c r="F90" s="10" t="s">
         <v>524</v>
       </c>
-      <c r="G90" s="10" t="s">
+      <c r="G90" s="16" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H90" s="19"/>
+      <c r="I90" s="19"/>
+      <c r="J90" s="19"/>
+      <c r="K90" s="19"/>
+      <c r="L90" s="19"/>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>525</v>
       </c>
@@ -5176,11 +5690,16 @@
       <c r="F91" s="10" t="s">
         <v>526</v>
       </c>
-      <c r="G91" s="10" t="s">
+      <c r="G91" s="16" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H91" s="19"/>
+      <c r="I91" s="19"/>
+      <c r="J91" s="19"/>
+      <c r="K91" s="19"/>
+      <c r="L91" s="19"/>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>117</v>
       </c>
@@ -5200,11 +5719,16 @@
       <c r="F92" s="10" t="s">
         <v>528</v>
       </c>
-      <c r="G92" s="10" t="s">
+      <c r="G92" s="16" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H92" s="19"/>
+      <c r="I92" s="19"/>
+      <c r="J92" s="19"/>
+      <c r="K92" s="19"/>
+      <c r="L92" s="19"/>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>529</v>
       </c>
@@ -5224,11 +5748,16 @@
       <c r="F93" s="10" t="s">
         <v>530</v>
       </c>
-      <c r="G93" s="10" t="s">
+      <c r="G93" s="16" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H93" s="19"/>
+      <c r="I93" s="19"/>
+      <c r="J93" s="19"/>
+      <c r="K93" s="19"/>
+      <c r="L93" s="19"/>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>529</v>
       </c>
@@ -5248,11 +5777,16 @@
       <c r="F94" s="10" t="s">
         <v>530</v>
       </c>
-      <c r="G94" s="10" t="s">
+      <c r="G94" s="16" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H94" s="19"/>
+      <c r="I94" s="19"/>
+      <c r="J94" s="19"/>
+      <c r="K94" s="19"/>
+      <c r="L94" s="19"/>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>529</v>
       </c>
@@ -5272,11 +5806,16 @@
       <c r="F95" s="10" t="s">
         <v>530</v>
       </c>
-      <c r="G95" s="10" t="s">
+      <c r="G95" s="16" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H95" s="19"/>
+      <c r="I95" s="19"/>
+      <c r="J95" s="19"/>
+      <c r="K95" s="19"/>
+      <c r="L95" s="19"/>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>531</v>
       </c>
@@ -5296,11 +5835,16 @@
       <c r="F96" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="G96" s="10" t="s">
+      <c r="G96" s="16" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H96" s="19"/>
+      <c r="I96" s="19"/>
+      <c r="J96" s="19"/>
+      <c r="K96" s="19"/>
+      <c r="L96" s="19"/>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>536</v>
       </c>
@@ -5320,11 +5864,16 @@
       <c r="F97" s="10" t="s">
         <v>538</v>
       </c>
-      <c r="G97" s="10" t="s">
+      <c r="G97" s="16" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H97" s="19"/>
+      <c r="I97" s="19"/>
+      <c r="J97" s="19"/>
+      <c r="K97" s="19"/>
+      <c r="L97" s="19"/>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>536</v>
       </c>
@@ -5344,11 +5893,16 @@
       <c r="F98" s="10" t="s">
         <v>538</v>
       </c>
-      <c r="G98" s="10" t="s">
+      <c r="G98" s="16" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H98" s="19"/>
+      <c r="I98" s="19"/>
+      <c r="J98" s="19"/>
+      <c r="K98" s="19"/>
+      <c r="L98" s="19"/>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>534</v>
       </c>
@@ -5368,11 +5922,16 @@
       <c r="F99" s="10" t="s">
         <v>535</v>
       </c>
-      <c r="G99" s="10" t="s">
+      <c r="G99" s="16" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H99" s="19"/>
+      <c r="I99" s="19"/>
+      <c r="J99" s="19"/>
+      <c r="K99" s="19"/>
+      <c r="L99" s="19"/>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>267</v>
       </c>
@@ -5392,11 +5951,16 @@
       <c r="F100" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="G100" s="10" t="s">
+      <c r="G100" s="16" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H100" s="19"/>
+      <c r="I100" s="19"/>
+      <c r="J100" s="19"/>
+      <c r="K100" s="19"/>
+      <c r="L100" s="19"/>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>267</v>
       </c>
@@ -5416,11 +5980,16 @@
       <c r="F101" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="G101" s="10" t="s">
+      <c r="G101" s="16" t="s">
         <v>539</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H101" s="19"/>
+      <c r="I101" s="19"/>
+      <c r="J101" s="19"/>
+      <c r="K101" s="19"/>
+      <c r="L101" s="19"/>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>540</v>
       </c>
@@ -5440,11 +6009,16 @@
       <c r="F102" s="10" t="s">
         <v>542</v>
       </c>
-      <c r="G102" s="10" t="s">
+      <c r="G102" s="16" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H102" s="19"/>
+      <c r="I102" s="19"/>
+      <c r="J102" s="19"/>
+      <c r="K102" s="19"/>
+      <c r="L102" s="19"/>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>540</v>
       </c>
@@ -5464,11 +6038,16 @@
       <c r="F103" s="10" t="s">
         <v>542</v>
       </c>
-      <c r="G103" s="10" t="s">
+      <c r="G103" s="16" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H103" s="19"/>
+      <c r="I103" s="19"/>
+      <c r="J103" s="19"/>
+      <c r="K103" s="19"/>
+      <c r="L103" s="19"/>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>540</v>
       </c>
@@ -5488,11 +6067,16 @@
       <c r="F104" s="10" t="s">
         <v>542</v>
       </c>
-      <c r="G104" s="10" t="s">
+      <c r="G104" s="16" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H104" s="19"/>
+      <c r="I104" s="19"/>
+      <c r="J104" s="19"/>
+      <c r="K104" s="19"/>
+      <c r="L104" s="19"/>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>543</v>
       </c>
@@ -5512,11 +6096,16 @@
       <c r="F105" s="10" t="s">
         <v>544</v>
       </c>
-      <c r="G105" s="10" t="s">
+      <c r="G105" s="16" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H105" s="19"/>
+      <c r="I105" s="19"/>
+      <c r="J105" s="19"/>
+      <c r="K105" s="19"/>
+      <c r="L105" s="19"/>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>543</v>
       </c>
@@ -5536,11 +6125,16 @@
       <c r="F106" s="10" t="s">
         <v>544</v>
       </c>
-      <c r="G106" s="10" t="s">
+      <c r="G106" s="16" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H106" s="19"/>
+      <c r="I106" s="19"/>
+      <c r="J106" s="19"/>
+      <c r="K106" s="19"/>
+      <c r="L106" s="19"/>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>545</v>
       </c>
@@ -5560,11 +6154,16 @@
       <c r="F107" s="10" t="s">
         <v>547</v>
       </c>
-      <c r="G107" s="10" t="s">
+      <c r="G107" s="16" t="s">
         <v>546</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H107" s="19"/>
+      <c r="I107" s="19"/>
+      <c r="J107" s="19"/>
+      <c r="K107" s="19"/>
+      <c r="L107" s="19"/>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>548</v>
       </c>
@@ -5584,11 +6183,16 @@
       <c r="F108" s="10" t="s">
         <v>550</v>
       </c>
-      <c r="G108" s="10" t="s">
+      <c r="G108" s="16" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H108" s="19"/>
+      <c r="I108" s="19"/>
+      <c r="J108" s="19"/>
+      <c r="K108" s="19"/>
+      <c r="L108" s="19"/>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>805</v>
       </c>
@@ -5608,11 +6212,16 @@
       <c r="F109" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="G109" s="10" t="s">
+      <c r="G109" s="16" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H109" s="19"/>
+      <c r="I109" s="19"/>
+      <c r="J109" s="19"/>
+      <c r="K109" s="19"/>
+      <c r="L109" s="19"/>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>167</v>
       </c>
@@ -5632,11 +6241,16 @@
       <c r="F110" s="10" t="s">
         <v>553</v>
       </c>
-      <c r="G110" s="10" t="s">
+      <c r="G110" s="16" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H110" s="19"/>
+      <c r="I110" s="19"/>
+      <c r="J110" s="19"/>
+      <c r="K110" s="19"/>
+      <c r="L110" s="19"/>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>554</v>
       </c>
@@ -5656,11 +6270,16 @@
       <c r="F111" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="G111" s="10" t="s">
+      <c r="G111" s="16" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H111" s="19"/>
+      <c r="I111" s="19"/>
+      <c r="J111" s="19"/>
+      <c r="K111" s="19"/>
+      <c r="L111" s="19"/>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>295</v>
       </c>
@@ -5680,11 +6299,16 @@
       <c r="F112" s="10" t="s">
         <v>557</v>
       </c>
-      <c r="G112" s="10" t="s">
+      <c r="G112" s="16" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H112" s="19"/>
+      <c r="I112" s="19"/>
+      <c r="J112" s="19"/>
+      <c r="K112" s="19"/>
+      <c r="L112" s="19"/>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>558</v>
       </c>
@@ -5704,11 +6328,16 @@
       <c r="F113" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="G113" s="10" t="s">
+      <c r="G113" s="16" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H113" s="19"/>
+      <c r="I113" s="19"/>
+      <c r="J113" s="19"/>
+      <c r="K113" s="19"/>
+      <c r="L113" s="19"/>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>560</v>
       </c>
@@ -5728,11 +6357,16 @@
       <c r="F114" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="G114" s="10" t="s">
+      <c r="G114" s="16" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H114" s="19"/>
+      <c r="I114" s="19"/>
+      <c r="J114" s="19"/>
+      <c r="K114" s="19"/>
+      <c r="L114" s="19"/>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>110</v>
       </c>
@@ -5752,11 +6386,16 @@
       <c r="F115" s="10" t="s">
         <v>563</v>
       </c>
-      <c r="G115" s="10" t="s">
+      <c r="G115" s="16" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H115" s="19"/>
+      <c r="I115" s="19"/>
+      <c r="J115" s="19"/>
+      <c r="K115" s="19"/>
+      <c r="L115" s="19"/>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>353</v>
       </c>
@@ -5776,11 +6415,16 @@
       <c r="F116" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="G116" s="10" t="s">
+      <c r="G116" s="16" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H116" s="19"/>
+      <c r="I116" s="19"/>
+      <c r="J116" s="19"/>
+      <c r="K116" s="19"/>
+      <c r="L116" s="19"/>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>564</v>
       </c>
@@ -5800,11 +6444,16 @@
       <c r="F117" s="10" t="s">
         <v>566</v>
       </c>
-      <c r="G117" s="10" t="s">
+      <c r="G117" s="16" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H117" s="19"/>
+      <c r="I117" s="19"/>
+      <c r="J117" s="19"/>
+      <c r="K117" s="19"/>
+      <c r="L117" s="19"/>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>564</v>
       </c>
@@ -5824,11 +6473,16 @@
       <c r="F118" s="10" t="s">
         <v>566</v>
       </c>
-      <c r="G118" s="10" t="s">
+      <c r="G118" s="16" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H118" s="19"/>
+      <c r="I118" s="19"/>
+      <c r="J118" s="19"/>
+      <c r="K118" s="19"/>
+      <c r="L118" s="19"/>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>350</v>
       </c>
@@ -5848,11 +6502,16 @@
       <c r="F119" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="G119" s="10" t="s">
+      <c r="G119" s="16" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H119" s="19"/>
+      <c r="I119" s="19"/>
+      <c r="J119" s="19"/>
+      <c r="K119" s="19"/>
+      <c r="L119" s="19"/>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>568</v>
       </c>
@@ -5872,11 +6531,16 @@
       <c r="F120" s="10" t="s">
         <v>570</v>
       </c>
-      <c r="G120" s="10" t="s">
+      <c r="G120" s="16" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H120" s="19"/>
+      <c r="I120" s="19"/>
+      <c r="J120" s="19"/>
+      <c r="K120" s="19"/>
+      <c r="L120" s="19"/>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>568</v>
       </c>
@@ -5896,11 +6560,16 @@
       <c r="F121" s="10" t="s">
         <v>570</v>
       </c>
-      <c r="G121" s="10" t="s">
+      <c r="G121" s="16" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H121" s="19"/>
+      <c r="I121" s="19"/>
+      <c r="J121" s="19"/>
+      <c r="K121" s="19"/>
+      <c r="L121" s="19"/>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>800</v>
       </c>
@@ -5920,11 +6589,16 @@
       <c r="F122" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="G122" s="10" t="s">
+      <c r="G122" s="16" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H122" s="19"/>
+      <c r="I122" s="19"/>
+      <c r="J122" s="19"/>
+      <c r="K122" s="19"/>
+      <c r="L122" s="19"/>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>121</v>
       </c>
@@ -5944,11 +6618,16 @@
       <c r="F123" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="G123" s="10" t="s">
+      <c r="G123" s="16" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H123" s="19"/>
+      <c r="I123" s="19"/>
+      <c r="J123" s="19"/>
+      <c r="K123" s="19"/>
+      <c r="L123" s="19"/>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>572</v>
       </c>
@@ -5968,11 +6647,16 @@
       <c r="F124" s="10" t="s">
         <v>574</v>
       </c>
-      <c r="G124" s="10" t="s">
+      <c r="G124" s="16" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H124" s="19"/>
+      <c r="I124" s="19"/>
+      <c r="J124" s="19"/>
+      <c r="K124" s="19"/>
+      <c r="L124" s="19"/>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>572</v>
       </c>
@@ -5992,11 +6676,16 @@
       <c r="F125" s="10" t="s">
         <v>574</v>
       </c>
-      <c r="G125" s="10" t="s">
+      <c r="G125" s="16" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H125" s="19"/>
+      <c r="I125" s="19"/>
+      <c r="J125" s="19"/>
+      <c r="K125" s="19"/>
+      <c r="L125" s="19"/>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>575</v>
       </c>
@@ -6016,11 +6705,16 @@
       <c r="F126" s="10" t="s">
         <v>577</v>
       </c>
-      <c r="G126" s="10" t="s">
+      <c r="G126" s="16" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H126" s="19"/>
+      <c r="I126" s="19"/>
+      <c r="J126" s="19"/>
+      <c r="K126" s="19"/>
+      <c r="L126" s="19"/>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>135</v>
       </c>
@@ -6040,11 +6734,16 @@
       <c r="F127" s="10" t="s">
         <v>579</v>
       </c>
-      <c r="G127" s="10" t="s">
+      <c r="G127" s="16" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H127" s="19"/>
+      <c r="I127" s="19"/>
+      <c r="J127" s="19"/>
+      <c r="K127" s="19"/>
+      <c r="L127" s="19"/>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>231</v>
       </c>
@@ -6064,11 +6763,16 @@
       <c r="F128" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="G128" s="10" t="s">
+      <c r="G128" s="16" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H128" s="19"/>
+      <c r="I128" s="19"/>
+      <c r="J128" s="19"/>
+      <c r="K128" s="19"/>
+      <c r="L128" s="19"/>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>581</v>
       </c>
@@ -6088,11 +6792,16 @@
       <c r="F129" s="10" t="s">
         <v>583</v>
       </c>
-      <c r="G129" s="10" t="s">
+      <c r="G129" s="16" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H129" s="19"/>
+      <c r="I129" s="19"/>
+      <c r="J129" s="19"/>
+      <c r="K129" s="19"/>
+      <c r="L129" s="19"/>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>581</v>
       </c>
@@ -6112,11 +6821,16 @@
       <c r="F130" s="10" t="s">
         <v>583</v>
       </c>
-      <c r="G130" s="10" t="s">
+      <c r="G130" s="16" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
+      <c r="J130" s="19"/>
+      <c r="K130" s="19"/>
+      <c r="L130" s="19"/>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>584</v>
       </c>
@@ -6136,11 +6850,16 @@
       <c r="F131" s="10" t="s">
         <v>586</v>
       </c>
-      <c r="G131" s="10" t="s">
+      <c r="G131" s="16" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H131" s="19"/>
+      <c r="I131" s="19"/>
+      <c r="J131" s="19"/>
+      <c r="K131" s="19"/>
+      <c r="L131" s="19"/>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>587</v>
       </c>
@@ -6160,11 +6879,16 @@
       <c r="F132" s="10" t="s">
         <v>589</v>
       </c>
-      <c r="G132" s="10" t="s">
+      <c r="G132" s="16" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H132" s="19"/>
+      <c r="I132" s="19"/>
+      <c r="J132" s="19"/>
+      <c r="K132" s="19"/>
+      <c r="L132" s="19"/>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>590</v>
       </c>
@@ -6184,11 +6908,16 @@
       <c r="F133" s="10" t="s">
         <v>592</v>
       </c>
-      <c r="G133" s="10" t="s">
+      <c r="G133" s="16" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H133" s="19"/>
+      <c r="I133" s="19"/>
+      <c r="J133" s="19"/>
+      <c r="K133" s="19"/>
+      <c r="L133" s="19"/>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>593</v>
       </c>
@@ -6208,11 +6937,16 @@
       <c r="F134" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="G134" s="10" t="s">
+      <c r="G134" s="16" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H134" s="19"/>
+      <c r="I134" s="19"/>
+      <c r="J134" s="19"/>
+      <c r="K134" s="19"/>
+      <c r="L134" s="19"/>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>145</v>
       </c>
@@ -6232,11 +6966,16 @@
       <c r="F135" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="G135" s="10" t="s">
+      <c r="G135" s="16" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H135" s="19"/>
+      <c r="I135" s="19"/>
+      <c r="J135" s="19"/>
+      <c r="K135" s="19"/>
+      <c r="L135" s="19"/>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>596</v>
       </c>
@@ -6256,11 +6995,16 @@
       <c r="F136" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="G136" s="10" t="s">
+      <c r="G136" s="16" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H136" s="19"/>
+      <c r="I136" s="19"/>
+      <c r="J136" s="19"/>
+      <c r="K136" s="19"/>
+      <c r="L136" s="19"/>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>598</v>
       </c>
@@ -6280,11 +7024,16 @@
       <c r="F137" s="10" t="s">
         <v>600</v>
       </c>
-      <c r="G137" s="10" t="s">
+      <c r="G137" s="16" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H137" s="19"/>
+      <c r="I137" s="19"/>
+      <c r="J137" s="19"/>
+      <c r="K137" s="19"/>
+      <c r="L137" s="19"/>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>601</v>
       </c>
@@ -6304,11 +7053,16 @@
       <c r="F138" s="10" t="s">
         <v>603</v>
       </c>
-      <c r="G138" s="10" t="s">
+      <c r="G138" s="16" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H138" s="19"/>
+      <c r="I138" s="19"/>
+      <c r="J138" s="19"/>
+      <c r="K138" s="19"/>
+      <c r="L138" s="19"/>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>604</v>
       </c>
@@ -6328,11 +7082,16 @@
       <c r="F139" s="10" t="s">
         <v>606</v>
       </c>
-      <c r="G139" s="10" t="s">
+      <c r="G139" s="16" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H139" s="19"/>
+      <c r="I139" s="19"/>
+      <c r="J139" s="19"/>
+      <c r="K139" s="19"/>
+      <c r="L139" s="19"/>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>607</v>
       </c>
@@ -6352,11 +7111,16 @@
       <c r="F140" s="10" t="s">
         <v>609</v>
       </c>
-      <c r="G140" s="10" t="s">
+      <c r="G140" s="16" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H140" s="19"/>
+      <c r="I140" s="19"/>
+      <c r="J140" s="19"/>
+      <c r="K140" s="19"/>
+      <c r="L140" s="19"/>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>610</v>
       </c>
@@ -6376,11 +7140,16 @@
       <c r="F141" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="G141" s="10" t="s">
+      <c r="G141" s="16" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H141" s="19"/>
+      <c r="I141" s="19"/>
+      <c r="J141" s="19"/>
+      <c r="K141" s="19"/>
+      <c r="L141" s="19"/>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>613</v>
       </c>
@@ -6400,11 +7169,16 @@
       <c r="F142" s="10" t="s">
         <v>615</v>
       </c>
-      <c r="G142" s="10" t="s">
+      <c r="G142" s="16" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H142" s="19"/>
+      <c r="I142" s="19"/>
+      <c r="J142" s="19"/>
+      <c r="K142" s="19"/>
+      <c r="L142" s="19"/>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>616</v>
       </c>
@@ -6424,11 +7198,16 @@
       <c r="F143" s="10" t="s">
         <v>618</v>
       </c>
-      <c r="G143" s="10" t="s">
+      <c r="G143" s="16" t="s">
         <v>617</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H143" s="19"/>
+      <c r="I143" s="19"/>
+      <c r="J143" s="19"/>
+      <c r="K143" s="19"/>
+      <c r="L143" s="19"/>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>619</v>
       </c>
@@ -6448,11 +7227,16 @@
       <c r="F144" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="G144" s="10" t="s">
+      <c r="G144" s="16" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H144" s="19"/>
+      <c r="I144" s="19"/>
+      <c r="J144" s="19"/>
+      <c r="K144" s="19"/>
+      <c r="L144" s="19"/>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>622</v>
       </c>
@@ -6472,11 +7256,16 @@
       <c r="F145" s="10" t="s">
         <v>623</v>
       </c>
-      <c r="G145" s="10" t="s">
+      <c r="G145" s="16" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H145" s="19"/>
+      <c r="I145" s="19"/>
+      <c r="J145" s="19"/>
+      <c r="K145" s="19"/>
+      <c r="L145" s="19"/>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>622</v>
       </c>
@@ -6496,11 +7285,16 @@
       <c r="F146" s="10" t="s">
         <v>623</v>
       </c>
-      <c r="G146" s="10" t="s">
+      <c r="G146" s="16" t="s">
         <v>620</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H146" s="19"/>
+      <c r="I146" s="19"/>
+      <c r="J146" s="19"/>
+      <c r="K146" s="19"/>
+      <c r="L146" s="19"/>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>624</v>
       </c>
@@ -6520,11 +7314,16 @@
       <c r="F147" s="10" t="s">
         <v>626</v>
       </c>
-      <c r="G147" s="10" t="s">
+      <c r="G147" s="16" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H147" s="19"/>
+      <c r="I147" s="19"/>
+      <c r="J147" s="19"/>
+      <c r="K147" s="19"/>
+      <c r="L147" s="19"/>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>627</v>
       </c>
@@ -6544,11 +7343,16 @@
       <c r="F148" s="10" t="s">
         <v>629</v>
       </c>
-      <c r="G148" s="10" t="s">
+      <c r="G148" s="16" t="s">
         <v>628</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H148" s="19"/>
+      <c r="I148" s="19"/>
+      <c r="J148" s="19"/>
+      <c r="K148" s="19"/>
+      <c r="L148" s="19"/>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>630</v>
       </c>
@@ -6568,11 +7372,16 @@
       <c r="F149" s="10" t="s">
         <v>632</v>
       </c>
-      <c r="G149" s="10" t="s">
+      <c r="G149" s="16" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H149" s="19"/>
+      <c r="I149" s="19"/>
+      <c r="J149" s="19"/>
+      <c r="K149" s="19"/>
+      <c r="L149" s="19"/>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>633</v>
       </c>
@@ -6592,11 +7401,16 @@
       <c r="F150" s="10" t="s">
         <v>635</v>
       </c>
-      <c r="G150" s="10" t="s">
+      <c r="G150" s="16" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H150" s="19"/>
+      <c r="I150" s="19"/>
+      <c r="J150" s="19"/>
+      <c r="K150" s="19"/>
+      <c r="L150" s="19"/>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>636</v>
       </c>
@@ -6616,11 +7430,16 @@
       <c r="F151" s="10" t="s">
         <v>638</v>
       </c>
-      <c r="G151" s="10" t="s">
+      <c r="G151" s="16" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H151" s="19"/>
+      <c r="I151" s="19"/>
+      <c r="J151" s="19"/>
+      <c r="K151" s="19"/>
+      <c r="L151" s="19"/>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>639</v>
       </c>
@@ -6640,11 +7459,16 @@
       <c r="F152" s="10" t="s">
         <v>640</v>
       </c>
-      <c r="G152" s="10" t="s">
+      <c r="G152" s="16" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H152" s="19"/>
+      <c r="I152" s="19"/>
+      <c r="J152" s="19"/>
+      <c r="K152" s="19"/>
+      <c r="L152" s="19"/>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>202</v>
       </c>
@@ -6664,11 +7488,16 @@
       <c r="F153" s="10" t="s">
         <v>642</v>
       </c>
-      <c r="G153" s="10" t="s">
+      <c r="G153" s="16" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H153" s="19"/>
+      <c r="I153" s="19"/>
+      <c r="J153" s="19"/>
+      <c r="K153" s="19"/>
+      <c r="L153" s="19"/>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>122</v>
       </c>
@@ -6688,11 +7517,16 @@
       <c r="F154" s="10" t="s">
         <v>644</v>
       </c>
-      <c r="G154" s="10" t="s">
+      <c r="G154" s="16" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H154" s="19"/>
+      <c r="I154" s="19"/>
+      <c r="J154" s="19"/>
+      <c r="K154" s="19"/>
+      <c r="L154" s="19"/>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>122</v>
       </c>
@@ -6712,11 +7546,16 @@
       <c r="F155" s="10" t="s">
         <v>644</v>
       </c>
-      <c r="G155" s="10" t="s">
+      <c r="G155" s="16" t="s">
         <v>643</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H155" s="19"/>
+      <c r="I155" s="19"/>
+      <c r="J155" s="19"/>
+      <c r="K155" s="19"/>
+      <c r="L155" s="19"/>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>103</v>
       </c>
@@ -6736,11 +7575,16 @@
       <c r="F156" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="G156" s="10" t="s">
+      <c r="G156" s="16" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H156" s="19"/>
+      <c r="I156" s="19"/>
+      <c r="J156" s="19"/>
+      <c r="K156" s="19"/>
+      <c r="L156" s="19"/>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>105</v>
       </c>
@@ -6760,11 +7604,16 @@
       <c r="F157" s="10" t="s">
         <v>647</v>
       </c>
-      <c r="G157" s="10" t="s">
+      <c r="G157" s="16" t="s">
         <v>646</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H157" s="19"/>
+      <c r="I157" s="19"/>
+      <c r="J157" s="19"/>
+      <c r="K157" s="19"/>
+      <c r="L157" s="19"/>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>107</v>
       </c>
@@ -6784,11 +7633,16 @@
       <c r="F158" s="10" t="s">
         <v>649</v>
       </c>
-      <c r="G158" s="10" t="s">
+      <c r="G158" s="16" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H158" s="19"/>
+      <c r="I158" s="19"/>
+      <c r="J158" s="19"/>
+      <c r="K158" s="19"/>
+      <c r="L158" s="19"/>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>111</v>
       </c>
@@ -6808,11 +7662,16 @@
       <c r="F159" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="G159" s="10" t="s">
+      <c r="G159" s="16" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H159" s="19"/>
+      <c r="I159" s="19"/>
+      <c r="J159" s="19"/>
+      <c r="K159" s="19"/>
+      <c r="L159" s="19"/>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>651</v>
       </c>
@@ -6832,11 +7691,16 @@
       <c r="F160" s="10" t="s">
         <v>653</v>
       </c>
-      <c r="G160" s="10" t="s">
+      <c r="G160" s="16" t="s">
         <v>652</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H160" s="19"/>
+      <c r="I160" s="19"/>
+      <c r="J160" s="19"/>
+      <c r="K160" s="19"/>
+      <c r="L160" s="19"/>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>654</v>
       </c>
@@ -6856,11 +7720,16 @@
       <c r="F161" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="G161" s="10" t="s">
+      <c r="G161" s="16" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H161" s="19"/>
+      <c r="I161" s="19"/>
+      <c r="J161" s="19"/>
+      <c r="K161" s="19"/>
+      <c r="L161" s="19"/>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>148</v>
       </c>
@@ -6880,11 +7749,16 @@
       <c r="F162" s="10" t="s">
         <v>657</v>
       </c>
-      <c r="G162" s="10" t="s">
+      <c r="G162" s="16" t="s">
         <v>656</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H162" s="19"/>
+      <c r="I162" s="19"/>
+      <c r="J162" s="19"/>
+      <c r="K162" s="19"/>
+      <c r="L162" s="19"/>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>134</v>
       </c>
@@ -6904,11 +7778,16 @@
       <c r="F163" s="10" t="s">
         <v>659</v>
       </c>
-      <c r="G163" s="10" t="s">
+      <c r="G163" s="16" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H163" s="19"/>
+      <c r="I163" s="19"/>
+      <c r="J163" s="19"/>
+      <c r="K163" s="19"/>
+      <c r="L163" s="19"/>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>282</v>
       </c>
@@ -6928,11 +7807,16 @@
       <c r="F164" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="G164" s="10" t="s">
+      <c r="G164" s="16" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H164" s="19"/>
+      <c r="I164" s="19"/>
+      <c r="J164" s="19"/>
+      <c r="K164" s="19"/>
+      <c r="L164" s="19"/>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>127</v>
       </c>
@@ -6952,11 +7836,16 @@
       <c r="F165" s="10" t="s">
         <v>662</v>
       </c>
-      <c r="G165" s="10" t="s">
+      <c r="G165" s="16" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H165" s="19"/>
+      <c r="I165" s="19"/>
+      <c r="J165" s="19"/>
+      <c r="K165" s="19"/>
+      <c r="L165" s="19"/>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>127</v>
       </c>
@@ -6976,11 +7865,16 @@
       <c r="F166" s="10" t="s">
         <v>662</v>
       </c>
-      <c r="G166" s="10" t="s">
+      <c r="G166" s="16" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H166" s="19"/>
+      <c r="I166" s="19"/>
+      <c r="J166" s="19"/>
+      <c r="K166" s="19"/>
+      <c r="L166" s="19"/>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>158</v>
       </c>
@@ -7000,11 +7894,16 @@
       <c r="F167" s="10" t="s">
         <v>664</v>
       </c>
-      <c r="G167" s="10" t="s">
+      <c r="G167" s="16" t="s">
         <v>663</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H167" s="19"/>
+      <c r="I167" s="19"/>
+      <c r="J167" s="19"/>
+      <c r="K167" s="19"/>
+      <c r="L167" s="19"/>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>177</v>
       </c>
@@ -7024,11 +7923,16 @@
       <c r="F168" s="10" t="s">
         <v>666</v>
       </c>
-      <c r="G168" s="10" t="s">
+      <c r="G168" s="16" t="s">
         <v>665</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H168" s="19"/>
+      <c r="I168" s="19"/>
+      <c r="J168" s="19"/>
+      <c r="K168" s="19"/>
+      <c r="L168" s="19"/>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>132</v>
       </c>
@@ -7048,11 +7952,16 @@
       <c r="F169" s="10" t="s">
         <v>668</v>
       </c>
-      <c r="G169" s="10" t="s">
+      <c r="G169" s="16" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H169" s="19"/>
+      <c r="I169" s="19"/>
+      <c r="J169" s="19"/>
+      <c r="K169" s="19"/>
+      <c r="L169" s="19"/>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>131</v>
       </c>
@@ -7072,11 +7981,16 @@
       <c r="F170" s="10" t="s">
         <v>670</v>
       </c>
-      <c r="G170" s="10" t="s">
+      <c r="G170" s="16" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H170" s="19"/>
+      <c r="I170" s="19"/>
+      <c r="J170" s="19"/>
+      <c r="K170" s="19"/>
+      <c r="L170" s="19"/>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>141</v>
       </c>
@@ -7096,11 +8010,16 @@
       <c r="F171" s="10" t="s">
         <v>672</v>
       </c>
-      <c r="G171" s="10" t="s">
+      <c r="G171" s="16" t="s">
         <v>671</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H171" s="19"/>
+      <c r="I171" s="19"/>
+      <c r="J171" s="19"/>
+      <c r="K171" s="19"/>
+      <c r="L171" s="19"/>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>142</v>
       </c>
@@ -7120,11 +8039,16 @@
       <c r="F172" s="10" t="s">
         <v>674</v>
       </c>
-      <c r="G172" s="10" t="s">
+      <c r="G172" s="16" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H172" s="19"/>
+      <c r="I172" s="19"/>
+      <c r="J172" s="19"/>
+      <c r="K172" s="19"/>
+      <c r="L172" s="19"/>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>228</v>
       </c>
@@ -7144,11 +8068,16 @@
       <c r="F173" s="10" t="s">
         <v>796</v>
       </c>
-      <c r="G173" s="10" t="s">
+      <c r="G173" s="16" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H173" s="19"/>
+      <c r="I173" s="19"/>
+      <c r="J173" s="19"/>
+      <c r="K173" s="19"/>
+      <c r="L173" s="19"/>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>230</v>
       </c>
@@ -7168,11 +8097,16 @@
       <c r="F174" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="G174" s="10" t="s">
+      <c r="G174" s="16" t="s">
         <v>675</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H174" s="19"/>
+      <c r="I174" s="19"/>
+      <c r="J174" s="19"/>
+      <c r="K174" s="19"/>
+      <c r="L174" s="19"/>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>147</v>
       </c>
@@ -7192,11 +8126,16 @@
       <c r="F175" s="10" t="s">
         <v>678</v>
       </c>
-      <c r="G175" s="10" t="s">
+      <c r="G175" s="16" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H175" s="19"/>
+      <c r="I175" s="19"/>
+      <c r="J175" s="19"/>
+      <c r="K175" s="19"/>
+      <c r="L175" s="19"/>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>151</v>
       </c>
@@ -7216,11 +8155,16 @@
       <c r="F176" s="10" t="s">
         <v>680</v>
       </c>
-      <c r="G176" s="10" t="s">
+      <c r="G176" s="16" t="s">
         <v>679</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H176" s="19"/>
+      <c r="I176" s="19"/>
+      <c r="J176" s="19"/>
+      <c r="K176" s="19"/>
+      <c r="L176" s="19"/>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>681</v>
       </c>
@@ -7240,11 +8184,16 @@
       <c r="F177" s="10" t="s">
         <v>683</v>
       </c>
-      <c r="G177" s="10" t="s">
+      <c r="G177" s="16" t="s">
         <v>682</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H177" s="19"/>
+      <c r="I177" s="19"/>
+      <c r="J177" s="19"/>
+      <c r="K177" s="19"/>
+      <c r="L177" s="19"/>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>154</v>
       </c>
@@ -7264,11 +8213,16 @@
       <c r="F178" s="10" t="s">
         <v>685</v>
       </c>
-      <c r="G178" s="10" t="s">
+      <c r="G178" s="16" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H178" s="19"/>
+      <c r="I178" s="19"/>
+      <c r="J178" s="19"/>
+      <c r="K178" s="19"/>
+      <c r="L178" s="19"/>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>156</v>
       </c>
@@ -7288,11 +8242,16 @@
       <c r="F179" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="G179" s="10" t="s">
+      <c r="G179" s="16" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H179" s="19"/>
+      <c r="I179" s="19"/>
+      <c r="J179" s="19"/>
+      <c r="K179" s="19"/>
+      <c r="L179" s="19"/>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>168</v>
       </c>
@@ -7312,11 +8271,16 @@
       <c r="F180" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="G180" s="10" t="s">
+      <c r="G180" s="16" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H180" s="19"/>
+      <c r="I180" s="19"/>
+      <c r="J180" s="19"/>
+      <c r="K180" s="19"/>
+      <c r="L180" s="19"/>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>163</v>
       </c>
@@ -7336,11 +8300,16 @@
       <c r="F181" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="G181" s="10" t="s">
+      <c r="G181" s="16" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H181" s="19"/>
+      <c r="I181" s="19"/>
+      <c r="J181" s="19"/>
+      <c r="K181" s="19"/>
+      <c r="L181" s="19"/>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>374</v>
       </c>
@@ -7360,11 +8329,16 @@
       <c r="F182" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="G182" s="10" t="s">
+      <c r="G182" s="16" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H182" s="19"/>
+      <c r="I182" s="19"/>
+      <c r="J182" s="19"/>
+      <c r="K182" s="19"/>
+      <c r="L182" s="19"/>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>173</v>
       </c>
@@ -7384,11 +8358,16 @@
       <c r="F183" s="10" t="s">
         <v>691</v>
       </c>
-      <c r="G183" s="10" t="s">
+      <c r="G183" s="16" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H183" s="19"/>
+      <c r="I183" s="19"/>
+      <c r="J183" s="19"/>
+      <c r="K183" s="19"/>
+      <c r="L183" s="19"/>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>173</v>
       </c>
@@ -7408,11 +8387,16 @@
       <c r="F184" s="10" t="s">
         <v>691</v>
       </c>
-      <c r="G184" s="10" t="s">
+      <c r="G184" s="16" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H184" s="19"/>
+      <c r="I184" s="19"/>
+      <c r="J184" s="19"/>
+      <c r="K184" s="19"/>
+      <c r="L184" s="19"/>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>175</v>
       </c>
@@ -7432,11 +8416,16 @@
       <c r="F185" s="10" t="s">
         <v>693</v>
       </c>
-      <c r="G185" s="10" t="s">
+      <c r="G185" s="16" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H185" s="19"/>
+      <c r="I185" s="19"/>
+      <c r="J185" s="19"/>
+      <c r="K185" s="19"/>
+      <c r="L185" s="19"/>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>175</v>
       </c>
@@ -7456,11 +8445,16 @@
       <c r="F186" s="10" t="s">
         <v>693</v>
       </c>
-      <c r="G186" s="10" t="s">
+      <c r="G186" s="16" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H186" s="19"/>
+      <c r="I186" s="19"/>
+      <c r="J186" s="19"/>
+      <c r="K186" s="19"/>
+      <c r="L186" s="19"/>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>175</v>
       </c>
@@ -7480,11 +8474,16 @@
       <c r="F187" s="10" t="s">
         <v>693</v>
       </c>
-      <c r="G187" s="10" t="s">
+      <c r="G187" s="16" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H187" s="19"/>
+      <c r="I187" s="19"/>
+      <c r="J187" s="19"/>
+      <c r="K187" s="19"/>
+      <c r="L187" s="19"/>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>179</v>
       </c>
@@ -7504,11 +8503,16 @@
       <c r="F188" s="10" t="s">
         <v>695</v>
       </c>
-      <c r="G188" s="10" t="s">
+      <c r="G188" s="16" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H188" s="19"/>
+      <c r="I188" s="19"/>
+      <c r="J188" s="19"/>
+      <c r="K188" s="19"/>
+      <c r="L188" s="19"/>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>696</v>
       </c>
@@ -7528,11 +8532,16 @@
       <c r="F189" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="G189" s="10" t="s">
+      <c r="G189" s="16" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H189" s="19"/>
+      <c r="I189" s="19"/>
+      <c r="J189" s="19"/>
+      <c r="K189" s="19"/>
+      <c r="L189" s="19"/>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>298</v>
       </c>
@@ -7552,11 +8561,16 @@
       <c r="F190" s="10" t="s">
         <v>698</v>
       </c>
-      <c r="G190" s="10" t="s">
+      <c r="G190" s="16" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H190" s="19"/>
+      <c r="I190" s="19"/>
+      <c r="J190" s="19"/>
+      <c r="K190" s="19"/>
+      <c r="L190" s="19"/>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>797</v>
       </c>
@@ -7576,11 +8590,16 @@
       <c r="F191" s="10" t="s">
         <v>798</v>
       </c>
-      <c r="G191" s="10" t="s">
+      <c r="G191" s="16" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H191" s="19"/>
+      <c r="I191" s="19"/>
+      <c r="J191" s="19"/>
+      <c r="K191" s="19"/>
+      <c r="L191" s="19"/>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>185</v>
       </c>
@@ -7600,11 +8619,16 @@
       <c r="F192" s="10" t="s">
         <v>700</v>
       </c>
-      <c r="G192" s="10" t="s">
+      <c r="G192" s="16" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H192" s="19"/>
+      <c r="I192" s="19"/>
+      <c r="J192" s="19"/>
+      <c r="K192" s="19"/>
+      <c r="L192" s="19"/>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>185</v>
       </c>
@@ -7624,11 +8648,16 @@
       <c r="F193" s="10" t="s">
         <v>700</v>
       </c>
-      <c r="G193" s="10" t="s">
+      <c r="G193" s="16" t="s">
         <v>699</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H193" s="19"/>
+      <c r="I193" s="19"/>
+      <c r="J193" s="19"/>
+      <c r="K193" s="19"/>
+      <c r="L193" s="19"/>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>183</v>
       </c>
@@ -7648,11 +8677,16 @@
       <c r="F194" s="10" t="s">
         <v>702</v>
       </c>
-      <c r="G194" s="10" t="s">
+      <c r="G194" s="16" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H194" s="19"/>
+      <c r="I194" s="19"/>
+      <c r="J194" s="19"/>
+      <c r="K194" s="19"/>
+      <c r="L194" s="19"/>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>703</v>
       </c>
@@ -7672,11 +8706,16 @@
       <c r="F195" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="G195" s="10" t="s">
+      <c r="G195" s="16" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H195" s="19"/>
+      <c r="I195" s="19"/>
+      <c r="J195" s="19"/>
+      <c r="K195" s="19"/>
+      <c r="L195" s="19"/>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>705</v>
       </c>
@@ -7696,11 +8735,16 @@
       <c r="F196" s="10" t="s">
         <v>707</v>
       </c>
-      <c r="G196" s="10" t="s">
+      <c r="G196" s="16" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H196" s="19"/>
+      <c r="I196" s="19"/>
+      <c r="J196" s="19"/>
+      <c r="K196" s="19"/>
+      <c r="L196" s="19"/>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>188</v>
       </c>
@@ -7720,11 +8764,16 @@
       <c r="F197" s="10" t="s">
         <v>341</v>
       </c>
-      <c r="G197" s="10" t="s">
+      <c r="G197" s="16" t="s">
         <v>708</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H197" s="19"/>
+      <c r="I197" s="19"/>
+      <c r="J197" s="19"/>
+      <c r="K197" s="19"/>
+      <c r="L197" s="19"/>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>191</v>
       </c>
@@ -7744,11 +8793,16 @@
       <c r="F198" s="10" t="s">
         <v>710</v>
       </c>
-      <c r="G198" s="10" t="s">
+      <c r="G198" s="16" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H198" s="19"/>
+      <c r="I198" s="19"/>
+      <c r="J198" s="19"/>
+      <c r="K198" s="19"/>
+      <c r="L198" s="19"/>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>711</v>
       </c>
@@ -7768,11 +8822,16 @@
       <c r="F199" s="10" t="s">
         <v>712</v>
       </c>
-      <c r="G199" s="10" t="s">
+      <c r="G199" s="16" t="s">
         <v>541</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H199" s="19"/>
+      <c r="I199" s="19"/>
+      <c r="J199" s="19"/>
+      <c r="K199" s="19"/>
+      <c r="L199" s="19"/>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>219</v>
       </c>
@@ -7795,8 +8854,13 @@
       <c r="G200" t="s">
         <v>808</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H200" s="19"/>
+      <c r="I200" s="19"/>
+      <c r="J200" s="19"/>
+      <c r="K200" s="19"/>
+      <c r="L200" s="19"/>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>713</v>
       </c>
@@ -7816,11 +8880,16 @@
       <c r="F201" s="10" t="s">
         <v>715</v>
       </c>
-      <c r="G201" s="10" t="s">
+      <c r="G201" s="16" t="s">
         <v>714</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H201" s="19"/>
+      <c r="I201" s="19"/>
+      <c r="J201" s="19"/>
+      <c r="K201" s="19"/>
+      <c r="L201" s="19"/>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>716</v>
       </c>
@@ -7840,11 +8909,16 @@
       <c r="F202" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="G202" s="10" t="s">
+      <c r="G202" s="16" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H202" s="19"/>
+      <c r="I202" s="19"/>
+      <c r="J202" s="19"/>
+      <c r="K202" s="19"/>
+      <c r="L202" s="19"/>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>359</v>
       </c>
@@ -7864,11 +8938,16 @@
       <c r="F203" s="10" t="s">
         <v>719</v>
       </c>
-      <c r="G203" s="10" t="s">
+      <c r="G203" s="16" t="s">
         <v>718</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H203" s="19"/>
+      <c r="I203" s="19"/>
+      <c r="J203" s="19"/>
+      <c r="K203" s="19"/>
+      <c r="L203" s="19"/>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>204</v>
       </c>
@@ -7888,11 +8967,16 @@
       <c r="F204" s="10" t="s">
         <v>721</v>
       </c>
-      <c r="G204" s="10" t="s">
+      <c r="G204" s="16" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H204" s="19"/>
+      <c r="I204" s="19"/>
+      <c r="J204" s="19"/>
+      <c r="K204" s="19"/>
+      <c r="L204" s="19"/>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>206</v>
       </c>
@@ -7912,11 +8996,16 @@
       <c r="F205" s="10" t="s">
         <v>723</v>
       </c>
-      <c r="G205" s="10" t="s">
+      <c r="G205" s="16" t="s">
         <v>722</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H205" s="19"/>
+      <c r="I205" s="19"/>
+      <c r="J205" s="19"/>
+      <c r="K205" s="19"/>
+      <c r="L205" s="19"/>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>240</v>
       </c>
@@ -7936,11 +9025,16 @@
       <c r="F206" s="10" t="s">
         <v>725</v>
       </c>
-      <c r="G206" s="10" t="s">
+      <c r="G206" s="16" t="s">
         <v>724</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H206" s="19"/>
+      <c r="I206" s="19"/>
+      <c r="J206" s="19"/>
+      <c r="K206" s="19"/>
+      <c r="L206" s="19"/>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>212</v>
       </c>
@@ -7960,11 +9054,16 @@
       <c r="F207" s="10" t="s">
         <v>727</v>
       </c>
-      <c r="G207" s="10" t="s">
+      <c r="G207" s="16" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H207" s="19"/>
+      <c r="I207" s="19"/>
+      <c r="J207" s="19"/>
+      <c r="K207" s="19"/>
+      <c r="L207" s="19"/>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>226</v>
       </c>
@@ -7984,11 +9083,16 @@
       <c r="F208" s="10" t="s">
         <v>729</v>
       </c>
-      <c r="G208" s="10" t="s">
+      <c r="G208" s="16" t="s">
         <v>728</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H208" s="19"/>
+      <c r="I208" s="19"/>
+      <c r="J208" s="19"/>
+      <c r="K208" s="19"/>
+      <c r="L208" s="19"/>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>221</v>
       </c>
@@ -8008,11 +9112,16 @@
       <c r="F209" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="G209" s="10" t="s">
+      <c r="G209" s="16" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H209" s="19"/>
+      <c r="I209" s="19"/>
+      <c r="J209" s="19"/>
+      <c r="K209" s="19"/>
+      <c r="L209" s="19"/>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>221</v>
       </c>
@@ -8032,11 +9141,16 @@
       <c r="F210" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="G210" s="10" t="s">
+      <c r="G210" s="16" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H210" s="19"/>
+      <c r="I210" s="19"/>
+      <c r="J210" s="19"/>
+      <c r="K210" s="19"/>
+      <c r="L210" s="19"/>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>221</v>
       </c>
@@ -8056,11 +9170,16 @@
       <c r="F211" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="G211" s="10" t="s">
+      <c r="G211" s="16" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H211" s="19"/>
+      <c r="I211" s="19"/>
+      <c r="J211" s="19"/>
+      <c r="K211" s="19"/>
+      <c r="L211" s="19"/>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>221</v>
       </c>
@@ -8080,11 +9199,16 @@
       <c r="F212" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="G212" s="10" t="s">
+      <c r="G212" s="16" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H212" s="19"/>
+      <c r="I212" s="19"/>
+      <c r="J212" s="19"/>
+      <c r="K212" s="19"/>
+      <c r="L212" s="19"/>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>221</v>
       </c>
@@ -8104,11 +9228,16 @@
       <c r="F213" s="10" t="s">
         <v>731</v>
       </c>
-      <c r="G213" s="10" t="s">
+      <c r="G213" s="16" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H213" s="19"/>
+      <c r="I213" s="19"/>
+      <c r="J213" s="19"/>
+      <c r="K213" s="19"/>
+      <c r="L213" s="19"/>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>732</v>
       </c>
@@ -8128,11 +9257,16 @@
       <c r="F214" s="10" t="s">
         <v>734</v>
       </c>
-      <c r="G214" s="10" t="s">
+      <c r="G214" s="16" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H214" s="19"/>
+      <c r="I214" s="19"/>
+      <c r="J214" s="19"/>
+      <c r="K214" s="19"/>
+      <c r="L214" s="19"/>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>232</v>
       </c>
@@ -8152,11 +9286,16 @@
       <c r="F215" s="10" t="s">
         <v>736</v>
       </c>
-      <c r="G215" s="10" t="s">
+      <c r="G215" s="16" t="s">
         <v>735</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H215" s="19"/>
+      <c r="I215" s="19"/>
+      <c r="J215" s="19"/>
+      <c r="K215" s="19"/>
+      <c r="L215" s="19"/>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>242</v>
       </c>
@@ -8176,11 +9315,16 @@
       <c r="F216" s="10" t="s">
         <v>738</v>
       </c>
-      <c r="G216" s="10" t="s">
+      <c r="G216" s="16" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H216" s="19"/>
+      <c r="I216" s="19"/>
+      <c r="J216" s="19"/>
+      <c r="K216" s="19"/>
+      <c r="L216" s="19"/>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>247</v>
       </c>
@@ -8200,11 +9344,16 @@
       <c r="F217" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="G217" s="10" t="s">
+      <c r="G217" s="16" t="s">
         <v>739</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H217" s="19"/>
+      <c r="I217" s="19"/>
+      <c r="J217" s="19"/>
+      <c r="K217" s="19"/>
+      <c r="L217" s="19"/>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>740</v>
       </c>
@@ -8224,11 +9373,16 @@
       <c r="F218" s="10" t="s">
         <v>742</v>
       </c>
-      <c r="G218" s="10" t="s">
+      <c r="G218" s="16" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H218" s="19"/>
+      <c r="I218" s="19"/>
+      <c r="J218" s="19"/>
+      <c r="K218" s="19"/>
+      <c r="L218" s="19"/>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>251</v>
       </c>
@@ -8248,11 +9402,16 @@
       <c r="F219" s="10" t="s">
         <v>744</v>
       </c>
-      <c r="G219" s="10" t="s">
+      <c r="G219" s="16" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H219" s="19"/>
+      <c r="I219" s="19"/>
+      <c r="J219" s="19"/>
+      <c r="K219" s="19"/>
+      <c r="L219" s="19"/>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>276</v>
       </c>
@@ -8272,11 +9431,16 @@
       <c r="F220" s="10" t="s">
         <v>809</v>
       </c>
-      <c r="G220" s="10" t="s">
+      <c r="G220" s="16" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H220" s="19"/>
+      <c r="I220" s="19"/>
+      <c r="J220" s="19"/>
+      <c r="K220" s="19"/>
+      <c r="L220" s="19"/>
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>746</v>
       </c>
@@ -8296,11 +9460,16 @@
       <c r="F221" s="10" t="s">
         <v>747</v>
       </c>
-      <c r="G221" s="10" t="s">
+      <c r="G221" s="16" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H221" s="19"/>
+      <c r="I221" s="19"/>
+      <c r="J221" s="19"/>
+      <c r="K221" s="19"/>
+      <c r="L221" s="19"/>
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>257</v>
       </c>
@@ -8320,11 +9489,16 @@
       <c r="F222" s="10" t="s">
         <v>811</v>
       </c>
-      <c r="G222" s="10" t="s">
+      <c r="G222" s="16" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H222" s="19"/>
+      <c r="I222" s="19"/>
+      <c r="J222" s="19"/>
+      <c r="K222" s="19"/>
+      <c r="L222" s="19"/>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>748</v>
       </c>
@@ -8344,11 +9518,16 @@
       <c r="F223" s="10" t="s">
         <v>750</v>
       </c>
-      <c r="G223" s="10" t="s">
+      <c r="G223" s="16" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H223" s="19"/>
+      <c r="I223" s="19"/>
+      <c r="J223" s="19"/>
+      <c r="K223" s="19"/>
+      <c r="L223" s="19"/>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>263</v>
       </c>
@@ -8368,11 +9547,16 @@
       <c r="F224" s="10" t="s">
         <v>752</v>
       </c>
-      <c r="G224" s="10" t="s">
+      <c r="G224" s="16" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H224" s="19"/>
+      <c r="I224" s="19"/>
+      <c r="J224" s="19"/>
+      <c r="K224" s="19"/>
+      <c r="L224" s="19"/>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>260</v>
       </c>
@@ -8392,11 +9576,16 @@
       <c r="F225" s="10" t="s">
         <v>754</v>
       </c>
-      <c r="G225" s="10" t="s">
+      <c r="G225" s="16" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H225" s="19"/>
+      <c r="I225" s="19"/>
+      <c r="J225" s="19"/>
+      <c r="K225" s="19"/>
+      <c r="L225" s="19"/>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>264</v>
       </c>
@@ -8416,11 +9605,16 @@
       <c r="F226" s="10" t="s">
         <v>756</v>
       </c>
-      <c r="G226" s="10" t="s">
+      <c r="G226" s="16" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H226" s="19"/>
+      <c r="I226" s="19"/>
+      <c r="J226" s="19"/>
+      <c r="K226" s="19"/>
+      <c r="L226" s="19"/>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>269</v>
       </c>
@@ -8440,11 +9634,16 @@
       <c r="F227" s="10" t="s">
         <v>758</v>
       </c>
-      <c r="G227" s="10" t="s">
+      <c r="G227" s="16" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H227" s="19"/>
+      <c r="I227" s="19"/>
+      <c r="J227" s="19"/>
+      <c r="K227" s="19"/>
+      <c r="L227" s="19"/>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>270</v>
       </c>
@@ -8464,11 +9663,16 @@
       <c r="F228" s="10" t="s">
         <v>760</v>
       </c>
-      <c r="G228" s="10" t="s">
+      <c r="G228" s="16" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H228" s="19"/>
+      <c r="I228" s="19"/>
+      <c r="J228" s="19"/>
+      <c r="K228" s="19"/>
+      <c r="L228" s="19"/>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>270</v>
       </c>
@@ -8488,11 +9692,16 @@
       <c r="F229" s="10" t="s">
         <v>760</v>
       </c>
-      <c r="G229" s="10" t="s">
+      <c r="G229" s="16" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H229" s="19"/>
+      <c r="I229" s="19"/>
+      <c r="J229" s="19"/>
+      <c r="K229" s="19"/>
+      <c r="L229" s="19"/>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>279</v>
       </c>
@@ -8512,11 +9721,16 @@
       <c r="F230" s="10" t="s">
         <v>762</v>
       </c>
-      <c r="G230" s="10" t="s">
+      <c r="G230" s="16" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H230" s="19"/>
+      <c r="I230" s="19"/>
+      <c r="J230" s="19"/>
+      <c r="K230" s="19"/>
+      <c r="L230" s="19"/>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>278</v>
       </c>
@@ -8536,11 +9750,16 @@
       <c r="F231" s="10" t="s">
         <v>764</v>
       </c>
-      <c r="G231" s="10" t="s">
+      <c r="G231" s="16" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H231" s="19"/>
+      <c r="I231" s="19"/>
+      <c r="J231" s="19"/>
+      <c r="K231" s="19"/>
+      <c r="L231" s="19"/>
+    </row>
+    <row r="232" spans="1:12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>284</v>
       </c>
@@ -8560,11 +9779,16 @@
       <c r="F232" s="13" t="s">
         <v>803</v>
       </c>
-      <c r="G232" s="13" t="s">
+      <c r="G232" s="17" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H232" s="20"/>
+      <c r="I232" s="20"/>
+      <c r="J232" s="20"/>
+      <c r="K232" s="20"/>
+      <c r="L232" s="20"/>
+    </row>
+    <row r="233" spans="1:12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>765</v>
       </c>
@@ -8584,11 +9808,16 @@
       <c r="F233" s="13" t="s">
         <v>767</v>
       </c>
-      <c r="G233" s="13" t="s">
+      <c r="G233" s="17" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="234" spans="1:7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H233" s="20"/>
+      <c r="I233" s="20"/>
+      <c r="J233" s="20"/>
+      <c r="K233" s="20"/>
+      <c r="L233" s="20"/>
+    </row>
+    <row r="234" spans="1:12" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>288</v>
       </c>
@@ -8608,11 +9837,16 @@
       <c r="F234" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="G234" s="13" t="s">
+      <c r="G234" s="17" t="s">
         <v>768</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H234" s="20"/>
+      <c r="I234" s="20"/>
+      <c r="J234" s="20"/>
+      <c r="K234" s="20"/>
+      <c r="L234" s="20"/>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>287</v>
       </c>
@@ -8632,11 +9866,16 @@
       <c r="F235" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="G235" s="10" t="s">
+      <c r="G235" s="16" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H235" s="19"/>
+      <c r="I235" s="19"/>
+      <c r="J235" s="19"/>
+      <c r="K235" s="19"/>
+      <c r="L235" s="19"/>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>289</v>
       </c>
@@ -8656,11 +9895,16 @@
       <c r="F236" s="10" t="s">
         <v>771</v>
       </c>
-      <c r="G236" s="10" t="s">
+      <c r="G236" s="16" t="s">
         <v>770</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H236" s="19"/>
+      <c r="I236" s="19"/>
+      <c r="J236" s="19"/>
+      <c r="K236" s="19"/>
+      <c r="L236" s="19"/>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>290</v>
       </c>
@@ -8680,11 +9924,16 @@
       <c r="F237" s="10" t="s">
         <v>773</v>
       </c>
-      <c r="G237" s="10" t="s">
+      <c r="G237" s="16" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H237" s="19"/>
+      <c r="I237" s="19"/>
+      <c r="J237" s="19"/>
+      <c r="K237" s="19"/>
+      <c r="L237" s="19"/>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>774</v>
       </c>
@@ -8704,11 +9953,16 @@
       <c r="F238" s="10" t="s">
         <v>776</v>
       </c>
-      <c r="G238" s="10" t="s">
+      <c r="G238" s="16" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H238" s="19"/>
+      <c r="I238" s="19"/>
+      <c r="J238" s="19"/>
+      <c r="K238" s="19"/>
+      <c r="L238" s="19"/>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>303</v>
       </c>
@@ -8728,11 +9982,16 @@
       <c r="F239" s="10" t="s">
         <v>778</v>
       </c>
-      <c r="G239" s="10" t="s">
+      <c r="G239" s="16" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H239" s="19"/>
+      <c r="I239" s="19"/>
+      <c r="J239" s="19"/>
+      <c r="K239" s="19"/>
+      <c r="L239" s="19"/>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>304</v>
       </c>
@@ -8752,11 +10011,16 @@
       <c r="F240" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="G240" s="10" t="s">
+      <c r="G240" s="16" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H240" s="19"/>
+      <c r="I240" s="19"/>
+      <c r="J240" s="19"/>
+      <c r="K240" s="19"/>
+      <c r="L240" s="19"/>
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>305</v>
       </c>
@@ -8776,11 +10040,16 @@
       <c r="F241" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="G241" s="10" t="s">
+      <c r="G241" s="16" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H241" s="19"/>
+      <c r="I241" s="19"/>
+      <c r="J241" s="19"/>
+      <c r="K241" s="19"/>
+      <c r="L241" s="19"/>
+    </row>
+    <row r="242" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>300</v>
       </c>
@@ -8800,11 +10069,16 @@
       <c r="F242" s="10" t="s">
         <v>780</v>
       </c>
-      <c r="G242" s="10" t="s">
+      <c r="G242" s="16" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H242" s="19"/>
+      <c r="I242" s="19"/>
+      <c r="J242" s="19"/>
+      <c r="K242" s="19"/>
+      <c r="L242" s="19"/>
+    </row>
+    <row r="243" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>348</v>
       </c>
@@ -8824,11 +10098,16 @@
       <c r="F243" s="10" t="s">
         <v>782</v>
       </c>
-      <c r="G243" s="10" t="s">
+      <c r="G243" s="16" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H243" s="19"/>
+      <c r="I243" s="19"/>
+      <c r="J243" s="19"/>
+      <c r="K243" s="19"/>
+      <c r="L243" s="19"/>
+    </row>
+    <row r="244" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>357</v>
       </c>
@@ -8848,11 +10127,16 @@
       <c r="F244" s="10" t="s">
         <v>784</v>
       </c>
-      <c r="G244" s="10" t="s">
+      <c r="G244" s="16" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H244" s="19"/>
+      <c r="I244" s="19"/>
+      <c r="J244" s="19"/>
+      <c r="K244" s="19"/>
+      <c r="L244" s="19"/>
+    </row>
+    <row r="245" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>351</v>
       </c>
@@ -8872,11 +10156,16 @@
       <c r="F245" s="10" t="s">
         <v>812</v>
       </c>
-      <c r="G245" s="10" t="s">
+      <c r="G245" s="16" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H245" s="19"/>
+      <c r="I245" s="19"/>
+      <c r="J245" s="19"/>
+      <c r="K245" s="19"/>
+      <c r="L245" s="19"/>
+    </row>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>361</v>
       </c>
@@ -8896,11 +10185,16 @@
       <c r="F246" s="10" t="s">
         <v>786</v>
       </c>
-      <c r="G246" s="10" t="s">
+      <c r="G246" s="16" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H246" s="19"/>
+      <c r="I246" s="19"/>
+      <c r="J246" s="19"/>
+      <c r="K246" s="19"/>
+      <c r="L246" s="19"/>
+    </row>
+    <row r="247" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>365</v>
       </c>
@@ -8920,11 +10214,16 @@
       <c r="F247" s="10" t="s">
         <v>787</v>
       </c>
-      <c r="G247" s="10" t="s">
+      <c r="G247" s="16" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H247" s="19"/>
+      <c r="I247" s="19"/>
+      <c r="J247" s="19"/>
+      <c r="K247" s="19"/>
+      <c r="L247" s="19"/>
+    </row>
+    <row r="248" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>363</v>
       </c>
@@ -8944,11 +10243,16 @@
       <c r="F248" s="10" t="s">
         <v>788</v>
       </c>
-      <c r="G248" s="10" t="s">
+      <c r="G248" s="16" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H248" s="19"/>
+      <c r="I248" s="19"/>
+      <c r="J248" s="19"/>
+      <c r="K248" s="19"/>
+      <c r="L248" s="19"/>
+    </row>
+    <row r="249" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>355</v>
       </c>
@@ -8968,11 +10272,16 @@
       <c r="F249" s="10" t="s">
         <v>790</v>
       </c>
-      <c r="G249" s="10" t="s">
+      <c r="G249" s="16" t="s">
         <v>789</v>
       </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H249" s="19"/>
+      <c r="I249" s="19"/>
+      <c r="J249" s="19"/>
+      <c r="K249" s="19"/>
+      <c r="L249" s="19"/>
+    </row>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>368</v>
       </c>
@@ -8992,11 +10301,16 @@
       <c r="F250" s="10" t="s">
         <v>792</v>
       </c>
-      <c r="G250" s="10" t="s">
+      <c r="G250" s="16" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H250" s="19"/>
+      <c r="I250" s="19"/>
+      <c r="J250" s="19"/>
+      <c r="K250" s="19"/>
+      <c r="L250" s="19"/>
+    </row>
+    <row r="251" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>367</v>
       </c>
@@ -9016,11 +10330,16 @@
       <c r="F251" s="10" t="s">
         <v>794</v>
       </c>
-      <c r="G251" s="10" t="s">
+      <c r="G251" s="16" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="252" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H251" s="19"/>
+      <c r="I251" s="19"/>
+      <c r="J251" s="19"/>
+      <c r="K251" s="19"/>
+      <c r="L251" s="19"/>
+    </row>
+    <row r="252" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>367</v>
       </c>
@@ -9040,11 +10359,16 @@
       <c r="F252" s="10" t="s">
         <v>794</v>
       </c>
-      <c r="G252" s="10" t="s">
+      <c r="G252" s="16" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H252" s="19"/>
+      <c r="I252" s="19"/>
+      <c r="J252" s="19"/>
+      <c r="K252" s="19"/>
+      <c r="L252" s="19"/>
+    </row>
+    <row r="253" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>371</v>
       </c>
@@ -9064,11 +10388,16 @@
       <c r="F253" s="10" t="s">
         <v>813</v>
       </c>
-      <c r="G253" s="10" t="s">
+      <c r="G253" s="16" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H253" s="19"/>
+      <c r="I253" s="19"/>
+      <c r="J253" s="19"/>
+      <c r="K253" s="19"/>
+      <c r="L253" s="19"/>
+    </row>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>816</v>
       </c>
@@ -9081,15 +10410,20 @@
       <c r="D254" s="7">
         <v>38123786122</v>
       </c>
-      <c r="E254" s="15" t="s">
+      <c r="E254" s="14" t="s">
         <v>820</v>
       </c>
       <c r="F254" s="10" t="s">
         <v>818</v>
       </c>
-      <c r="G254" s="14" t="s">
+      <c r="G254" s="18" t="s">
         <v>819</v>
       </c>
+      <c r="H254" s="19"/>
+      <c r="I254" s="19"/>
+      <c r="J254" s="19"/>
+      <c r="K254" s="19"/>
+      <c r="L254" s="19"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -9110,12 +10444,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100AF0C36E9CBDE43468AAB846756A8BA94" ma:contentTypeVersion="0" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="93c275e25462616b2c1de9b58ec156dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f6edc329ff236629c56e3b879b320d0">
     <xsd:element name="properties">
@@ -9229,6 +10557,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDD49F8-6691-4324-BC0D-0B1E4890A2C6}">
   <ds:schemaRefs>
@@ -9238,21 +10572,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEFD23-736F-4CE9-81DA-D9D145B9B572}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A01C7383-C303-4DC2-9970-99C89A193825}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9266,4 +10585,19 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEFD23-736F-4CE9-81DA-D9D145B9B572}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/procesos/inputs/Excel CCC Empresas.xlsx
+++ b/procesos/inputs/Excel CCC Empresas.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonza\OneDrive\Nodus\Proyectos\Nodus-app\parche-gestoria\procesos\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D7FB3E-ADB1-43F5-B504-10AD1CEDA0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DBD40A-3B58-4993-AA95-C70F225C335A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14205" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14595" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE DE DATOS (NO TOCAR)" sheetId="14" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS (NO TOCAR)'!$A$1:$K$254</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="826">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -2506,9 +2509,6 @@
   </si>
   <si>
     <t>AEAT</t>
-  </si>
-  <si>
-    <t>ART.42</t>
   </si>
   <si>
     <t>x</t>
@@ -3029,7 +3029,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:L254"/>
+  <dimension ref="A1:K254"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" style="6" bestFit="1" customWidth="1"/>
@@ -3038,12 +3038,12 @@
     <col min="4" max="4" width="11.81640625" style="8" customWidth="1"/>
     <col min="5" max="5" width="27.81640625" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="119.1796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="10.81640625" style="21"/>
-    <col min="13" max="16384" width="10.81640625" style="6"/>
+    <col min="7" max="7" width="58.7265625" style="6" customWidth="1"/>
+    <col min="8" max="11" width="10.81640625" style="21"/>
+    <col min="12" max="16384" width="10.81640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>815</v>
       </c>
@@ -3077,11 +3077,8 @@
       <c r="K1" s="9" t="s">
         <v>822</v>
       </c>
-      <c r="L1" s="9" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>40</v>
       </c>
@@ -3108,9 +3105,8 @@
       <c r="I2" s="19"/>
       <c r="J2" s="19"/>
       <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
@@ -3137,9 +3133,8 @@
       <c r="I3" s="19"/>
       <c r="J3" s="19"/>
       <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
@@ -3166,9 +3161,8 @@
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
       <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>40</v>
       </c>
@@ -3195,9 +3189,8 @@
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
       <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
@@ -3224,9 +3217,8 @@
       <c r="I6" s="19"/>
       <c r="J6" s="19"/>
       <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -3250,18 +3242,15 @@
         <v>385</v>
       </c>
       <c r="H7" s="19" t="s">
-        <v>826</v>
-      </c>
-      <c r="I7" s="19" t="s">
-        <v>826</v>
-      </c>
-      <c r="J7" s="19" t="s">
-        <v>826</v>
-      </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+        <v>825</v>
+      </c>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>215</v>
       </c>
@@ -3288,11 +3277,10 @@
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
       <c r="K8" s="19" t="s">
-        <v>826</v>
-      </c>
-      <c r="L8" s="19"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
@@ -3316,12 +3304,13 @@
         <v>389</v>
       </c>
       <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
+      <c r="I9" s="19" t="s">
+        <v>825</v>
+      </c>
       <c r="J9" s="19"/>
       <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
@@ -3348,9 +3337,8 @@
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
       <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>45</v>
       </c>
@@ -3377,9 +3365,8 @@
       <c r="I11" s="19"/>
       <c r="J11" s="19"/>
       <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>47</v>
       </c>
@@ -3406,9 +3393,8 @@
       <c r="I12" s="19"/>
       <c r="J12" s="19"/>
       <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
@@ -3431,13 +3417,18 @@
       <c r="G13" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
+      <c r="H13" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>825</v>
+      </c>
       <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>49</v>
       </c>
@@ -3460,13 +3451,18 @@
       <c r="G14" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
+      <c r="H14" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>825</v>
+      </c>
       <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>50</v>
       </c>
@@ -3492,10 +3488,11 @@
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
       <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K15" s="19" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -3520,11 +3517,12 @@
       </c>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
+      <c r="J16" s="19" t="s">
+        <v>825</v>
+      </c>
       <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>223</v>
       </c>
@@ -3551,9 +3549,8 @@
       <c r="I17" s="19"/>
       <c r="J17" s="19"/>
       <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>223</v>
       </c>
@@ -3580,9 +3577,8 @@
       <c r="I18" s="19"/>
       <c r="J18" s="19"/>
       <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>223</v>
       </c>
@@ -3609,9 +3605,8 @@
       <c r="I19" s="19"/>
       <c r="J19" s="19"/>
       <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>51</v>
       </c>
@@ -3638,9 +3633,8 @@
       <c r="I20" s="19"/>
       <c r="J20" s="19"/>
       <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-    </row>
-    <row r="21" spans="1:12" ht="12.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:11" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>112</v>
       </c>
@@ -3667,9 +3661,8 @@
       <c r="I21" s="19"/>
       <c r="J21" s="19"/>
       <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>52</v>
       </c>
@@ -3696,9 +3689,8 @@
       <c r="I22" s="19"/>
       <c r="J22" s="19"/>
       <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>52</v>
       </c>
@@ -3725,9 +3717,8 @@
       <c r="I23" s="19"/>
       <c r="J23" s="19"/>
       <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>236</v>
       </c>
@@ -3754,9 +3745,8 @@
       <c r="I24" s="19"/>
       <c r="J24" s="19"/>
       <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>54</v>
       </c>
@@ -3783,9 +3773,8 @@
       <c r="I25" s="19"/>
       <c r="J25" s="19"/>
       <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>55</v>
       </c>
@@ -3812,9 +3801,8 @@
       <c r="I26" s="19"/>
       <c r="J26" s="19"/>
       <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>57</v>
       </c>
@@ -3841,9 +3829,8 @@
       <c r="I27" s="19"/>
       <c r="J27" s="19"/>
       <c r="K27" s="19"/>
-      <c r="L27" s="19"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>59</v>
       </c>
@@ -3870,9 +3857,8 @@
       <c r="I28" s="19"/>
       <c r="J28" s="19"/>
       <c r="K28" s="19"/>
-      <c r="L28" s="19"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>61</v>
       </c>
@@ -3899,9 +3885,8 @@
       <c r="I29" s="19"/>
       <c r="J29" s="19"/>
       <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>61</v>
       </c>
@@ -3928,9 +3913,8 @@
       <c r="I30" s="19"/>
       <c r="J30" s="19"/>
       <c r="K30" s="19"/>
-      <c r="L30" s="19"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>62</v>
       </c>
@@ -3957,9 +3941,8 @@
       <c r="I31" s="19"/>
       <c r="J31" s="19"/>
       <c r="K31" s="19"/>
-      <c r="L31" s="19"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>63</v>
       </c>
@@ -3986,9 +3969,8 @@
       <c r="I32" s="19"/>
       <c r="J32" s="19"/>
       <c r="K32" s="19"/>
-      <c r="L32" s="19"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>208</v>
       </c>
@@ -4015,9 +3997,8 @@
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
       <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>65</v>
       </c>
@@ -4044,9 +4025,8 @@
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
       <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>238</v>
       </c>
@@ -4073,9 +4053,8 @@
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
       <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>113</v>
       </c>
@@ -4102,9 +4081,8 @@
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
       <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>113</v>
       </c>
@@ -4131,9 +4109,8 @@
       <c r="I37" s="19"/>
       <c r="J37" s="19"/>
       <c r="K37" s="19"/>
-      <c r="L37" s="19"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>67</v>
       </c>
@@ -4160,9 +4137,8 @@
       <c r="I38" s="19"/>
       <c r="J38" s="19"/>
       <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>69</v>
       </c>
@@ -4189,9 +4165,8 @@
       <c r="I39" s="19"/>
       <c r="J39" s="19"/>
       <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>71</v>
       </c>
@@ -4218,9 +4193,8 @@
       <c r="I40" s="19"/>
       <c r="J40" s="19"/>
       <c r="K40" s="19"/>
-      <c r="L40" s="19"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>72</v>
       </c>
@@ -4247,9 +4221,8 @@
       <c r="I41" s="19"/>
       <c r="J41" s="19"/>
       <c r="K41" s="19"/>
-      <c r="L41" s="19"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>431</v>
       </c>
@@ -4276,9 +4249,8 @@
       <c r="I42" s="19"/>
       <c r="J42" s="19"/>
       <c r="K42" s="19"/>
-      <c r="L42" s="19"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>434</v>
       </c>
@@ -4305,9 +4277,8 @@
       <c r="I43" s="19"/>
       <c r="J43" s="19"/>
       <c r="K43" s="19"/>
-      <c r="L43" s="19"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>436</v>
       </c>
@@ -4334,9 +4305,8 @@
       <c r="I44" s="19"/>
       <c r="J44" s="19"/>
       <c r="K44" s="19"/>
-      <c r="L44" s="19"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>439</v>
       </c>
@@ -4363,9 +4333,8 @@
       <c r="I45" s="19"/>
       <c r="J45" s="19"/>
       <c r="K45" s="19"/>
-      <c r="L45" s="19"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>442</v>
       </c>
@@ -4392,9 +4361,8 @@
       <c r="I46" s="19"/>
       <c r="J46" s="19"/>
       <c r="K46" s="19"/>
-      <c r="L46" s="19"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>164</v>
       </c>
@@ -4421,9 +4389,8 @@
       <c r="I47" s="19"/>
       <c r="J47" s="19"/>
       <c r="K47" s="19"/>
-      <c r="L47" s="19"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>214</v>
       </c>
@@ -4450,9 +4417,8 @@
       <c r="I48" s="19"/>
       <c r="J48" s="19"/>
       <c r="K48" s="19"/>
-      <c r="L48" s="19"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>449</v>
       </c>
@@ -4479,9 +4445,8 @@
       <c r="I49" s="19"/>
       <c r="J49" s="19"/>
       <c r="K49" s="19"/>
-      <c r="L49" s="19"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>262</v>
       </c>
@@ -4508,9 +4473,8 @@
       <c r="I50" s="19"/>
       <c r="J50" s="19"/>
       <c r="K50" s="19"/>
-      <c r="L50" s="19"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>262</v>
       </c>
@@ -4537,9 +4501,8 @@
       <c r="I51" s="19"/>
       <c r="J51" s="19"/>
       <c r="K51" s="19"/>
-      <c r="L51" s="19"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>451</v>
       </c>
@@ -4566,9 +4529,8 @@
       <c r="I52" s="19"/>
       <c r="J52" s="19"/>
       <c r="K52" s="19"/>
-      <c r="L52" s="19"/>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>217</v>
       </c>
@@ -4595,9 +4557,8 @@
       <c r="I53" s="19"/>
       <c r="J53" s="19"/>
       <c r="K53" s="19"/>
-      <c r="L53" s="19"/>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>217</v>
       </c>
@@ -4624,9 +4585,8 @@
       <c r="I54" s="19"/>
       <c r="J54" s="19"/>
       <c r="K54" s="19"/>
-      <c r="L54" s="19"/>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>217</v>
       </c>
@@ -4653,9 +4613,8 @@
       <c r="I55" s="19"/>
       <c r="J55" s="19"/>
       <c r="K55" s="19"/>
-      <c r="L55" s="19"/>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>217</v>
       </c>
@@ -4682,9 +4641,8 @@
       <c r="I56" s="19"/>
       <c r="J56" s="19"/>
       <c r="K56" s="19"/>
-      <c r="L56" s="19"/>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>217</v>
       </c>
@@ -4711,9 +4669,8 @@
       <c r="I57" s="19"/>
       <c r="J57" s="19"/>
       <c r="K57" s="19"/>
-      <c r="L57" s="19"/>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>217</v>
       </c>
@@ -4740,9 +4697,8 @@
       <c r="I58" s="19"/>
       <c r="J58" s="19"/>
       <c r="K58" s="19"/>
-      <c r="L58" s="19"/>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>458</v>
       </c>
@@ -4769,9 +4725,8 @@
       <c r="I59" s="19"/>
       <c r="J59" s="19"/>
       <c r="K59" s="19"/>
-      <c r="L59" s="19"/>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>461</v>
       </c>
@@ -4798,9 +4753,8 @@
       <c r="I60" s="19"/>
       <c r="J60" s="19"/>
       <c r="K60" s="19"/>
-      <c r="L60" s="19"/>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>464</v>
       </c>
@@ -4827,9 +4781,8 @@
       <c r="I61" s="19"/>
       <c r="J61" s="19"/>
       <c r="K61" s="19"/>
-      <c r="L61" s="19"/>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>467</v>
       </c>
@@ -4856,9 +4809,8 @@
       <c r="I62" s="19"/>
       <c r="J62" s="19"/>
       <c r="K62" s="19"/>
-      <c r="L62" s="19"/>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>198</v>
       </c>
@@ -4885,9 +4837,8 @@
       <c r="I63" s="19"/>
       <c r="J63" s="19"/>
       <c r="K63" s="19"/>
-      <c r="L63" s="19"/>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>198</v>
       </c>
@@ -4914,9 +4865,8 @@
       <c r="I64" s="19"/>
       <c r="J64" s="19"/>
       <c r="K64" s="19"/>
-      <c r="L64" s="19"/>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>472</v>
       </c>
@@ -4943,9 +4893,8 @@
       <c r="I65" s="19"/>
       <c r="J65" s="19"/>
       <c r="K65" s="19"/>
-      <c r="L65" s="19"/>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>474</v>
       </c>
@@ -4972,9 +4921,8 @@
       <c r="I66" s="19"/>
       <c r="J66" s="19"/>
       <c r="K66" s="19"/>
-      <c r="L66" s="19"/>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>196</v>
       </c>
@@ -5001,9 +4949,8 @@
       <c r="I67" s="19"/>
       <c r="J67" s="19"/>
       <c r="K67" s="19"/>
-      <c r="L67" s="19"/>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>478</v>
       </c>
@@ -5030,9 +4977,8 @@
       <c r="I68" s="19"/>
       <c r="J68" s="19"/>
       <c r="K68" s="19"/>
-      <c r="L68" s="19"/>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>480</v>
       </c>
@@ -5059,9 +5005,8 @@
       <c r="I69" s="19"/>
       <c r="J69" s="19"/>
       <c r="K69" s="19"/>
-      <c r="L69" s="19"/>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>480</v>
       </c>
@@ -5088,9 +5033,8 @@
       <c r="I70" s="19"/>
       <c r="J70" s="19"/>
       <c r="K70" s="19"/>
-      <c r="L70" s="19"/>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>115</v>
       </c>
@@ -5117,9 +5061,8 @@
       <c r="I71" s="19"/>
       <c r="J71" s="19"/>
       <c r="K71" s="19"/>
-      <c r="L71" s="19"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>485</v>
       </c>
@@ -5146,9 +5089,8 @@
       <c r="I72" s="19"/>
       <c r="J72" s="19"/>
       <c r="K72" s="19"/>
-      <c r="L72" s="19"/>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>488</v>
       </c>
@@ -5175,9 +5117,8 @@
       <c r="I73" s="19"/>
       <c r="J73" s="19"/>
       <c r="K73" s="19"/>
-      <c r="L73" s="19"/>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>491</v>
       </c>
@@ -5204,9 +5145,8 @@
       <c r="I74" s="19"/>
       <c r="J74" s="19"/>
       <c r="K74" s="19"/>
-      <c r="L74" s="19"/>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>494</v>
       </c>
@@ -5233,9 +5173,8 @@
       <c r="I75" s="19"/>
       <c r="J75" s="19"/>
       <c r="K75" s="19"/>
-      <c r="L75" s="19"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>494</v>
       </c>
@@ -5262,9 +5201,8 @@
       <c r="I76" s="19"/>
       <c r="J76" s="19"/>
       <c r="K76" s="19"/>
-      <c r="L76" s="19"/>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>170</v>
       </c>
@@ -5291,9 +5229,8 @@
       <c r="I77" s="19"/>
       <c r="J77" s="19"/>
       <c r="K77" s="19"/>
-      <c r="L77" s="19"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>130</v>
       </c>
@@ -5320,9 +5257,8 @@
       <c r="I78" s="19"/>
       <c r="J78" s="19"/>
       <c r="K78" s="19"/>
-      <c r="L78" s="19"/>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>161</v>
       </c>
@@ -5349,9 +5285,8 @@
       <c r="I79" s="19"/>
       <c r="J79" s="19"/>
       <c r="K79" s="19"/>
-      <c r="L79" s="19"/>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>137</v>
       </c>
@@ -5378,9 +5313,8 @@
       <c r="I80" s="19"/>
       <c r="J80" s="19"/>
       <c r="K80" s="19"/>
-      <c r="L80" s="19"/>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>503</v>
       </c>
@@ -5407,9 +5341,8 @@
       <c r="I81" s="19"/>
       <c r="J81" s="19"/>
       <c r="K81" s="19"/>
-      <c r="L81" s="19"/>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>506</v>
       </c>
@@ -5436,9 +5369,8 @@
       <c r="I82" s="19"/>
       <c r="J82" s="19"/>
       <c r="K82" s="19"/>
-      <c r="L82" s="19"/>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>509</v>
       </c>
@@ -5465,9 +5397,8 @@
       <c r="I83" s="19"/>
       <c r="J83" s="19"/>
       <c r="K83" s="19"/>
-      <c r="L83" s="19"/>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>512</v>
       </c>
@@ -5494,9 +5425,8 @@
       <c r="I84" s="19"/>
       <c r="J84" s="19"/>
       <c r="K84" s="19"/>
-      <c r="L84" s="19"/>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>116</v>
       </c>
@@ -5523,9 +5453,8 @@
       <c r="I85" s="19"/>
       <c r="J85" s="19"/>
       <c r="K85" s="19"/>
-      <c r="L85" s="19"/>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>516</v>
       </c>
@@ -5552,9 +5481,8 @@
       <c r="I86" s="19"/>
       <c r="J86" s="19"/>
       <c r="K86" s="19"/>
-      <c r="L86" s="19"/>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>519</v>
       </c>
@@ -5581,9 +5509,8 @@
       <c r="I87" s="19"/>
       <c r="J87" s="19"/>
       <c r="K87" s="19"/>
-      <c r="L87" s="19"/>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>519</v>
       </c>
@@ -5610,9 +5537,8 @@
       <c r="I88" s="19"/>
       <c r="J88" s="19"/>
       <c r="K88" s="19"/>
-      <c r="L88" s="19"/>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>519</v>
       </c>
@@ -5639,9 +5565,8 @@
       <c r="I89" s="19"/>
       <c r="J89" s="19"/>
       <c r="K89" s="19"/>
-      <c r="L89" s="19"/>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>522</v>
       </c>
@@ -5668,9 +5593,8 @@
       <c r="I90" s="19"/>
       <c r="J90" s="19"/>
       <c r="K90" s="19"/>
-      <c r="L90" s="19"/>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>525</v>
       </c>
@@ -5697,9 +5621,8 @@
       <c r="I91" s="19"/>
       <c r="J91" s="19"/>
       <c r="K91" s="19"/>
-      <c r="L91" s="19"/>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>117</v>
       </c>
@@ -5726,9 +5649,8 @@
       <c r="I92" s="19"/>
       <c r="J92" s="19"/>
       <c r="K92" s="19"/>
-      <c r="L92" s="19"/>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>529</v>
       </c>
@@ -5755,9 +5677,8 @@
       <c r="I93" s="19"/>
       <c r="J93" s="19"/>
       <c r="K93" s="19"/>
-      <c r="L93" s="19"/>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>529</v>
       </c>
@@ -5784,9 +5705,8 @@
       <c r="I94" s="19"/>
       <c r="J94" s="19"/>
       <c r="K94" s="19"/>
-      <c r="L94" s="19"/>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>529</v>
       </c>
@@ -5813,9 +5733,8 @@
       <c r="I95" s="19"/>
       <c r="J95" s="19"/>
       <c r="K95" s="19"/>
-      <c r="L95" s="19"/>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>531</v>
       </c>
@@ -5842,9 +5761,8 @@
       <c r="I96" s="19"/>
       <c r="J96" s="19"/>
       <c r="K96" s="19"/>
-      <c r="L96" s="19"/>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>536</v>
       </c>
@@ -5871,9 +5789,8 @@
       <c r="I97" s="19"/>
       <c r="J97" s="19"/>
       <c r="K97" s="19"/>
-      <c r="L97" s="19"/>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>536</v>
       </c>
@@ -5900,9 +5817,8 @@
       <c r="I98" s="19"/>
       <c r="J98" s="19"/>
       <c r="K98" s="19"/>
-      <c r="L98" s="19"/>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>534</v>
       </c>
@@ -5929,9 +5845,8 @@
       <c r="I99" s="19"/>
       <c r="J99" s="19"/>
       <c r="K99" s="19"/>
-      <c r="L99" s="19"/>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>267</v>
       </c>
@@ -5958,9 +5873,8 @@
       <c r="I100" s="19"/>
       <c r="J100" s="19"/>
       <c r="K100" s="19"/>
-      <c r="L100" s="19"/>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>267</v>
       </c>
@@ -5987,9 +5901,8 @@
       <c r="I101" s="19"/>
       <c r="J101" s="19"/>
       <c r="K101" s="19"/>
-      <c r="L101" s="19"/>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>540</v>
       </c>
@@ -6016,9 +5929,8 @@
       <c r="I102" s="19"/>
       <c r="J102" s="19"/>
       <c r="K102" s="19"/>
-      <c r="L102" s="19"/>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>540</v>
       </c>
@@ -6045,9 +5957,8 @@
       <c r="I103" s="19"/>
       <c r="J103" s="19"/>
       <c r="K103" s="19"/>
-      <c r="L103" s="19"/>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>540</v>
       </c>
@@ -6074,9 +5985,8 @@
       <c r="I104" s="19"/>
       <c r="J104" s="19"/>
       <c r="K104" s="19"/>
-      <c r="L104" s="19"/>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>543</v>
       </c>
@@ -6103,9 +6013,8 @@
       <c r="I105" s="19"/>
       <c r="J105" s="19"/>
       <c r="K105" s="19"/>
-      <c r="L105" s="19"/>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>543</v>
       </c>
@@ -6132,9 +6041,8 @@
       <c r="I106" s="19"/>
       <c r="J106" s="19"/>
       <c r="K106" s="19"/>
-      <c r="L106" s="19"/>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>545</v>
       </c>
@@ -6161,9 +6069,8 @@
       <c r="I107" s="19"/>
       <c r="J107" s="19"/>
       <c r="K107" s="19"/>
-      <c r="L107" s="19"/>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>548</v>
       </c>
@@ -6190,9 +6097,8 @@
       <c r="I108" s="19"/>
       <c r="J108" s="19"/>
       <c r="K108" s="19"/>
-      <c r="L108" s="19"/>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>805</v>
       </c>
@@ -6219,9 +6125,8 @@
       <c r="I109" s="19"/>
       <c r="J109" s="19"/>
       <c r="K109" s="19"/>
-      <c r="L109" s="19"/>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>167</v>
       </c>
@@ -6248,9 +6153,8 @@
       <c r="I110" s="19"/>
       <c r="J110" s="19"/>
       <c r="K110" s="19"/>
-      <c r="L110" s="19"/>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>554</v>
       </c>
@@ -6277,9 +6181,8 @@
       <c r="I111" s="19"/>
       <c r="J111" s="19"/>
       <c r="K111" s="19"/>
-      <c r="L111" s="19"/>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>295</v>
       </c>
@@ -6306,9 +6209,8 @@
       <c r="I112" s="19"/>
       <c r="J112" s="19"/>
       <c r="K112" s="19"/>
-      <c r="L112" s="19"/>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>558</v>
       </c>
@@ -6335,9 +6237,8 @@
       <c r="I113" s="19"/>
       <c r="J113" s="19"/>
       <c r="K113" s="19"/>
-      <c r="L113" s="19"/>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>560</v>
       </c>
@@ -6364,9 +6265,8 @@
       <c r="I114" s="19"/>
       <c r="J114" s="19"/>
       <c r="K114" s="19"/>
-      <c r="L114" s="19"/>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>110</v>
       </c>
@@ -6393,9 +6293,8 @@
       <c r="I115" s="19"/>
       <c r="J115" s="19"/>
       <c r="K115" s="19"/>
-      <c r="L115" s="19"/>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>353</v>
       </c>
@@ -6422,9 +6321,8 @@
       <c r="I116" s="19"/>
       <c r="J116" s="19"/>
       <c r="K116" s="19"/>
-      <c r="L116" s="19"/>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>564</v>
       </c>
@@ -6451,9 +6349,8 @@
       <c r="I117" s="19"/>
       <c r="J117" s="19"/>
       <c r="K117" s="19"/>
-      <c r="L117" s="19"/>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>564</v>
       </c>
@@ -6480,9 +6377,8 @@
       <c r="I118" s="19"/>
       <c r="J118" s="19"/>
       <c r="K118" s="19"/>
-      <c r="L118" s="19"/>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>350</v>
       </c>
@@ -6509,9 +6405,8 @@
       <c r="I119" s="19"/>
       <c r="J119" s="19"/>
       <c r="K119" s="19"/>
-      <c r="L119" s="19"/>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>568</v>
       </c>
@@ -6538,9 +6433,8 @@
       <c r="I120" s="19"/>
       <c r="J120" s="19"/>
       <c r="K120" s="19"/>
-      <c r="L120" s="19"/>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>568</v>
       </c>
@@ -6567,9 +6461,8 @@
       <c r="I121" s="19"/>
       <c r="J121" s="19"/>
       <c r="K121" s="19"/>
-      <c r="L121" s="19"/>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>800</v>
       </c>
@@ -6596,9 +6489,8 @@
       <c r="I122" s="19"/>
       <c r="J122" s="19"/>
       <c r="K122" s="19"/>
-      <c r="L122" s="19"/>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>121</v>
       </c>
@@ -6625,9 +6517,8 @@
       <c r="I123" s="19"/>
       <c r="J123" s="19"/>
       <c r="K123" s="19"/>
-      <c r="L123" s="19"/>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>572</v>
       </c>
@@ -6654,9 +6545,8 @@
       <c r="I124" s="19"/>
       <c r="J124" s="19"/>
       <c r="K124" s="19"/>
-      <c r="L124" s="19"/>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>572</v>
       </c>
@@ -6683,9 +6573,8 @@
       <c r="I125" s="19"/>
       <c r="J125" s="19"/>
       <c r="K125" s="19"/>
-      <c r="L125" s="19"/>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>575</v>
       </c>
@@ -6712,9 +6601,8 @@
       <c r="I126" s="19"/>
       <c r="J126" s="19"/>
       <c r="K126" s="19"/>
-      <c r="L126" s="19"/>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>135</v>
       </c>
@@ -6741,9 +6629,8 @@
       <c r="I127" s="19"/>
       <c r="J127" s="19"/>
       <c r="K127" s="19"/>
-      <c r="L127" s="19"/>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>231</v>
       </c>
@@ -6770,9 +6657,8 @@
       <c r="I128" s="19"/>
       <c r="J128" s="19"/>
       <c r="K128" s="19"/>
-      <c r="L128" s="19"/>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>581</v>
       </c>
@@ -6799,9 +6685,8 @@
       <c r="I129" s="19"/>
       <c r="J129" s="19"/>
       <c r="K129" s="19"/>
-      <c r="L129" s="19"/>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>581</v>
       </c>
@@ -6828,9 +6713,8 @@
       <c r="I130" s="19"/>
       <c r="J130" s="19"/>
       <c r="K130" s="19"/>
-      <c r="L130" s="19"/>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>584</v>
       </c>
@@ -6857,9 +6741,8 @@
       <c r="I131" s="19"/>
       <c r="J131" s="19"/>
       <c r="K131" s="19"/>
-      <c r="L131" s="19"/>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>587</v>
       </c>
@@ -6886,9 +6769,8 @@
       <c r="I132" s="19"/>
       <c r="J132" s="19"/>
       <c r="K132" s="19"/>
-      <c r="L132" s="19"/>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>590</v>
       </c>
@@ -6915,9 +6797,8 @@
       <c r="I133" s="19"/>
       <c r="J133" s="19"/>
       <c r="K133" s="19"/>
-      <c r="L133" s="19"/>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>593</v>
       </c>
@@ -6944,9 +6825,8 @@
       <c r="I134" s="19"/>
       <c r="J134" s="19"/>
       <c r="K134" s="19"/>
-      <c r="L134" s="19"/>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>145</v>
       </c>
@@ -6973,9 +6853,8 @@
       <c r="I135" s="19"/>
       <c r="J135" s="19"/>
       <c r="K135" s="19"/>
-      <c r="L135" s="19"/>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>596</v>
       </c>
@@ -7002,9 +6881,8 @@
       <c r="I136" s="19"/>
       <c r="J136" s="19"/>
       <c r="K136" s="19"/>
-      <c r="L136" s="19"/>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>598</v>
       </c>
@@ -7031,9 +6909,8 @@
       <c r="I137" s="19"/>
       <c r="J137" s="19"/>
       <c r="K137" s="19"/>
-      <c r="L137" s="19"/>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>601</v>
       </c>
@@ -7060,9 +6937,8 @@
       <c r="I138" s="19"/>
       <c r="J138" s="19"/>
       <c r="K138" s="19"/>
-      <c r="L138" s="19"/>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>604</v>
       </c>
@@ -7089,9 +6965,8 @@
       <c r="I139" s="19"/>
       <c r="J139" s="19"/>
       <c r="K139" s="19"/>
-      <c r="L139" s="19"/>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>607</v>
       </c>
@@ -7118,9 +6993,8 @@
       <c r="I140" s="19"/>
       <c r="J140" s="19"/>
       <c r="K140" s="19"/>
-      <c r="L140" s="19"/>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>610</v>
       </c>
@@ -7147,9 +7021,8 @@
       <c r="I141" s="19"/>
       <c r="J141" s="19"/>
       <c r="K141" s="19"/>
-      <c r="L141" s="19"/>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>613</v>
       </c>
@@ -7176,9 +7049,8 @@
       <c r="I142" s="19"/>
       <c r="J142" s="19"/>
       <c r="K142" s="19"/>
-      <c r="L142" s="19"/>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>616</v>
       </c>
@@ -7205,9 +7077,8 @@
       <c r="I143" s="19"/>
       <c r="J143" s="19"/>
       <c r="K143" s="19"/>
-      <c r="L143" s="19"/>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>619</v>
       </c>
@@ -7234,9 +7105,8 @@
       <c r="I144" s="19"/>
       <c r="J144" s="19"/>
       <c r="K144" s="19"/>
-      <c r="L144" s="19"/>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>622</v>
       </c>
@@ -7263,9 +7133,8 @@
       <c r="I145" s="19"/>
       <c r="J145" s="19"/>
       <c r="K145" s="19"/>
-      <c r="L145" s="19"/>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>622</v>
       </c>
@@ -7292,9 +7161,8 @@
       <c r="I146" s="19"/>
       <c r="J146" s="19"/>
       <c r="K146" s="19"/>
-      <c r="L146" s="19"/>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>624</v>
       </c>
@@ -7321,9 +7189,8 @@
       <c r="I147" s="19"/>
       <c r="J147" s="19"/>
       <c r="K147" s="19"/>
-      <c r="L147" s="19"/>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>627</v>
       </c>
@@ -7350,9 +7217,8 @@
       <c r="I148" s="19"/>
       <c r="J148" s="19"/>
       <c r="K148" s="19"/>
-      <c r="L148" s="19"/>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>630</v>
       </c>
@@ -7379,9 +7245,8 @@
       <c r="I149" s="19"/>
       <c r="J149" s="19"/>
       <c r="K149" s="19"/>
-      <c r="L149" s="19"/>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>633</v>
       </c>
@@ -7408,9 +7273,8 @@
       <c r="I150" s="19"/>
       <c r="J150" s="19"/>
       <c r="K150" s="19"/>
-      <c r="L150" s="19"/>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>636</v>
       </c>
@@ -7437,9 +7301,8 @@
       <c r="I151" s="19"/>
       <c r="J151" s="19"/>
       <c r="K151" s="19"/>
-      <c r="L151" s="19"/>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>639</v>
       </c>
@@ -7466,9 +7329,8 @@
       <c r="I152" s="19"/>
       <c r="J152" s="19"/>
       <c r="K152" s="19"/>
-      <c r="L152" s="19"/>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>202</v>
       </c>
@@ -7495,9 +7357,8 @@
       <c r="I153" s="19"/>
       <c r="J153" s="19"/>
       <c r="K153" s="19"/>
-      <c r="L153" s="19"/>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>122</v>
       </c>
@@ -7524,9 +7385,8 @@
       <c r="I154" s="19"/>
       <c r="J154" s="19"/>
       <c r="K154" s="19"/>
-      <c r="L154" s="19"/>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>122</v>
       </c>
@@ -7553,9 +7413,8 @@
       <c r="I155" s="19"/>
       <c r="J155" s="19"/>
       <c r="K155" s="19"/>
-      <c r="L155" s="19"/>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>103</v>
       </c>
@@ -7582,9 +7441,8 @@
       <c r="I156" s="19"/>
       <c r="J156" s="19"/>
       <c r="K156" s="19"/>
-      <c r="L156" s="19"/>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>105</v>
       </c>
@@ -7611,9 +7469,8 @@
       <c r="I157" s="19"/>
       <c r="J157" s="19"/>
       <c r="K157" s="19"/>
-      <c r="L157" s="19"/>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>107</v>
       </c>
@@ -7640,9 +7497,8 @@
       <c r="I158" s="19"/>
       <c r="J158" s="19"/>
       <c r="K158" s="19"/>
-      <c r="L158" s="19"/>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>111</v>
       </c>
@@ -7669,9 +7525,8 @@
       <c r="I159" s="19"/>
       <c r="J159" s="19"/>
       <c r="K159" s="19"/>
-      <c r="L159" s="19"/>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>651</v>
       </c>
@@ -7698,9 +7553,8 @@
       <c r="I160" s="19"/>
       <c r="J160" s="19"/>
       <c r="K160" s="19"/>
-      <c r="L160" s="19"/>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>654</v>
       </c>
@@ -7727,9 +7581,8 @@
       <c r="I161" s="19"/>
       <c r="J161" s="19"/>
       <c r="K161" s="19"/>
-      <c r="L161" s="19"/>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>148</v>
       </c>
@@ -7756,9 +7609,8 @@
       <c r="I162" s="19"/>
       <c r="J162" s="19"/>
       <c r="K162" s="19"/>
-      <c r="L162" s="19"/>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>134</v>
       </c>
@@ -7785,9 +7637,8 @@
       <c r="I163" s="19"/>
       <c r="J163" s="19"/>
       <c r="K163" s="19"/>
-      <c r="L163" s="19"/>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>282</v>
       </c>
@@ -7814,9 +7665,8 @@
       <c r="I164" s="19"/>
       <c r="J164" s="19"/>
       <c r="K164" s="19"/>
-      <c r="L164" s="19"/>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>127</v>
       </c>
@@ -7843,9 +7693,8 @@
       <c r="I165" s="19"/>
       <c r="J165" s="19"/>
       <c r="K165" s="19"/>
-      <c r="L165" s="19"/>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>127</v>
       </c>
@@ -7872,9 +7721,8 @@
       <c r="I166" s="19"/>
       <c r="J166" s="19"/>
       <c r="K166" s="19"/>
-      <c r="L166" s="19"/>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>158</v>
       </c>
@@ -7901,9 +7749,8 @@
       <c r="I167" s="19"/>
       <c r="J167" s="19"/>
       <c r="K167" s="19"/>
-      <c r="L167" s="19"/>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>177</v>
       </c>
@@ -7930,9 +7777,8 @@
       <c r="I168" s="19"/>
       <c r="J168" s="19"/>
       <c r="K168" s="19"/>
-      <c r="L168" s="19"/>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>132</v>
       </c>
@@ -7959,9 +7805,8 @@
       <c r="I169" s="19"/>
       <c r="J169" s="19"/>
       <c r="K169" s="19"/>
-      <c r="L169" s="19"/>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>131</v>
       </c>
@@ -7988,9 +7833,8 @@
       <c r="I170" s="19"/>
       <c r="J170" s="19"/>
       <c r="K170" s="19"/>
-      <c r="L170" s="19"/>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>141</v>
       </c>
@@ -8017,9 +7861,8 @@
       <c r="I171" s="19"/>
       <c r="J171" s="19"/>
       <c r="K171" s="19"/>
-      <c r="L171" s="19"/>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>142</v>
       </c>
@@ -8046,9 +7889,8 @@
       <c r="I172" s="19"/>
       <c r="J172" s="19"/>
       <c r="K172" s="19"/>
-      <c r="L172" s="19"/>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>228</v>
       </c>
@@ -8075,9 +7917,8 @@
       <c r="I173" s="19"/>
       <c r="J173" s="19"/>
       <c r="K173" s="19"/>
-      <c r="L173" s="19"/>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>230</v>
       </c>
@@ -8104,9 +7945,8 @@
       <c r="I174" s="19"/>
       <c r="J174" s="19"/>
       <c r="K174" s="19"/>
-      <c r="L174" s="19"/>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>147</v>
       </c>
@@ -8133,9 +7973,8 @@
       <c r="I175" s="19"/>
       <c r="J175" s="19"/>
       <c r="K175" s="19"/>
-      <c r="L175" s="19"/>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>151</v>
       </c>
@@ -8162,9 +8001,8 @@
       <c r="I176" s="19"/>
       <c r="J176" s="19"/>
       <c r="K176" s="19"/>
-      <c r="L176" s="19"/>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>681</v>
       </c>
@@ -8191,9 +8029,8 @@
       <c r="I177" s="19"/>
       <c r="J177" s="19"/>
       <c r="K177" s="19"/>
-      <c r="L177" s="19"/>
-    </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>154</v>
       </c>
@@ -8220,9 +8057,8 @@
       <c r="I178" s="19"/>
       <c r="J178" s="19"/>
       <c r="K178" s="19"/>
-      <c r="L178" s="19"/>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>156</v>
       </c>
@@ -8249,9 +8085,8 @@
       <c r="I179" s="19"/>
       <c r="J179" s="19"/>
       <c r="K179" s="19"/>
-      <c r="L179" s="19"/>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>168</v>
       </c>
@@ -8278,9 +8113,8 @@
       <c r="I180" s="19"/>
       <c r="J180" s="19"/>
       <c r="K180" s="19"/>
-      <c r="L180" s="19"/>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>163</v>
       </c>
@@ -8307,9 +8141,8 @@
       <c r="I181" s="19"/>
       <c r="J181" s="19"/>
       <c r="K181" s="19"/>
-      <c r="L181" s="19"/>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>374</v>
       </c>
@@ -8336,9 +8169,8 @@
       <c r="I182" s="19"/>
       <c r="J182" s="19"/>
       <c r="K182" s="19"/>
-      <c r="L182" s="19"/>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>173</v>
       </c>
@@ -8365,9 +8197,8 @@
       <c r="I183" s="19"/>
       <c r="J183" s="19"/>
       <c r="K183" s="19"/>
-      <c r="L183" s="19"/>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>173</v>
       </c>
@@ -8394,9 +8225,8 @@
       <c r="I184" s="19"/>
       <c r="J184" s="19"/>
       <c r="K184" s="19"/>
-      <c r="L184" s="19"/>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>175</v>
       </c>
@@ -8423,9 +8253,8 @@
       <c r="I185" s="19"/>
       <c r="J185" s="19"/>
       <c r="K185" s="19"/>
-      <c r="L185" s="19"/>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>175</v>
       </c>
@@ -8452,9 +8281,8 @@
       <c r="I186" s="19"/>
       <c r="J186" s="19"/>
       <c r="K186" s="19"/>
-      <c r="L186" s="19"/>
-    </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>175</v>
       </c>
@@ -8481,9 +8309,8 @@
       <c r="I187" s="19"/>
       <c r="J187" s="19"/>
       <c r="K187" s="19"/>
-      <c r="L187" s="19"/>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>179</v>
       </c>
@@ -8510,9 +8337,8 @@
       <c r="I188" s="19"/>
       <c r="J188" s="19"/>
       <c r="K188" s="19"/>
-      <c r="L188" s="19"/>
-    </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>696</v>
       </c>
@@ -8539,9 +8365,8 @@
       <c r="I189" s="19"/>
       <c r="J189" s="19"/>
       <c r="K189" s="19"/>
-      <c r="L189" s="19"/>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>298</v>
       </c>
@@ -8568,9 +8393,8 @@
       <c r="I190" s="19"/>
       <c r="J190" s="19"/>
       <c r="K190" s="19"/>
-      <c r="L190" s="19"/>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>797</v>
       </c>
@@ -8597,9 +8421,8 @@
       <c r="I191" s="19"/>
       <c r="J191" s="19"/>
       <c r="K191" s="19"/>
-      <c r="L191" s="19"/>
-    </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>185</v>
       </c>
@@ -8626,9 +8449,8 @@
       <c r="I192" s="19"/>
       <c r="J192" s="19"/>
       <c r="K192" s="19"/>
-      <c r="L192" s="19"/>
-    </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>185</v>
       </c>
@@ -8655,9 +8477,8 @@
       <c r="I193" s="19"/>
       <c r="J193" s="19"/>
       <c r="K193" s="19"/>
-      <c r="L193" s="19"/>
-    </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>183</v>
       </c>
@@ -8684,9 +8505,8 @@
       <c r="I194" s="19"/>
       <c r="J194" s="19"/>
       <c r="K194" s="19"/>
-      <c r="L194" s="19"/>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>703</v>
       </c>
@@ -8713,9 +8533,8 @@
       <c r="I195" s="19"/>
       <c r="J195" s="19"/>
       <c r="K195" s="19"/>
-      <c r="L195" s="19"/>
-    </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>705</v>
       </c>
@@ -8742,9 +8561,8 @@
       <c r="I196" s="19"/>
       <c r="J196" s="19"/>
       <c r="K196" s="19"/>
-      <c r="L196" s="19"/>
-    </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>188</v>
       </c>
@@ -8771,9 +8589,8 @@
       <c r="I197" s="19"/>
       <c r="J197" s="19"/>
       <c r="K197" s="19"/>
-      <c r="L197" s="19"/>
-    </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>191</v>
       </c>
@@ -8800,9 +8617,8 @@
       <c r="I198" s="19"/>
       <c r="J198" s="19"/>
       <c r="K198" s="19"/>
-      <c r="L198" s="19"/>
-    </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>711</v>
       </c>
@@ -8829,9 +8645,8 @@
       <c r="I199" s="19"/>
       <c r="J199" s="19"/>
       <c r="K199" s="19"/>
-      <c r="L199" s="19"/>
-    </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>219</v>
       </c>
@@ -8858,9 +8673,8 @@
       <c r="I200" s="19"/>
       <c r="J200" s="19"/>
       <c r="K200" s="19"/>
-      <c r="L200" s="19"/>
-    </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>713</v>
       </c>
@@ -8887,9 +8701,8 @@
       <c r="I201" s="19"/>
       <c r="J201" s="19"/>
       <c r="K201" s="19"/>
-      <c r="L201" s="19"/>
-    </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>716</v>
       </c>
@@ -8916,9 +8729,8 @@
       <c r="I202" s="19"/>
       <c r="J202" s="19"/>
       <c r="K202" s="19"/>
-      <c r="L202" s="19"/>
-    </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>359</v>
       </c>
@@ -8945,9 +8757,8 @@
       <c r="I203" s="19"/>
       <c r="J203" s="19"/>
       <c r="K203" s="19"/>
-      <c r="L203" s="19"/>
-    </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>204</v>
       </c>
@@ -8974,9 +8785,8 @@
       <c r="I204" s="19"/>
       <c r="J204" s="19"/>
       <c r="K204" s="19"/>
-      <c r="L204" s="19"/>
-    </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>206</v>
       </c>
@@ -9003,9 +8813,8 @@
       <c r="I205" s="19"/>
       <c r="J205" s="19"/>
       <c r="K205" s="19"/>
-      <c r="L205" s="19"/>
-    </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>240</v>
       </c>
@@ -9032,9 +8841,8 @@
       <c r="I206" s="19"/>
       <c r="J206" s="19"/>
       <c r="K206" s="19"/>
-      <c r="L206" s="19"/>
-    </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>212</v>
       </c>
@@ -9061,9 +8869,8 @@
       <c r="I207" s="19"/>
       <c r="J207" s="19"/>
       <c r="K207" s="19"/>
-      <c r="L207" s="19"/>
-    </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>226</v>
       </c>
@@ -9090,9 +8897,8 @@
       <c r="I208" s="19"/>
       <c r="J208" s="19"/>
       <c r="K208" s="19"/>
-      <c r="L208" s="19"/>
-    </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>221</v>
       </c>
@@ -9119,9 +8925,8 @@
       <c r="I209" s="19"/>
       <c r="J209" s="19"/>
       <c r="K209" s="19"/>
-      <c r="L209" s="19"/>
-    </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>221</v>
       </c>
@@ -9148,9 +8953,8 @@
       <c r="I210" s="19"/>
       <c r="J210" s="19"/>
       <c r="K210" s="19"/>
-      <c r="L210" s="19"/>
-    </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>221</v>
       </c>
@@ -9177,9 +8981,8 @@
       <c r="I211" s="19"/>
       <c r="J211" s="19"/>
       <c r="K211" s="19"/>
-      <c r="L211" s="19"/>
-    </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>221</v>
       </c>
@@ -9206,9 +9009,8 @@
       <c r="I212" s="19"/>
       <c r="J212" s="19"/>
       <c r="K212" s="19"/>
-      <c r="L212" s="19"/>
-    </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>221</v>
       </c>
@@ -9235,9 +9037,8 @@
       <c r="I213" s="19"/>
       <c r="J213" s="19"/>
       <c r="K213" s="19"/>
-      <c r="L213" s="19"/>
-    </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>732</v>
       </c>
@@ -9264,9 +9065,8 @@
       <c r="I214" s="19"/>
       <c r="J214" s="19"/>
       <c r="K214" s="19"/>
-      <c r="L214" s="19"/>
-    </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>232</v>
       </c>
@@ -9293,9 +9093,8 @@
       <c r="I215" s="19"/>
       <c r="J215" s="19"/>
       <c r="K215" s="19"/>
-      <c r="L215" s="19"/>
-    </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>242</v>
       </c>
@@ -9322,9 +9121,8 @@
       <c r="I216" s="19"/>
       <c r="J216" s="19"/>
       <c r="K216" s="19"/>
-      <c r="L216" s="19"/>
-    </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>247</v>
       </c>
@@ -9351,9 +9149,8 @@
       <c r="I217" s="19"/>
       <c r="J217" s="19"/>
       <c r="K217" s="19"/>
-      <c r="L217" s="19"/>
-    </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>740</v>
       </c>
@@ -9380,9 +9177,8 @@
       <c r="I218" s="19"/>
       <c r="J218" s="19"/>
       <c r="K218" s="19"/>
-      <c r="L218" s="19"/>
-    </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>251</v>
       </c>
@@ -9409,9 +9205,8 @@
       <c r="I219" s="19"/>
       <c r="J219" s="19"/>
       <c r="K219" s="19"/>
-      <c r="L219" s="19"/>
-    </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>276</v>
       </c>
@@ -9438,9 +9233,8 @@
       <c r="I220" s="19"/>
       <c r="J220" s="19"/>
       <c r="K220" s="19"/>
-      <c r="L220" s="19"/>
-    </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>746</v>
       </c>
@@ -9467,9 +9261,8 @@
       <c r="I221" s="19"/>
       <c r="J221" s="19"/>
       <c r="K221" s="19"/>
-      <c r="L221" s="19"/>
-    </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>257</v>
       </c>
@@ -9496,9 +9289,8 @@
       <c r="I222" s="19"/>
       <c r="J222" s="19"/>
       <c r="K222" s="19"/>
-      <c r="L222" s="19"/>
-    </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>748</v>
       </c>
@@ -9525,9 +9317,8 @@
       <c r="I223" s="19"/>
       <c r="J223" s="19"/>
       <c r="K223" s="19"/>
-      <c r="L223" s="19"/>
-    </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>263</v>
       </c>
@@ -9554,9 +9345,8 @@
       <c r="I224" s="19"/>
       <c r="J224" s="19"/>
       <c r="K224" s="19"/>
-      <c r="L224" s="19"/>
-    </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>260</v>
       </c>
@@ -9583,9 +9373,8 @@
       <c r="I225" s="19"/>
       <c r="J225" s="19"/>
       <c r="K225" s="19"/>
-      <c r="L225" s="19"/>
-    </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>264</v>
       </c>
@@ -9612,9 +9401,8 @@
       <c r="I226" s="19"/>
       <c r="J226" s="19"/>
       <c r="K226" s="19"/>
-      <c r="L226" s="19"/>
-    </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>269</v>
       </c>
@@ -9641,9 +9429,8 @@
       <c r="I227" s="19"/>
       <c r="J227" s="19"/>
       <c r="K227" s="19"/>
-      <c r="L227" s="19"/>
-    </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>270</v>
       </c>
@@ -9670,9 +9457,8 @@
       <c r="I228" s="19"/>
       <c r="J228" s="19"/>
       <c r="K228" s="19"/>
-      <c r="L228" s="19"/>
-    </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>270</v>
       </c>
@@ -9699,9 +9485,8 @@
       <c r="I229" s="19"/>
       <c r="J229" s="19"/>
       <c r="K229" s="19"/>
-      <c r="L229" s="19"/>
-    </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>279</v>
       </c>
@@ -9728,9 +9513,8 @@
       <c r="I230" s="19"/>
       <c r="J230" s="19"/>
       <c r="K230" s="19"/>
-      <c r="L230" s="19"/>
-    </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>278</v>
       </c>
@@ -9757,9 +9541,8 @@
       <c r="I231" s="19"/>
       <c r="J231" s="19"/>
       <c r="K231" s="19"/>
-      <c r="L231" s="19"/>
-    </row>
-    <row r="232" spans="1:12" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="232" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>284</v>
       </c>
@@ -9786,9 +9569,8 @@
       <c r="I232" s="20"/>
       <c r="J232" s="20"/>
       <c r="K232" s="20"/>
-      <c r="L232" s="20"/>
-    </row>
-    <row r="233" spans="1:12" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="233" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>765</v>
       </c>
@@ -9815,9 +9597,8 @@
       <c r="I233" s="20"/>
       <c r="J233" s="20"/>
       <c r="K233" s="20"/>
-      <c r="L233" s="20"/>
-    </row>
-    <row r="234" spans="1:12" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="234" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>288</v>
       </c>
@@ -9844,9 +9625,8 @@
       <c r="I234" s="20"/>
       <c r="J234" s="20"/>
       <c r="K234" s="20"/>
-      <c r="L234" s="20"/>
-    </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>287</v>
       </c>
@@ -9873,9 +9653,8 @@
       <c r="I235" s="19"/>
       <c r="J235" s="19"/>
       <c r="K235" s="19"/>
-      <c r="L235" s="19"/>
-    </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>289</v>
       </c>
@@ -9902,9 +9681,8 @@
       <c r="I236" s="19"/>
       <c r="J236" s="19"/>
       <c r="K236" s="19"/>
-      <c r="L236" s="19"/>
-    </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>290</v>
       </c>
@@ -9931,9 +9709,8 @@
       <c r="I237" s="19"/>
       <c r="J237" s="19"/>
       <c r="K237" s="19"/>
-      <c r="L237" s="19"/>
-    </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>774</v>
       </c>
@@ -9960,9 +9737,8 @@
       <c r="I238" s="19"/>
       <c r="J238" s="19"/>
       <c r="K238" s="19"/>
-      <c r="L238" s="19"/>
-    </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>303</v>
       </c>
@@ -9989,9 +9765,8 @@
       <c r="I239" s="19"/>
       <c r="J239" s="19"/>
       <c r="K239" s="19"/>
-      <c r="L239" s="19"/>
-    </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>304</v>
       </c>
@@ -10018,9 +9793,8 @@
       <c r="I240" s="19"/>
       <c r="J240" s="19"/>
       <c r="K240" s="19"/>
-      <c r="L240" s="19"/>
-    </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>305</v>
       </c>
@@ -10047,9 +9821,8 @@
       <c r="I241" s="19"/>
       <c r="J241" s="19"/>
       <c r="K241" s="19"/>
-      <c r="L241" s="19"/>
-    </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>300</v>
       </c>
@@ -10076,9 +9849,8 @@
       <c r="I242" s="19"/>
       <c r="J242" s="19"/>
       <c r="K242" s="19"/>
-      <c r="L242" s="19"/>
-    </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>348</v>
       </c>
@@ -10105,9 +9877,8 @@
       <c r="I243" s="19"/>
       <c r="J243" s="19"/>
       <c r="K243" s="19"/>
-      <c r="L243" s="19"/>
-    </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>357</v>
       </c>
@@ -10134,9 +9905,8 @@
       <c r="I244" s="19"/>
       <c r="J244" s="19"/>
       <c r="K244" s="19"/>
-      <c r="L244" s="19"/>
-    </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>351</v>
       </c>
@@ -10163,9 +9933,8 @@
       <c r="I245" s="19"/>
       <c r="J245" s="19"/>
       <c r="K245" s="19"/>
-      <c r="L245" s="19"/>
-    </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>361</v>
       </c>
@@ -10192,9 +9961,8 @@
       <c r="I246" s="19"/>
       <c r="J246" s="19"/>
       <c r="K246" s="19"/>
-      <c r="L246" s="19"/>
-    </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>365</v>
       </c>
@@ -10221,9 +9989,8 @@
       <c r="I247" s="19"/>
       <c r="J247" s="19"/>
       <c r="K247" s="19"/>
-      <c r="L247" s="19"/>
-    </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>363</v>
       </c>
@@ -10250,9 +10017,8 @@
       <c r="I248" s="19"/>
       <c r="J248" s="19"/>
       <c r="K248" s="19"/>
-      <c r="L248" s="19"/>
-    </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>355</v>
       </c>
@@ -10279,9 +10045,8 @@
       <c r="I249" s="19"/>
       <c r="J249" s="19"/>
       <c r="K249" s="19"/>
-      <c r="L249" s="19"/>
-    </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>368</v>
       </c>
@@ -10308,9 +10073,8 @@
       <c r="I250" s="19"/>
       <c r="J250" s="19"/>
       <c r="K250" s="19"/>
-      <c r="L250" s="19"/>
-    </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>367</v>
       </c>
@@ -10337,9 +10101,8 @@
       <c r="I251" s="19"/>
       <c r="J251" s="19"/>
       <c r="K251" s="19"/>
-      <c r="L251" s="19"/>
-    </row>
-    <row r="252" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="252" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>367</v>
       </c>
@@ -10366,9 +10129,8 @@
       <c r="I252" s="19"/>
       <c r="J252" s="19"/>
       <c r="K252" s="19"/>
-      <c r="L252" s="19"/>
-    </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>371</v>
       </c>
@@ -10395,9 +10157,8 @@
       <c r="I253" s="19"/>
       <c r="J253" s="19"/>
       <c r="K253" s="19"/>
-      <c r="L253" s="19"/>
-    </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.35">
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>816</v>
       </c>
@@ -10423,7 +10184,6 @@
       <c r="I254" s="19"/>
       <c r="J254" s="19"/>
       <c r="K254" s="19"/>
-      <c r="L254" s="19"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -10444,6 +10204,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100AF0C36E9CBDE43468AAB846756A8BA94" ma:contentTypeVersion="0" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="93c275e25462616b2c1de9b58ec156dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f6edc329ff236629c56e3b879b320d0">
     <xsd:element name="properties">
@@ -10557,12 +10323,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDD49F8-6691-4324-BC0D-0B1E4890A2C6}">
   <ds:schemaRefs>
@@ -10572,6 +10332,21 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEFD23-736F-4CE9-81DA-D9D145B9B572}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A01C7383-C303-4DC2-9970-99C89A193825}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10585,19 +10360,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEFD23-736F-4CE9-81DA-D9D145B9B572}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/procesos/inputs/Excel CCC Empresas.xlsx
+++ b/procesos/inputs/Excel CCC Empresas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonza\OneDrive\Nodus\Proyectos\Nodus-app\parche-gestoria\procesos\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DBD40A-3B58-4993-AA95-C70F225C335A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320CCD95-5745-4A57-8267-90C79DE2569C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14595" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,9 +16,9 @@
     <sheet name="BASE DE DATOS (NO TOCAR)" sheetId="14" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS (NO TOCAR)'!$A$1:$K$254</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS (NO TOCAR)'!$A$1:$J$254</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="826">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -2617,7 +2617,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2658,6 +2658,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3069,13 +3072,13 @@
         <v>823</v>
       </c>
       <c r="I1" s="9" t="s">
+        <v>821</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>822</v>
+      </c>
+      <c r="K1" s="9" t="s">
         <v>824</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>821</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
@@ -3185,10 +3188,10 @@
       <c r="G5" s="16" t="s">
         <v>383</v>
       </c>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
       <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
+      <c r="K5" s="22"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
@@ -3245,10 +3248,10 @@
         <v>825</v>
       </c>
       <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19" t="s">
+      <c r="J7" s="19" t="s">
         <v>825</v>
       </c>
+      <c r="K7" s="19"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
@@ -3276,9 +3279,7 @@
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
-      <c r="K8" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="K8" s="19"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
@@ -3304,9 +3305,7 @@
         <v>389</v>
       </c>
       <c r="H9" s="19"/>
-      <c r="I9" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="I9" s="19"/>
       <c r="J9" s="19"/>
       <c r="K9" s="19"/>
     </row>
@@ -3333,10 +3332,10 @@
       <c r="G10" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
       <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
+      <c r="K10" s="22"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
@@ -3389,10 +3388,18 @@
       <c r="G12" s="16" t="s">
         <v>393</v>
       </c>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
+      <c r="H12" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>825</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
@@ -3417,15 +3424,9 @@
       <c r="G13" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="H13" s="19" t="s">
-        <v>825</v>
-      </c>
-      <c r="I13" s="19" t="s">
-        <v>825</v>
-      </c>
-      <c r="J13" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
       <c r="K13" s="19"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -3451,15 +3452,9 @@
       <c r="G14" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="H14" s="19" t="s">
-        <v>825</v>
-      </c>
-      <c r="I14" s="19" t="s">
-        <v>825</v>
-      </c>
-      <c r="J14" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
       <c r="K14" s="19"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -3488,9 +3483,7 @@
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
       <c r="J15" s="19"/>
-      <c r="K15" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="K15" s="19"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
@@ -3517,9 +3510,7 @@
       </c>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
-      <c r="J16" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="J16" s="19"/>
       <c r="K16" s="19"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">

--- a/procesos/inputs/Excel CCC Empresas.xlsx
+++ b/procesos/inputs/Excel CCC Empresas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonza\OneDrive\Nodus\Proyectos\Nodus-app\parche-gestoria\procesos\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320CCD95-5745-4A57-8267-90C79DE2569C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD454C1B-0158-4083-9BF7-A71E771EED16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14595" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="BASE DE DATOS (NO TOCAR)" sheetId="14" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS (NO TOCAR)'!$A$1:$J$254</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BASE DE DATOS (NO TOCAR)'!$A$1:$K$254</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="826">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -3244,13 +3244,9 @@
       <c r="G7" s="16" t="s">
         <v>385</v>
       </c>
-      <c r="H7" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="H7" s="19"/>
       <c r="I7" s="19"/>
-      <c r="J7" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="J7" s="19"/>
       <c r="K7" s="19"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.35">
@@ -3279,7 +3275,9 @@
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
+      <c r="K8" s="19" t="s">
+        <v>825</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
@@ -4460,10 +4458,18 @@
       <c r="G50" s="16" t="s">
         <v>454</v>
       </c>
-      <c r="H50" s="19"/>
-      <c r="I50" s="19"/>
-      <c r="J50" s="19"/>
-      <c r="K50" s="19"/>
+      <c r="H50" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="I50" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="J50" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="K50" s="19" t="s">
+        <v>825</v>
+      </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
@@ -4488,10 +4494,18 @@
       <c r="G51" s="16" t="s">
         <v>454</v>
       </c>
-      <c r="H51" s="19"/>
-      <c r="I51" s="19"/>
-      <c r="J51" s="19"/>
-      <c r="K51" s="19"/>
+      <c r="H51" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="I51" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="J51" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="K51" s="19" t="s">
+        <v>825</v>
+      </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
@@ -7316,10 +7330,16 @@
       <c r="G152" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="H152" s="19"/>
-      <c r="I152" s="19"/>
+      <c r="H152" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="I152" s="19" t="s">
+        <v>825</v>
+      </c>
       <c r="J152" s="19"/>
-      <c r="K152" s="19"/>
+      <c r="K152" s="19" t="s">
+        <v>825</v>
+      </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
@@ -7627,7 +7647,9 @@
       <c r="H163" s="19"/>
       <c r="I163" s="19"/>
       <c r="J163" s="19"/>
-      <c r="K163" s="19"/>
+      <c r="K163" s="19" t="s">
+        <v>825</v>
+      </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
@@ -8355,7 +8377,9 @@
       <c r="H189" s="19"/>
       <c r="I189" s="19"/>
       <c r="J189" s="19"/>
-      <c r="K189" s="19"/>
+      <c r="K189" s="19" t="s">
+        <v>825</v>
+      </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
@@ -8719,7 +8743,9 @@
       <c r="H202" s="19"/>
       <c r="I202" s="19"/>
       <c r="J202" s="19"/>
-      <c r="K202" s="19"/>
+      <c r="K202" s="19" t="s">
+        <v>825</v>
+      </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
@@ -10177,6 +10203,7 @@
       <c r="K254" s="19"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K254" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="G254" r:id="rId1" xr:uid="{99771A5B-A528-4903-9C40-A57E66882FE1}"/>
   </hyperlinks>
@@ -10195,12 +10222,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100AF0C36E9CBDE43468AAB846756A8BA94" ma:contentTypeVersion="0" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="93c275e25462616b2c1de9b58ec156dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f6edc329ff236629c56e3b879b320d0">
     <xsd:element name="properties">
@@ -10314,6 +10335,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDD49F8-6691-4324-BC0D-0B1E4890A2C6}">
   <ds:schemaRefs>
@@ -10323,21 +10350,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEFD23-736F-4CE9-81DA-D9D145B9B572}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A01C7383-C303-4DC2-9970-99C89A193825}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10351,4 +10363,19 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEFD23-736F-4CE9-81DA-D9D145B9B572}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/procesos/inputs/Excel CCC Empresas.xlsx
+++ b/procesos/inputs/Excel CCC Empresas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonza\OneDrive\Nodus\Proyectos\Nodus-app\parche-gestoria\procesos\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD454C1B-0158-4083-9BF7-A71E771EED16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8B8180-7D09-47FF-9444-9131E349C0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14595" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE DE DATOS (NO TOCAR)" sheetId="14" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="826">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -3275,9 +3275,7 @@
       <c r="H8" s="19"/>
       <c r="I8" s="19"/>
       <c r="J8" s="19"/>
-      <c r="K8" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="K8" s="19"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
@@ -7337,9 +7335,7 @@
         <v>825</v>
       </c>
       <c r="J152" s="19"/>
-      <c r="K152" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="K152" s="19"/>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
@@ -10222,6 +10218,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100AF0C36E9CBDE43468AAB846756A8BA94" ma:contentTypeVersion="0" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="93c275e25462616b2c1de9b58ec156dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f6edc329ff236629c56e3b879b320d0">
     <xsd:element name="properties">
@@ -10335,12 +10337,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDD49F8-6691-4324-BC0D-0B1E4890A2C6}">
   <ds:schemaRefs>
@@ -10350,6 +10346,21 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEFD23-736F-4CE9-81DA-D9D145B9B572}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A01C7383-C303-4DC2-9970-99C89A193825}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10363,19 +10374,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEFD23-736F-4CE9-81DA-D9D145B9B572}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/procesos/inputs/Excel CCC Empresas.xlsx
+++ b/procesos/inputs/Excel CCC Empresas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonza\OneDrive\Nodus\Proyectos\Nodus-app\parche-gestoria\procesos\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D8B8180-7D09-47FF-9444-9131E349C0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C242D7F7-E515-4789-A0C5-D30CE6FD833A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/procesos/inputs/Excel CCC Empresas.xlsx
+++ b/procesos/inputs/Excel CCC Empresas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonza\OneDrive\Nodus\Proyectos\Nodus-app\parche-gestoria\procesos\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C242D7F7-E515-4789-A0C5-D30CE6FD833A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43299255-1594-49F4-914F-007F71A18D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14595" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE DE DATOS (NO TOCAR)" sheetId="14" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="826">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -3038,7 +3038,7 @@
     <col min="1" max="1" width="10.54296875" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="42.453125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.1796875" style="12" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="14.1796875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.81640625" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="58.7265625" style="6" customWidth="1"/>
@@ -3104,9 +3104,15 @@
       <c r="G2" s="16" t="s">
         <v>383</v>
       </c>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
+      <c r="H2" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>825</v>
+      </c>
       <c r="K2" s="19"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
@@ -3132,9 +3138,15 @@
       <c r="G3" s="16" t="s">
         <v>383</v>
       </c>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
+      <c r="H3" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>825</v>
+      </c>
       <c r="K3" s="19"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -3160,9 +3172,15 @@
       <c r="G4" s="16" t="s">
         <v>383</v>
       </c>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
+      <c r="H4" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="J4" s="19" t="s">
+        <v>825</v>
+      </c>
       <c r="K4" s="19"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
@@ -3188,9 +3206,15 @@
       <c r="G5" s="16" t="s">
         <v>383</v>
       </c>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="19"/>
+      <c r="H5" s="22" t="s">
+        <v>825</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>825</v>
+      </c>
+      <c r="J5" s="22" t="s">
+        <v>825</v>
+      </c>
       <c r="K5" s="22"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -3216,9 +3240,15 @@
       <c r="G6" s="16" t="s">
         <v>383</v>
       </c>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
+      <c r="H6" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>825</v>
+      </c>
+      <c r="J6" s="19" t="s">
+        <v>825</v>
+      </c>
       <c r="K6" s="19"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -3272,9 +3302,13 @@
       <c r="G8" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="H8" s="19"/>
+      <c r="H8" s="19" t="s">
+        <v>825</v>
+      </c>
       <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
+      <c r="J8" s="19" t="s">
+        <v>825</v>
+      </c>
       <c r="K8" s="19"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
@@ -3357,7 +3391,9 @@
         <v>391</v>
       </c>
       <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
+      <c r="I11" s="19" t="s">
+        <v>825</v>
+      </c>
       <c r="J11" s="19"/>
       <c r="K11" s="19"/>
     </row>
@@ -3384,15 +3420,9 @@
       <c r="G12" s="16" t="s">
         <v>393</v>
       </c>
-      <c r="H12" s="19" t="s">
-        <v>825</v>
-      </c>
-      <c r="I12" s="19" t="s">
-        <v>825</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
       <c r="K12" s="19" t="s">
         <v>825</v>
       </c>
@@ -4456,15 +4486,9 @@
       <c r="G50" s="16" t="s">
         <v>454</v>
       </c>
-      <c r="H50" s="19" t="s">
-        <v>825</v>
-      </c>
-      <c r="I50" s="19" t="s">
-        <v>825</v>
-      </c>
-      <c r="J50" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="H50" s="19"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="19"/>
       <c r="K50" s="19" t="s">
         <v>825</v>
       </c>
@@ -4492,15 +4516,9 @@
       <c r="G51" s="16" t="s">
         <v>454</v>
       </c>
-      <c r="H51" s="19" t="s">
-        <v>825</v>
-      </c>
-      <c r="I51" s="19" t="s">
-        <v>825</v>
-      </c>
-      <c r="J51" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="19"/>
       <c r="K51" s="19" t="s">
         <v>825</v>
       </c>

--- a/procesos/inputs/Excel CCC Empresas.xlsx
+++ b/procesos/inputs/Excel CCC Empresas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonza\OneDrive\Nodus\Proyectos\Nodus-app\parche-gestoria\procesos\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43299255-1594-49F4-914F-007F71A18D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEECCF61-CF74-4EC7-BC91-C9DB9055BA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14595" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="826">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -3423,9 +3423,7 @@
       <c r="H12" s="19"/>
       <c r="I12" s="19"/>
       <c r="J12" s="19"/>
-      <c r="K12" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="K12" s="19"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
@@ -4489,9 +4487,7 @@
       <c r="H50" s="19"/>
       <c r="I50" s="19"/>
       <c r="J50" s="19"/>
-      <c r="K50" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="K50" s="19"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
@@ -4519,9 +4515,7 @@
       <c r="H51" s="19"/>
       <c r="I51" s="19"/>
       <c r="J51" s="19"/>
-      <c r="K51" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="K51" s="19"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
@@ -7661,9 +7655,7 @@
       <c r="H163" s="19"/>
       <c r="I163" s="19"/>
       <c r="J163" s="19"/>
-      <c r="K163" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="K163" s="19"/>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
@@ -8391,9 +8383,7 @@
       <c r="H189" s="19"/>
       <c r="I189" s="19"/>
       <c r="J189" s="19"/>
-      <c r="K189" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="K189" s="19"/>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
@@ -10236,12 +10226,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100AF0C36E9CBDE43468AAB846756A8BA94" ma:contentTypeVersion="0" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="93c275e25462616b2c1de9b58ec156dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f6edc329ff236629c56e3b879b320d0">
     <xsd:element name="properties">
@@ -10355,6 +10339,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDD49F8-6691-4324-BC0D-0B1E4890A2C6}">
   <ds:schemaRefs>
@@ -10364,21 +10354,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEFD23-736F-4CE9-81DA-D9D145B9B572}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A01C7383-C303-4DC2-9970-99C89A193825}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10392,4 +10367,19 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEFD23-736F-4CE9-81DA-D9D145B9B572}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/procesos/inputs/Excel CCC Empresas.xlsx
+++ b/procesos/inputs/Excel CCC Empresas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonza\OneDrive\Nodus\Proyectos\Nodus-app\parche-gestoria\procesos\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEECCF61-CF74-4EC7-BC91-C9DB9055BA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8DA043-1D93-4251-915B-6B03C80601E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14595" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="826">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -3309,7 +3309,9 @@
       <c r="J8" s="19" t="s">
         <v>825</v>
       </c>
-      <c r="K8" s="19"/>
+      <c r="K8" s="19" t="s">
+        <v>825</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
@@ -6615,7 +6617,9 @@
       <c r="H126" s="19"/>
       <c r="I126" s="19"/>
       <c r="J126" s="19"/>
-      <c r="K126" s="19"/>
+      <c r="K126" s="19" t="s">
+        <v>825</v>
+      </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
@@ -10226,6 +10230,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100AF0C36E9CBDE43468AAB846756A8BA94" ma:contentTypeVersion="0" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="93c275e25462616b2c1de9b58ec156dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f6edc329ff236629c56e3b879b320d0">
     <xsd:element name="properties">
@@ -10339,12 +10349,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDD49F8-6691-4324-BC0D-0B1E4890A2C6}">
   <ds:schemaRefs>
@@ -10354,6 +10358,21 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEFD23-736F-4CE9-81DA-D9D145B9B572}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A01C7383-C303-4DC2-9970-99C89A193825}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10367,19 +10386,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEFD23-736F-4CE9-81DA-D9D145B9B572}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/procesos/inputs/Excel CCC Empresas.xlsx
+++ b/procesos/inputs/Excel CCC Empresas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonza\OneDrive\Nodus\Proyectos\Nodus-app\parche-gestoria\procesos\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\preprod\Documents\Proyectos\parche-gestoria\procesos\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEECCF61-CF74-4EC7-BC91-C9DB9055BA29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E9639C-05C2-4436-B1E1-829E28E4BA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14595" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE DE DATOS (NO TOCAR)" sheetId="14" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="826">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -3033,20 +3033,20 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:K254"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1796875" style="12" customWidth="1"/>
-    <col min="4" max="4" width="14.1796875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="58.7265625" style="6" customWidth="1"/>
-    <col min="8" max="11" width="10.81640625" style="21"/>
-    <col min="12" max="16384" width="10.81640625" style="6"/>
+    <col min="1" max="1" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="58.7109375" style="6" customWidth="1"/>
+    <col min="8" max="11" width="10.85546875" style="21"/>
+    <col min="12" max="16384" width="10.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>815</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>40</v>
       </c>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="K2" s="19"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K3" s="19"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="K4" s="19"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>40</v>
       </c>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="K5" s="22"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="K6" s="19"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -3279,7 +3279,7 @@
       <c r="J7" s="19"/>
       <c r="K7" s="19"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>215</v>
       </c>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="K8" s="19"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
@@ -3339,7 +3339,7 @@
       <c r="J9" s="19"/>
       <c r="K9" s="19"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
@@ -3367,7 +3367,7 @@
       <c r="J10" s="19"/>
       <c r="K10" s="22"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>45</v>
       </c>
@@ -3397,7 +3397,7 @@
       <c r="J11" s="19"/>
       <c r="K11" s="19"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>47</v>
       </c>
@@ -3425,7 +3425,7 @@
       <c r="J12" s="19"/>
       <c r="K12" s="19"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
@@ -3453,7 +3453,7 @@
       <c r="J13" s="19"/>
       <c r="K13" s="19"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>49</v>
       </c>
@@ -3481,7 +3481,7 @@
       <c r="J14" s="19"/>
       <c r="K14" s="19"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>50</v>
       </c>
@@ -3509,7 +3509,7 @@
       <c r="J15" s="19"/>
       <c r="K15" s="19"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -3537,7 +3537,7 @@
       <c r="J16" s="19"/>
       <c r="K16" s="19"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>223</v>
       </c>
@@ -3565,7 +3565,7 @@
       <c r="J17" s="19"/>
       <c r="K17" s="19"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>223</v>
       </c>
@@ -3593,7 +3593,7 @@
       <c r="J18" s="19"/>
       <c r="K18" s="19"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>223</v>
       </c>
@@ -3621,7 +3621,7 @@
       <c r="J19" s="19"/>
       <c r="K19" s="19"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>51</v>
       </c>
@@ -3649,7 +3649,7 @@
       <c r="J20" s="19"/>
       <c r="K20" s="19"/>
     </row>
-    <row r="21" spans="1:11" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>112</v>
       </c>
@@ -3677,7 +3677,7 @@
       <c r="J21" s="19"/>
       <c r="K21" s="19"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>52</v>
       </c>
@@ -3705,7 +3705,7 @@
       <c r="J22" s="19"/>
       <c r="K22" s="19"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>52</v>
       </c>
@@ -3733,7 +3733,7 @@
       <c r="J23" s="19"/>
       <c r="K23" s="19"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>236</v>
       </c>
@@ -3761,7 +3761,7 @@
       <c r="J24" s="19"/>
       <c r="K24" s="19"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>54</v>
       </c>
@@ -3789,7 +3789,7 @@
       <c r="J25" s="19"/>
       <c r="K25" s="19"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>55</v>
       </c>
@@ -3817,7 +3817,7 @@
       <c r="J26" s="19"/>
       <c r="K26" s="19"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>57</v>
       </c>
@@ -3845,7 +3845,7 @@
       <c r="J27" s="19"/>
       <c r="K27" s="19"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>59</v>
       </c>
@@ -3873,7 +3873,7 @@
       <c r="J28" s="19"/>
       <c r="K28" s="19"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>61</v>
       </c>
@@ -3901,7 +3901,7 @@
       <c r="J29" s="19"/>
       <c r="K29" s="19"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>61</v>
       </c>
@@ -3929,7 +3929,7 @@
       <c r="J30" s="19"/>
       <c r="K30" s="19"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>62</v>
       </c>
@@ -3957,7 +3957,7 @@
       <c r="J31" s="19"/>
       <c r="K31" s="19"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>63</v>
       </c>
@@ -3985,7 +3985,7 @@
       <c r="J32" s="19"/>
       <c r="K32" s="19"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>208</v>
       </c>
@@ -4013,7 +4013,7 @@
       <c r="J33" s="19"/>
       <c r="K33" s="19"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>65</v>
       </c>
@@ -4041,7 +4041,7 @@
       <c r="J34" s="19"/>
       <c r="K34" s="19"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>238</v>
       </c>
@@ -4069,7 +4069,7 @@
       <c r="J35" s="19"/>
       <c r="K35" s="19"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>113</v>
       </c>
@@ -4097,7 +4097,7 @@
       <c r="J36" s="19"/>
       <c r="K36" s="19"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>113</v>
       </c>
@@ -4125,7 +4125,7 @@
       <c r="J37" s="19"/>
       <c r="K37" s="19"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>67</v>
       </c>
@@ -4153,7 +4153,7 @@
       <c r="J38" s="19"/>
       <c r="K38" s="19"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>69</v>
       </c>
@@ -4181,7 +4181,7 @@
       <c r="J39" s="19"/>
       <c r="K39" s="19"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>71</v>
       </c>
@@ -4209,7 +4209,7 @@
       <c r="J40" s="19"/>
       <c r="K40" s="19"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>72</v>
       </c>
@@ -4237,7 +4237,7 @@
       <c r="J41" s="19"/>
       <c r="K41" s="19"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>431</v>
       </c>
@@ -4265,7 +4265,7 @@
       <c r="J42" s="19"/>
       <c r="K42" s="19"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>434</v>
       </c>
@@ -4293,7 +4293,7 @@
       <c r="J43" s="19"/>
       <c r="K43" s="19"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>436</v>
       </c>
@@ -4321,7 +4321,7 @@
       <c r="J44" s="19"/>
       <c r="K44" s="19"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>439</v>
       </c>
@@ -4349,7 +4349,7 @@
       <c r="J45" s="19"/>
       <c r="K45" s="19"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>442</v>
       </c>
@@ -4377,7 +4377,7 @@
       <c r="J46" s="19"/>
       <c r="K46" s="19"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>164</v>
       </c>
@@ -4405,7 +4405,7 @@
       <c r="J47" s="19"/>
       <c r="K47" s="19"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>214</v>
       </c>
@@ -4433,7 +4433,7 @@
       <c r="J48" s="19"/>
       <c r="K48" s="19"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>449</v>
       </c>
@@ -4461,7 +4461,7 @@
       <c r="J49" s="19"/>
       <c r="K49" s="19"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>262</v>
       </c>
@@ -4489,7 +4489,7 @@
       <c r="J50" s="19"/>
       <c r="K50" s="19"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>262</v>
       </c>
@@ -4517,7 +4517,7 @@
       <c r="J51" s="19"/>
       <c r="K51" s="19"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>451</v>
       </c>
@@ -4545,7 +4545,7 @@
       <c r="J52" s="19"/>
       <c r="K52" s="19"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>217</v>
       </c>
@@ -4573,7 +4573,7 @@
       <c r="J53" s="19"/>
       <c r="K53" s="19"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>217</v>
       </c>
@@ -4601,7 +4601,7 @@
       <c r="J54" s="19"/>
       <c r="K54" s="19"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>217</v>
       </c>
@@ -4629,7 +4629,7 @@
       <c r="J55" s="19"/>
       <c r="K55" s="19"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>217</v>
       </c>
@@ -4657,7 +4657,7 @@
       <c r="J56" s="19"/>
       <c r="K56" s="19"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>217</v>
       </c>
@@ -4685,7 +4685,7 @@
       <c r="J57" s="19"/>
       <c r="K57" s="19"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>217</v>
       </c>
@@ -4713,7 +4713,7 @@
       <c r="J58" s="19"/>
       <c r="K58" s="19"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>458</v>
       </c>
@@ -4741,7 +4741,7 @@
       <c r="J59" s="19"/>
       <c r="K59" s="19"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>461</v>
       </c>
@@ -4769,7 +4769,7 @@
       <c r="J60" s="19"/>
       <c r="K60" s="19"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>464</v>
       </c>
@@ -4797,7 +4797,7 @@
       <c r="J61" s="19"/>
       <c r="K61" s="19"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>467</v>
       </c>
@@ -4825,7 +4825,7 @@
       <c r="J62" s="19"/>
       <c r="K62" s="19"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>198</v>
       </c>
@@ -4853,7 +4853,7 @@
       <c r="J63" s="19"/>
       <c r="K63" s="19"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>198</v>
       </c>
@@ -4881,7 +4881,7 @@
       <c r="J64" s="19"/>
       <c r="K64" s="19"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>472</v>
       </c>
@@ -4909,7 +4909,7 @@
       <c r="J65" s="19"/>
       <c r="K65" s="19"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>474</v>
       </c>
@@ -4937,7 +4937,7 @@
       <c r="J66" s="19"/>
       <c r="K66" s="19"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>196</v>
       </c>
@@ -4965,7 +4965,7 @@
       <c r="J67" s="19"/>
       <c r="K67" s="19"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>478</v>
       </c>
@@ -4993,7 +4993,7 @@
       <c r="J68" s="19"/>
       <c r="K68" s="19"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>480</v>
       </c>
@@ -5021,7 +5021,7 @@
       <c r="J69" s="19"/>
       <c r="K69" s="19"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>480</v>
       </c>
@@ -5049,7 +5049,7 @@
       <c r="J70" s="19"/>
       <c r="K70" s="19"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>115</v>
       </c>
@@ -5077,7 +5077,7 @@
       <c r="J71" s="19"/>
       <c r="K71" s="19"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>485</v>
       </c>
@@ -5105,7 +5105,7 @@
       <c r="J72" s="19"/>
       <c r="K72" s="19"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>488</v>
       </c>
@@ -5133,7 +5133,7 @@
       <c r="J73" s="19"/>
       <c r="K73" s="19"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>491</v>
       </c>
@@ -5161,7 +5161,7 @@
       <c r="J74" s="19"/>
       <c r="K74" s="19"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>494</v>
       </c>
@@ -5189,7 +5189,7 @@
       <c r="J75" s="19"/>
       <c r="K75" s="19"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>494</v>
       </c>
@@ -5217,7 +5217,7 @@
       <c r="J76" s="19"/>
       <c r="K76" s="19"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>170</v>
       </c>
@@ -5245,7 +5245,7 @@
       <c r="J77" s="19"/>
       <c r="K77" s="19"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>130</v>
       </c>
@@ -5273,7 +5273,7 @@
       <c r="J78" s="19"/>
       <c r="K78" s="19"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>161</v>
       </c>
@@ -5301,7 +5301,7 @@
       <c r="J79" s="19"/>
       <c r="K79" s="19"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>137</v>
       </c>
@@ -5329,7 +5329,7 @@
       <c r="J80" s="19"/>
       <c r="K80" s="19"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>503</v>
       </c>
@@ -5357,7 +5357,7 @@
       <c r="J81" s="19"/>
       <c r="K81" s="19"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>506</v>
       </c>
@@ -5385,7 +5385,7 @@
       <c r="J82" s="19"/>
       <c r="K82" s="19"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>509</v>
       </c>
@@ -5413,7 +5413,7 @@
       <c r="J83" s="19"/>
       <c r="K83" s="19"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>512</v>
       </c>
@@ -5441,7 +5441,7 @@
       <c r="J84" s="19"/>
       <c r="K84" s="19"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>116</v>
       </c>
@@ -5469,7 +5469,7 @@
       <c r="J85" s="19"/>
       <c r="K85" s="19"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>516</v>
       </c>
@@ -5497,7 +5497,7 @@
       <c r="J86" s="19"/>
       <c r="K86" s="19"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>519</v>
       </c>
@@ -5525,7 +5525,7 @@
       <c r="J87" s="19"/>
       <c r="K87" s="19"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>519</v>
       </c>
@@ -5553,7 +5553,7 @@
       <c r="J88" s="19"/>
       <c r="K88" s="19"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>519</v>
       </c>
@@ -5581,7 +5581,7 @@
       <c r="J89" s="19"/>
       <c r="K89" s="19"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>522</v>
       </c>
@@ -5609,7 +5609,7 @@
       <c r="J90" s="19"/>
       <c r="K90" s="19"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>525</v>
       </c>
@@ -5637,7 +5637,7 @@
       <c r="J91" s="19"/>
       <c r="K91" s="19"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>117</v>
       </c>
@@ -5665,7 +5665,7 @@
       <c r="J92" s="19"/>
       <c r="K92" s="19"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>529</v>
       </c>
@@ -5693,7 +5693,7 @@
       <c r="J93" s="19"/>
       <c r="K93" s="19"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>529</v>
       </c>
@@ -5721,7 +5721,7 @@
       <c r="J94" s="19"/>
       <c r="K94" s="19"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>529</v>
       </c>
@@ -5749,7 +5749,7 @@
       <c r="J95" s="19"/>
       <c r="K95" s="19"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>531</v>
       </c>
@@ -5777,7 +5777,7 @@
       <c r="J96" s="19"/>
       <c r="K96" s="19"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>536</v>
       </c>
@@ -5805,7 +5805,7 @@
       <c r="J97" s="19"/>
       <c r="K97" s="19"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>536</v>
       </c>
@@ -5833,7 +5833,7 @@
       <c r="J98" s="19"/>
       <c r="K98" s="19"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>534</v>
       </c>
@@ -5861,7 +5861,7 @@
       <c r="J99" s="19"/>
       <c r="K99" s="19"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>267</v>
       </c>
@@ -5889,7 +5889,7 @@
       <c r="J100" s="19"/>
       <c r="K100" s="19"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>267</v>
       </c>
@@ -5917,7 +5917,7 @@
       <c r="J101" s="19"/>
       <c r="K101" s="19"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>540</v>
       </c>
@@ -5945,7 +5945,7 @@
       <c r="J102" s="19"/>
       <c r="K102" s="19"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>540</v>
       </c>
@@ -5973,7 +5973,7 @@
       <c r="J103" s="19"/>
       <c r="K103" s="19"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>540</v>
       </c>
@@ -6001,7 +6001,7 @@
       <c r="J104" s="19"/>
       <c r="K104" s="19"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>543</v>
       </c>
@@ -6029,7 +6029,7 @@
       <c r="J105" s="19"/>
       <c r="K105" s="19"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>543</v>
       </c>
@@ -6057,7 +6057,7 @@
       <c r="J106" s="19"/>
       <c r="K106" s="19"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>545</v>
       </c>
@@ -6085,7 +6085,7 @@
       <c r="J107" s="19"/>
       <c r="K107" s="19"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>548</v>
       </c>
@@ -6113,7 +6113,7 @@
       <c r="J108" s="19"/>
       <c r="K108" s="19"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>805</v>
       </c>
@@ -6141,7 +6141,7 @@
       <c r="J109" s="19"/>
       <c r="K109" s="19"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>167</v>
       </c>
@@ -6169,7 +6169,7 @@
       <c r="J110" s="19"/>
       <c r="K110" s="19"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>554</v>
       </c>
@@ -6197,7 +6197,7 @@
       <c r="J111" s="19"/>
       <c r="K111" s="19"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>295</v>
       </c>
@@ -6225,7 +6225,7 @@
       <c r="J112" s="19"/>
       <c r="K112" s="19"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>558</v>
       </c>
@@ -6253,7 +6253,7 @@
       <c r="J113" s="19"/>
       <c r="K113" s="19"/>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>560</v>
       </c>
@@ -6281,7 +6281,7 @@
       <c r="J114" s="19"/>
       <c r="K114" s="19"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>110</v>
       </c>
@@ -6309,7 +6309,7 @@
       <c r="J115" s="19"/>
       <c r="K115" s="19"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>353</v>
       </c>
@@ -6337,7 +6337,7 @@
       <c r="J116" s="19"/>
       <c r="K116" s="19"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>564</v>
       </c>
@@ -6365,7 +6365,7 @@
       <c r="J117" s="19"/>
       <c r="K117" s="19"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>564</v>
       </c>
@@ -6393,7 +6393,7 @@
       <c r="J118" s="19"/>
       <c r="K118" s="19"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>350</v>
       </c>
@@ -6421,7 +6421,7 @@
       <c r="J119" s="19"/>
       <c r="K119" s="19"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>568</v>
       </c>
@@ -6449,7 +6449,7 @@
       <c r="J120" s="19"/>
       <c r="K120" s="19"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>568</v>
       </c>
@@ -6477,7 +6477,7 @@
       <c r="J121" s="19"/>
       <c r="K121" s="19"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>800</v>
       </c>
@@ -6505,7 +6505,7 @@
       <c r="J122" s="19"/>
       <c r="K122" s="19"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>121</v>
       </c>
@@ -6533,7 +6533,7 @@
       <c r="J123" s="19"/>
       <c r="K123" s="19"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>572</v>
       </c>
@@ -6561,7 +6561,7 @@
       <c r="J124" s="19"/>
       <c r="K124" s="19"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>572</v>
       </c>
@@ -6589,7 +6589,7 @@
       <c r="J125" s="19"/>
       <c r="K125" s="19"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>575</v>
       </c>
@@ -6615,9 +6615,11 @@
       <c r="H126" s="19"/>
       <c r="I126" s="19"/>
       <c r="J126" s="19"/>
-      <c r="K126" s="19"/>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K126" s="19" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>135</v>
       </c>
@@ -6645,7 +6647,7 @@
       <c r="J127" s="19"/>
       <c r="K127" s="19"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>231</v>
       </c>
@@ -6673,7 +6675,7 @@
       <c r="J128" s="19"/>
       <c r="K128" s="19"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>581</v>
       </c>
@@ -6701,7 +6703,7 @@
       <c r="J129" s="19"/>
       <c r="K129" s="19"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>581</v>
       </c>
@@ -6729,7 +6731,7 @@
       <c r="J130" s="19"/>
       <c r="K130" s="19"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>584</v>
       </c>
@@ -6757,7 +6759,7 @@
       <c r="J131" s="19"/>
       <c r="K131" s="19"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>587</v>
       </c>
@@ -6785,7 +6787,7 @@
       <c r="J132" s="19"/>
       <c r="K132" s="19"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>590</v>
       </c>
@@ -6813,7 +6815,7 @@
       <c r="J133" s="19"/>
       <c r="K133" s="19"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>593</v>
       </c>
@@ -6841,7 +6843,7 @@
       <c r="J134" s="19"/>
       <c r="K134" s="19"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>145</v>
       </c>
@@ -6869,7 +6871,7 @@
       <c r="J135" s="19"/>
       <c r="K135" s="19"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>596</v>
       </c>
@@ -6897,7 +6899,7 @@
       <c r="J136" s="19"/>
       <c r="K136" s="19"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>598</v>
       </c>
@@ -6925,7 +6927,7 @@
       <c r="J137" s="19"/>
       <c r="K137" s="19"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>601</v>
       </c>
@@ -6953,7 +6955,7 @@
       <c r="J138" s="19"/>
       <c r="K138" s="19"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>604</v>
       </c>
@@ -6981,7 +6983,7 @@
       <c r="J139" s="19"/>
       <c r="K139" s="19"/>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>607</v>
       </c>
@@ -7009,7 +7011,7 @@
       <c r="J140" s="19"/>
       <c r="K140" s="19"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>610</v>
       </c>
@@ -7037,7 +7039,7 @@
       <c r="J141" s="19"/>
       <c r="K141" s="19"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>613</v>
       </c>
@@ -7065,7 +7067,7 @@
       <c r="J142" s="19"/>
       <c r="K142" s="19"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>616</v>
       </c>
@@ -7093,7 +7095,7 @@
       <c r="J143" s="19"/>
       <c r="K143" s="19"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>619</v>
       </c>
@@ -7121,7 +7123,7 @@
       <c r="J144" s="19"/>
       <c r="K144" s="19"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>622</v>
       </c>
@@ -7149,7 +7151,7 @@
       <c r="J145" s="19"/>
       <c r="K145" s="19"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>622</v>
       </c>
@@ -7177,7 +7179,7 @@
       <c r="J146" s="19"/>
       <c r="K146" s="19"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>624</v>
       </c>
@@ -7205,7 +7207,7 @@
       <c r="J147" s="19"/>
       <c r="K147" s="19"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>627</v>
       </c>
@@ -7233,7 +7235,7 @@
       <c r="J148" s="19"/>
       <c r="K148" s="19"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>630</v>
       </c>
@@ -7261,7 +7263,7 @@
       <c r="J149" s="19"/>
       <c r="K149" s="19"/>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>633</v>
       </c>
@@ -7289,7 +7291,7 @@
       <c r="J150" s="19"/>
       <c r="K150" s="19"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>636</v>
       </c>
@@ -7317,7 +7319,7 @@
       <c r="J151" s="19"/>
       <c r="K151" s="19"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>639</v>
       </c>
@@ -7349,7 +7351,7 @@
       <c r="J152" s="19"/>
       <c r="K152" s="19"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>202</v>
       </c>
@@ -7377,7 +7379,7 @@
       <c r="J153" s="19"/>
       <c r="K153" s="19"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>122</v>
       </c>
@@ -7405,7 +7407,7 @@
       <c r="J154" s="19"/>
       <c r="K154" s="19"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>122</v>
       </c>
@@ -7433,7 +7435,7 @@
       <c r="J155" s="19"/>
       <c r="K155" s="19"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>103</v>
       </c>
@@ -7461,7 +7463,7 @@
       <c r="J156" s="19"/>
       <c r="K156" s="19"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>105</v>
       </c>
@@ -7489,7 +7491,7 @@
       <c r="J157" s="19"/>
       <c r="K157" s="19"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>107</v>
       </c>
@@ -7517,7 +7519,7 @@
       <c r="J158" s="19"/>
       <c r="K158" s="19"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>111</v>
       </c>
@@ -7545,7 +7547,7 @@
       <c r="J159" s="19"/>
       <c r="K159" s="19"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>651</v>
       </c>
@@ -7573,7 +7575,7 @@
       <c r="J160" s="19"/>
       <c r="K160" s="19"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>654</v>
       </c>
@@ -7601,7 +7603,7 @@
       <c r="J161" s="19"/>
       <c r="K161" s="19"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>148</v>
       </c>
@@ -7629,7 +7631,7 @@
       <c r="J162" s="19"/>
       <c r="K162" s="19"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>134</v>
       </c>
@@ -7655,9 +7657,11 @@
       <c r="H163" s="19"/>
       <c r="I163" s="19"/>
       <c r="J163" s="19"/>
-      <c r="K163" s="19"/>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K163" s="19" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>282</v>
       </c>
@@ -7685,7 +7689,7 @@
       <c r="J164" s="19"/>
       <c r="K164" s="19"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>127</v>
       </c>
@@ -7713,7 +7717,7 @@
       <c r="J165" s="19"/>
       <c r="K165" s="19"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>127</v>
       </c>
@@ -7741,7 +7745,7 @@
       <c r="J166" s="19"/>
       <c r="K166" s="19"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>158</v>
       </c>
@@ -7769,7 +7773,7 @@
       <c r="J167" s="19"/>
       <c r="K167" s="19"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>177</v>
       </c>
@@ -7797,7 +7801,7 @@
       <c r="J168" s="19"/>
       <c r="K168" s="19"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>132</v>
       </c>
@@ -7825,7 +7829,7 @@
       <c r="J169" s="19"/>
       <c r="K169" s="19"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>131</v>
       </c>
@@ -7853,7 +7857,7 @@
       <c r="J170" s="19"/>
       <c r="K170" s="19"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>141</v>
       </c>
@@ -7881,7 +7885,7 @@
       <c r="J171" s="19"/>
       <c r="K171" s="19"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>142</v>
       </c>
@@ -7909,7 +7913,7 @@
       <c r="J172" s="19"/>
       <c r="K172" s="19"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>228</v>
       </c>
@@ -7937,7 +7941,7 @@
       <c r="J173" s="19"/>
       <c r="K173" s="19"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>230</v>
       </c>
@@ -7965,7 +7969,7 @@
       <c r="J174" s="19"/>
       <c r="K174" s="19"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>147</v>
       </c>
@@ -7993,7 +7997,7 @@
       <c r="J175" s="19"/>
       <c r="K175" s="19"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>151</v>
       </c>
@@ -8021,7 +8025,7 @@
       <c r="J176" s="19"/>
       <c r="K176" s="19"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>681</v>
       </c>
@@ -8049,7 +8053,7 @@
       <c r="J177" s="19"/>
       <c r="K177" s="19"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>154</v>
       </c>
@@ -8077,7 +8081,7 @@
       <c r="J178" s="19"/>
       <c r="K178" s="19"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>156</v>
       </c>
@@ -8105,7 +8109,7 @@
       <c r="J179" s="19"/>
       <c r="K179" s="19"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>168</v>
       </c>
@@ -8133,7 +8137,7 @@
       <c r="J180" s="19"/>
       <c r="K180" s="19"/>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>163</v>
       </c>
@@ -8161,7 +8165,7 @@
       <c r="J181" s="19"/>
       <c r="K181" s="19"/>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>374</v>
       </c>
@@ -8189,7 +8193,7 @@
       <c r="J182" s="19"/>
       <c r="K182" s="19"/>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>173</v>
       </c>
@@ -8217,7 +8221,7 @@
       <c r="J183" s="19"/>
       <c r="K183" s="19"/>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>173</v>
       </c>
@@ -8245,7 +8249,7 @@
       <c r="J184" s="19"/>
       <c r="K184" s="19"/>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>175</v>
       </c>
@@ -8273,7 +8277,7 @@
       <c r="J185" s="19"/>
       <c r="K185" s="19"/>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>175</v>
       </c>
@@ -8301,7 +8305,7 @@
       <c r="J186" s="19"/>
       <c r="K186" s="19"/>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>175</v>
       </c>
@@ -8329,7 +8333,7 @@
       <c r="J187" s="19"/>
       <c r="K187" s="19"/>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>179</v>
       </c>
@@ -8357,7 +8361,7 @@
       <c r="J188" s="19"/>
       <c r="K188" s="19"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>696</v>
       </c>
@@ -8383,9 +8387,11 @@
       <c r="H189" s="19"/>
       <c r="I189" s="19"/>
       <c r="J189" s="19"/>
-      <c r="K189" s="19"/>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K189" s="19" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>298</v>
       </c>
@@ -8413,7 +8419,7 @@
       <c r="J190" s="19"/>
       <c r="K190" s="19"/>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>797</v>
       </c>
@@ -8441,7 +8447,7 @@
       <c r="J191" s="19"/>
       <c r="K191" s="19"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>185</v>
       </c>
@@ -8469,7 +8475,7 @@
       <c r="J192" s="19"/>
       <c r="K192" s="19"/>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>185</v>
       </c>
@@ -8497,7 +8503,7 @@
       <c r="J193" s="19"/>
       <c r="K193" s="19"/>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>183</v>
       </c>
@@ -8525,7 +8531,7 @@
       <c r="J194" s="19"/>
       <c r="K194" s="19"/>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>703</v>
       </c>
@@ -8553,7 +8559,7 @@
       <c r="J195" s="19"/>
       <c r="K195" s="19"/>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>705</v>
       </c>
@@ -8581,7 +8587,7 @@
       <c r="J196" s="19"/>
       <c r="K196" s="19"/>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>188</v>
       </c>
@@ -8609,7 +8615,7 @@
       <c r="J197" s="19"/>
       <c r="K197" s="19"/>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>191</v>
       </c>
@@ -8637,7 +8643,7 @@
       <c r="J198" s="19"/>
       <c r="K198" s="19"/>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>711</v>
       </c>
@@ -8665,7 +8671,7 @@
       <c r="J199" s="19"/>
       <c r="K199" s="19"/>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>219</v>
       </c>
@@ -8693,7 +8699,7 @@
       <c r="J200" s="19"/>
       <c r="K200" s="19"/>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>713</v>
       </c>
@@ -8721,7 +8727,7 @@
       <c r="J201" s="19"/>
       <c r="K201" s="19"/>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>716</v>
       </c>
@@ -8751,7 +8757,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>359</v>
       </c>
@@ -8779,7 +8785,7 @@
       <c r="J203" s="19"/>
       <c r="K203" s="19"/>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>204</v>
       </c>
@@ -8807,7 +8813,7 @@
       <c r="J204" s="19"/>
       <c r="K204" s="19"/>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>206</v>
       </c>
@@ -8835,7 +8841,7 @@
       <c r="J205" s="19"/>
       <c r="K205" s="19"/>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>240</v>
       </c>
@@ -8863,7 +8869,7 @@
       <c r="J206" s="19"/>
       <c r="K206" s="19"/>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>212</v>
       </c>
@@ -8891,7 +8897,7 @@
       <c r="J207" s="19"/>
       <c r="K207" s="19"/>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>226</v>
       </c>
@@ -8919,7 +8925,7 @@
       <c r="J208" s="19"/>
       <c r="K208" s="19"/>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>221</v>
       </c>
@@ -8947,7 +8953,7 @@
       <c r="J209" s="19"/>
       <c r="K209" s="19"/>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>221</v>
       </c>
@@ -8975,7 +8981,7 @@
       <c r="J210" s="19"/>
       <c r="K210" s="19"/>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>221</v>
       </c>
@@ -9003,7 +9009,7 @@
       <c r="J211" s="19"/>
       <c r="K211" s="19"/>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>221</v>
       </c>
@@ -9031,7 +9037,7 @@
       <c r="J212" s="19"/>
       <c r="K212" s="19"/>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>221</v>
       </c>
@@ -9059,7 +9065,7 @@
       <c r="J213" s="19"/>
       <c r="K213" s="19"/>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>732</v>
       </c>
@@ -9087,7 +9093,7 @@
       <c r="J214" s="19"/>
       <c r="K214" s="19"/>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>232</v>
       </c>
@@ -9115,7 +9121,7 @@
       <c r="J215" s="19"/>
       <c r="K215" s="19"/>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>242</v>
       </c>
@@ -9143,7 +9149,7 @@
       <c r="J216" s="19"/>
       <c r="K216" s="19"/>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>247</v>
       </c>
@@ -9171,7 +9177,7 @@
       <c r="J217" s="19"/>
       <c r="K217" s="19"/>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>740</v>
       </c>
@@ -9199,7 +9205,7 @@
       <c r="J218" s="19"/>
       <c r="K218" s="19"/>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>251</v>
       </c>
@@ -9227,7 +9233,7 @@
       <c r="J219" s="19"/>
       <c r="K219" s="19"/>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>276</v>
       </c>
@@ -9255,7 +9261,7 @@
       <c r="J220" s="19"/>
       <c r="K220" s="19"/>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>746</v>
       </c>
@@ -9283,7 +9289,7 @@
       <c r="J221" s="19"/>
       <c r="K221" s="19"/>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>257</v>
       </c>
@@ -9311,7 +9317,7 @@
       <c r="J222" s="19"/>
       <c r="K222" s="19"/>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>748</v>
       </c>
@@ -9339,7 +9345,7 @@
       <c r="J223" s="19"/>
       <c r="K223" s="19"/>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>263</v>
       </c>
@@ -9367,7 +9373,7 @@
       <c r="J224" s="19"/>
       <c r="K224" s="19"/>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>260</v>
       </c>
@@ -9395,7 +9401,7 @@
       <c r="J225" s="19"/>
       <c r="K225" s="19"/>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>264</v>
       </c>
@@ -9423,7 +9429,7 @@
       <c r="J226" s="19"/>
       <c r="K226" s="19"/>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>269</v>
       </c>
@@ -9451,7 +9457,7 @@
       <c r="J227" s="19"/>
       <c r="K227" s="19"/>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>270</v>
       </c>
@@ -9479,7 +9485,7 @@
       <c r="J228" s="19"/>
       <c r="K228" s="19"/>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>270</v>
       </c>
@@ -9507,7 +9513,7 @@
       <c r="J229" s="19"/>
       <c r="K229" s="19"/>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>279</v>
       </c>
@@ -9535,7 +9541,7 @@
       <c r="J230" s="19"/>
       <c r="K230" s="19"/>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>278</v>
       </c>
@@ -9563,7 +9569,7 @@
       <c r="J231" s="19"/>
       <c r="K231" s="19"/>
     </row>
-    <row r="232" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>284</v>
       </c>
@@ -9591,7 +9597,7 @@
       <c r="J232" s="20"/>
       <c r="K232" s="20"/>
     </row>
-    <row r="233" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>765</v>
       </c>
@@ -9619,7 +9625,7 @@
       <c r="J233" s="20"/>
       <c r="K233" s="20"/>
     </row>
-    <row r="234" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>288</v>
       </c>
@@ -9647,7 +9653,7 @@
       <c r="J234" s="20"/>
       <c r="K234" s="20"/>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>287</v>
       </c>
@@ -9675,7 +9681,7 @@
       <c r="J235" s="19"/>
       <c r="K235" s="19"/>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>289</v>
       </c>
@@ -9703,7 +9709,7 @@
       <c r="J236" s="19"/>
       <c r="K236" s="19"/>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>290</v>
       </c>
@@ -9731,7 +9737,7 @@
       <c r="J237" s="19"/>
       <c r="K237" s="19"/>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>774</v>
       </c>
@@ -9759,7 +9765,7 @@
       <c r="J238" s="19"/>
       <c r="K238" s="19"/>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>303</v>
       </c>
@@ -9787,7 +9793,7 @@
       <c r="J239" s="19"/>
       <c r="K239" s="19"/>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>304</v>
       </c>
@@ -9815,7 +9821,7 @@
       <c r="J240" s="19"/>
       <c r="K240" s="19"/>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>305</v>
       </c>
@@ -9843,7 +9849,7 @@
       <c r="J241" s="19"/>
       <c r="K241" s="19"/>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>300</v>
       </c>
@@ -9871,7 +9877,7 @@
       <c r="J242" s="19"/>
       <c r="K242" s="19"/>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>348</v>
       </c>
@@ -9899,7 +9905,7 @@
       <c r="J243" s="19"/>
       <c r="K243" s="19"/>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>357</v>
       </c>
@@ -9927,7 +9933,7 @@
       <c r="J244" s="19"/>
       <c r="K244" s="19"/>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>351</v>
       </c>
@@ -9955,7 +9961,7 @@
       <c r="J245" s="19"/>
       <c r="K245" s="19"/>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>361</v>
       </c>
@@ -9983,7 +9989,7 @@
       <c r="J246" s="19"/>
       <c r="K246" s="19"/>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>365</v>
       </c>
@@ -10011,7 +10017,7 @@
       <c r="J247" s="19"/>
       <c r="K247" s="19"/>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>363</v>
       </c>
@@ -10039,7 +10045,7 @@
       <c r="J248" s="19"/>
       <c r="K248" s="19"/>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>355</v>
       </c>
@@ -10067,7 +10073,7 @@
       <c r="J249" s="19"/>
       <c r="K249" s="19"/>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>368</v>
       </c>
@@ -10095,7 +10101,7 @@
       <c r="J250" s="19"/>
       <c r="K250" s="19"/>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>367</v>
       </c>
@@ -10123,7 +10129,7 @@
       <c r="J251" s="19"/>
       <c r="K251" s="19"/>
     </row>
-    <row r="252" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>367</v>
       </c>
@@ -10151,7 +10157,7 @@
       <c r="J252" s="19"/>
       <c r="K252" s="19"/>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>371</v>
       </c>
@@ -10179,7 +10185,7 @@
       <c r="J253" s="19"/>
       <c r="K253" s="19"/>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>816</v>
       </c>
@@ -10217,12 +10223,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10340,15 +10343,25 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDD49F8-6691-4324-BC0D-0B1E4890A2C6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEFD23-736F-4CE9-81DA-D9D145B9B572}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10370,16 +10383,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEFD23-736F-4CE9-81DA-D9D145B9B572}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDD49F8-6691-4324-BC0D-0B1E4890A2C6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/procesos/inputs/Excel CCC Empresas.xlsx
+++ b/procesos/inputs/Excel CCC Empresas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\preprod\Documents\Proyectos\parche-gestoria\procesos\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonza\OneDrive\Nodus\Proyectos\Nodus-app\parche-gestoria\procesos\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E9639C-05C2-4436-B1E1-829E28E4BA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8DA043-1D93-4251-915B-6B03C80601E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14595" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE DE DATOS (NO TOCAR)" sheetId="14" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="826">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -3033,20 +3033,20 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:K254"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="12" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="58.7109375" style="6" customWidth="1"/>
-    <col min="8" max="11" width="10.85546875" style="21"/>
-    <col min="12" max="16384" width="10.85546875" style="6"/>
+    <col min="1" max="1" width="10.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.1796875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="14.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="58.7265625" style="6" customWidth="1"/>
+    <col min="8" max="11" width="10.81640625" style="21"/>
+    <col min="12" max="16384" width="10.81640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>815</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>40</v>
       </c>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="K2" s="19"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K3" s="19"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="K4" s="19"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>40</v>
       </c>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="K5" s="22"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="K6" s="19"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -3279,7 +3279,7 @@
       <c r="J7" s="19"/>
       <c r="K7" s="19"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>215</v>
       </c>
@@ -3309,9 +3309,11 @@
       <c r="J8" s="19" t="s">
         <v>825</v>
       </c>
-      <c r="K8" s="19"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K8" s="19" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
@@ -3339,7 +3341,7 @@
       <c r="J9" s="19"/>
       <c r="K9" s="19"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
@@ -3367,7 +3369,7 @@
       <c r="J10" s="19"/>
       <c r="K10" s="22"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>45</v>
       </c>
@@ -3397,7 +3399,7 @@
       <c r="J11" s="19"/>
       <c r="K11" s="19"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>47</v>
       </c>
@@ -3425,7 +3427,7 @@
       <c r="J12" s="19"/>
       <c r="K12" s="19"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
@@ -3453,7 +3455,7 @@
       <c r="J13" s="19"/>
       <c r="K13" s="19"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>49</v>
       </c>
@@ -3481,7 +3483,7 @@
       <c r="J14" s="19"/>
       <c r="K14" s="19"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>50</v>
       </c>
@@ -3509,7 +3511,7 @@
       <c r="J15" s="19"/>
       <c r="K15" s="19"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -3537,7 +3539,7 @@
       <c r="J16" s="19"/>
       <c r="K16" s="19"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>223</v>
       </c>
@@ -3565,7 +3567,7 @@
       <c r="J17" s="19"/>
       <c r="K17" s="19"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>223</v>
       </c>
@@ -3593,7 +3595,7 @@
       <c r="J18" s="19"/>
       <c r="K18" s="19"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>223</v>
       </c>
@@ -3621,7 +3623,7 @@
       <c r="J19" s="19"/>
       <c r="K19" s="19"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>51</v>
       </c>
@@ -3649,7 +3651,7 @@
       <c r="J20" s="19"/>
       <c r="K20" s="19"/>
     </row>
-    <row r="21" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>112</v>
       </c>
@@ -3677,7 +3679,7 @@
       <c r="J21" s="19"/>
       <c r="K21" s="19"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>52</v>
       </c>
@@ -3705,7 +3707,7 @@
       <c r="J22" s="19"/>
       <c r="K22" s="19"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>52</v>
       </c>
@@ -3733,7 +3735,7 @@
       <c r="J23" s="19"/>
       <c r="K23" s="19"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>236</v>
       </c>
@@ -3761,7 +3763,7 @@
       <c r="J24" s="19"/>
       <c r="K24" s="19"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>54</v>
       </c>
@@ -3789,7 +3791,7 @@
       <c r="J25" s="19"/>
       <c r="K25" s="19"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>55</v>
       </c>
@@ -3817,7 +3819,7 @@
       <c r="J26" s="19"/>
       <c r="K26" s="19"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>57</v>
       </c>
@@ -3845,7 +3847,7 @@
       <c r="J27" s="19"/>
       <c r="K27" s="19"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>59</v>
       </c>
@@ -3873,7 +3875,7 @@
       <c r="J28" s="19"/>
       <c r="K28" s="19"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>61</v>
       </c>
@@ -3901,7 +3903,7 @@
       <c r="J29" s="19"/>
       <c r="K29" s="19"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>61</v>
       </c>
@@ -3929,7 +3931,7 @@
       <c r="J30" s="19"/>
       <c r="K30" s="19"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>62</v>
       </c>
@@ -3957,7 +3959,7 @@
       <c r="J31" s="19"/>
       <c r="K31" s="19"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>63</v>
       </c>
@@ -3985,7 +3987,7 @@
       <c r="J32" s="19"/>
       <c r="K32" s="19"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>208</v>
       </c>
@@ -4013,7 +4015,7 @@
       <c r="J33" s="19"/>
       <c r="K33" s="19"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>65</v>
       </c>
@@ -4041,7 +4043,7 @@
       <c r="J34" s="19"/>
       <c r="K34" s="19"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>238</v>
       </c>
@@ -4069,7 +4071,7 @@
       <c r="J35" s="19"/>
       <c r="K35" s="19"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>113</v>
       </c>
@@ -4097,7 +4099,7 @@
       <c r="J36" s="19"/>
       <c r="K36" s="19"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>113</v>
       </c>
@@ -4125,7 +4127,7 @@
       <c r="J37" s="19"/>
       <c r="K37" s="19"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>67</v>
       </c>
@@ -4153,7 +4155,7 @@
       <c r="J38" s="19"/>
       <c r="K38" s="19"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>69</v>
       </c>
@@ -4181,7 +4183,7 @@
       <c r="J39" s="19"/>
       <c r="K39" s="19"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>71</v>
       </c>
@@ -4209,7 +4211,7 @@
       <c r="J40" s="19"/>
       <c r="K40" s="19"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>72</v>
       </c>
@@ -4237,7 +4239,7 @@
       <c r="J41" s="19"/>
       <c r="K41" s="19"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>431</v>
       </c>
@@ -4265,7 +4267,7 @@
       <c r="J42" s="19"/>
       <c r="K42" s="19"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>434</v>
       </c>
@@ -4293,7 +4295,7 @@
       <c r="J43" s="19"/>
       <c r="K43" s="19"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>436</v>
       </c>
@@ -4321,7 +4323,7 @@
       <c r="J44" s="19"/>
       <c r="K44" s="19"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>439</v>
       </c>
@@ -4349,7 +4351,7 @@
       <c r="J45" s="19"/>
       <c r="K45" s="19"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>442</v>
       </c>
@@ -4377,7 +4379,7 @@
       <c r="J46" s="19"/>
       <c r="K46" s="19"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>164</v>
       </c>
@@ -4405,7 +4407,7 @@
       <c r="J47" s="19"/>
       <c r="K47" s="19"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>214</v>
       </c>
@@ -4433,7 +4435,7 @@
       <c r="J48" s="19"/>
       <c r="K48" s="19"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>449</v>
       </c>
@@ -4461,7 +4463,7 @@
       <c r="J49" s="19"/>
       <c r="K49" s="19"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>262</v>
       </c>
@@ -4489,7 +4491,7 @@
       <c r="J50" s="19"/>
       <c r="K50" s="19"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>262</v>
       </c>
@@ -4517,7 +4519,7 @@
       <c r="J51" s="19"/>
       <c r="K51" s="19"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>451</v>
       </c>
@@ -4545,7 +4547,7 @@
       <c r="J52" s="19"/>
       <c r="K52" s="19"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>217</v>
       </c>
@@ -4573,7 +4575,7 @@
       <c r="J53" s="19"/>
       <c r="K53" s="19"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>217</v>
       </c>
@@ -4601,7 +4603,7 @@
       <c r="J54" s="19"/>
       <c r="K54" s="19"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>217</v>
       </c>
@@ -4629,7 +4631,7 @@
       <c r="J55" s="19"/>
       <c r="K55" s="19"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>217</v>
       </c>
@@ -4657,7 +4659,7 @@
       <c r="J56" s="19"/>
       <c r="K56" s="19"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>217</v>
       </c>
@@ -4685,7 +4687,7 @@
       <c r="J57" s="19"/>
       <c r="K57" s="19"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>217</v>
       </c>
@@ -4713,7 +4715,7 @@
       <c r="J58" s="19"/>
       <c r="K58" s="19"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>458</v>
       </c>
@@ -4741,7 +4743,7 @@
       <c r="J59" s="19"/>
       <c r="K59" s="19"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>461</v>
       </c>
@@ -4769,7 +4771,7 @@
       <c r="J60" s="19"/>
       <c r="K60" s="19"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>464</v>
       </c>
@@ -4797,7 +4799,7 @@
       <c r="J61" s="19"/>
       <c r="K61" s="19"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>467</v>
       </c>
@@ -4825,7 +4827,7 @@
       <c r="J62" s="19"/>
       <c r="K62" s="19"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>198</v>
       </c>
@@ -4853,7 +4855,7 @@
       <c r="J63" s="19"/>
       <c r="K63" s="19"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>198</v>
       </c>
@@ -4881,7 +4883,7 @@
       <c r="J64" s="19"/>
       <c r="K64" s="19"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>472</v>
       </c>
@@ -4909,7 +4911,7 @@
       <c r="J65" s="19"/>
       <c r="K65" s="19"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>474</v>
       </c>
@@ -4937,7 +4939,7 @@
       <c r="J66" s="19"/>
       <c r="K66" s="19"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>196</v>
       </c>
@@ -4965,7 +4967,7 @@
       <c r="J67" s="19"/>
       <c r="K67" s="19"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>478</v>
       </c>
@@ -4993,7 +4995,7 @@
       <c r="J68" s="19"/>
       <c r="K68" s="19"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>480</v>
       </c>
@@ -5021,7 +5023,7 @@
       <c r="J69" s="19"/>
       <c r="K69" s="19"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>480</v>
       </c>
@@ -5049,7 +5051,7 @@
       <c r="J70" s="19"/>
       <c r="K70" s="19"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>115</v>
       </c>
@@ -5077,7 +5079,7 @@
       <c r="J71" s="19"/>
       <c r="K71" s="19"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>485</v>
       </c>
@@ -5105,7 +5107,7 @@
       <c r="J72" s="19"/>
       <c r="K72" s="19"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>488</v>
       </c>
@@ -5133,7 +5135,7 @@
       <c r="J73" s="19"/>
       <c r="K73" s="19"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>491</v>
       </c>
@@ -5161,7 +5163,7 @@
       <c r="J74" s="19"/>
       <c r="K74" s="19"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>494</v>
       </c>
@@ -5189,7 +5191,7 @@
       <c r="J75" s="19"/>
       <c r="K75" s="19"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>494</v>
       </c>
@@ -5217,7 +5219,7 @@
       <c r="J76" s="19"/>
       <c r="K76" s="19"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>170</v>
       </c>
@@ -5245,7 +5247,7 @@
       <c r="J77" s="19"/>
       <c r="K77" s="19"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>130</v>
       </c>
@@ -5273,7 +5275,7 @@
       <c r="J78" s="19"/>
       <c r="K78" s="19"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>161</v>
       </c>
@@ -5301,7 +5303,7 @@
       <c r="J79" s="19"/>
       <c r="K79" s="19"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>137</v>
       </c>
@@ -5329,7 +5331,7 @@
       <c r="J80" s="19"/>
       <c r="K80" s="19"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>503</v>
       </c>
@@ -5357,7 +5359,7 @@
       <c r="J81" s="19"/>
       <c r="K81" s="19"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>506</v>
       </c>
@@ -5385,7 +5387,7 @@
       <c r="J82" s="19"/>
       <c r="K82" s="19"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>509</v>
       </c>
@@ -5413,7 +5415,7 @@
       <c r="J83" s="19"/>
       <c r="K83" s="19"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>512</v>
       </c>
@@ -5441,7 +5443,7 @@
       <c r="J84" s="19"/>
       <c r="K84" s="19"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>116</v>
       </c>
@@ -5469,7 +5471,7 @@
       <c r="J85" s="19"/>
       <c r="K85" s="19"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>516</v>
       </c>
@@ -5497,7 +5499,7 @@
       <c r="J86" s="19"/>
       <c r="K86" s="19"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>519</v>
       </c>
@@ -5525,7 +5527,7 @@
       <c r="J87" s="19"/>
       <c r="K87" s="19"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>519</v>
       </c>
@@ -5553,7 +5555,7 @@
       <c r="J88" s="19"/>
       <c r="K88" s="19"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>519</v>
       </c>
@@ -5581,7 +5583,7 @@
       <c r="J89" s="19"/>
       <c r="K89" s="19"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>522</v>
       </c>
@@ -5609,7 +5611,7 @@
       <c r="J90" s="19"/>
       <c r="K90" s="19"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>525</v>
       </c>
@@ -5637,7 +5639,7 @@
       <c r="J91" s="19"/>
       <c r="K91" s="19"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>117</v>
       </c>
@@ -5665,7 +5667,7 @@
       <c r="J92" s="19"/>
       <c r="K92" s="19"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>529</v>
       </c>
@@ -5693,7 +5695,7 @@
       <c r="J93" s="19"/>
       <c r="K93" s="19"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>529</v>
       </c>
@@ -5721,7 +5723,7 @@
       <c r="J94" s="19"/>
       <c r="K94" s="19"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>529</v>
       </c>
@@ -5749,7 +5751,7 @@
       <c r="J95" s="19"/>
       <c r="K95" s="19"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>531</v>
       </c>
@@ -5777,7 +5779,7 @@
       <c r="J96" s="19"/>
       <c r="K96" s="19"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>536</v>
       </c>
@@ -5805,7 +5807,7 @@
       <c r="J97" s="19"/>
       <c r="K97" s="19"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>536</v>
       </c>
@@ -5833,7 +5835,7 @@
       <c r="J98" s="19"/>
       <c r="K98" s="19"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>534</v>
       </c>
@@ -5861,7 +5863,7 @@
       <c r="J99" s="19"/>
       <c r="K99" s="19"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>267</v>
       </c>
@@ -5889,7 +5891,7 @@
       <c r="J100" s="19"/>
       <c r="K100" s="19"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>267</v>
       </c>
@@ -5917,7 +5919,7 @@
       <c r="J101" s="19"/>
       <c r="K101" s="19"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>540</v>
       </c>
@@ -5945,7 +5947,7 @@
       <c r="J102" s="19"/>
       <c r="K102" s="19"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>540</v>
       </c>
@@ -5973,7 +5975,7 @@
       <c r="J103" s="19"/>
       <c r="K103" s="19"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>540</v>
       </c>
@@ -6001,7 +6003,7 @@
       <c r="J104" s="19"/>
       <c r="K104" s="19"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>543</v>
       </c>
@@ -6029,7 +6031,7 @@
       <c r="J105" s="19"/>
       <c r="K105" s="19"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>543</v>
       </c>
@@ -6057,7 +6059,7 @@
       <c r="J106" s="19"/>
       <c r="K106" s="19"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>545</v>
       </c>
@@ -6085,7 +6087,7 @@
       <c r="J107" s="19"/>
       <c r="K107" s="19"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>548</v>
       </c>
@@ -6113,7 +6115,7 @@
       <c r="J108" s="19"/>
       <c r="K108" s="19"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>805</v>
       </c>
@@ -6141,7 +6143,7 @@
       <c r="J109" s="19"/>
       <c r="K109" s="19"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>167</v>
       </c>
@@ -6169,7 +6171,7 @@
       <c r="J110" s="19"/>
       <c r="K110" s="19"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>554</v>
       </c>
@@ -6197,7 +6199,7 @@
       <c r="J111" s="19"/>
       <c r="K111" s="19"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>295</v>
       </c>
@@ -6225,7 +6227,7 @@
       <c r="J112" s="19"/>
       <c r="K112" s="19"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>558</v>
       </c>
@@ -6253,7 +6255,7 @@
       <c r="J113" s="19"/>
       <c r="K113" s="19"/>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>560</v>
       </c>
@@ -6281,7 +6283,7 @@
       <c r="J114" s="19"/>
       <c r="K114" s="19"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>110</v>
       </c>
@@ -6309,7 +6311,7 @@
       <c r="J115" s="19"/>
       <c r="K115" s="19"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>353</v>
       </c>
@@ -6337,7 +6339,7 @@
       <c r="J116" s="19"/>
       <c r="K116" s="19"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>564</v>
       </c>
@@ -6365,7 +6367,7 @@
       <c r="J117" s="19"/>
       <c r="K117" s="19"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>564</v>
       </c>
@@ -6393,7 +6395,7 @@
       <c r="J118" s="19"/>
       <c r="K118" s="19"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>350</v>
       </c>
@@ -6421,7 +6423,7 @@
       <c r="J119" s="19"/>
       <c r="K119" s="19"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>568</v>
       </c>
@@ -6449,7 +6451,7 @@
       <c r="J120" s="19"/>
       <c r="K120" s="19"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>568</v>
       </c>
@@ -6477,7 +6479,7 @@
       <c r="J121" s="19"/>
       <c r="K121" s="19"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>800</v>
       </c>
@@ -6505,7 +6507,7 @@
       <c r="J122" s="19"/>
       <c r="K122" s="19"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>121</v>
       </c>
@@ -6533,7 +6535,7 @@
       <c r="J123" s="19"/>
       <c r="K123" s="19"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>572</v>
       </c>
@@ -6561,7 +6563,7 @@
       <c r="J124" s="19"/>
       <c r="K124" s="19"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>572</v>
       </c>
@@ -6589,7 +6591,7 @@
       <c r="J125" s="19"/>
       <c r="K125" s="19"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>575</v>
       </c>
@@ -6619,7 +6621,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>135</v>
       </c>
@@ -6647,7 +6649,7 @@
       <c r="J127" s="19"/>
       <c r="K127" s="19"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>231</v>
       </c>
@@ -6675,7 +6677,7 @@
       <c r="J128" s="19"/>
       <c r="K128" s="19"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>581</v>
       </c>
@@ -6703,7 +6705,7 @@
       <c r="J129" s="19"/>
       <c r="K129" s="19"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>581</v>
       </c>
@@ -6731,7 +6733,7 @@
       <c r="J130" s="19"/>
       <c r="K130" s="19"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>584</v>
       </c>
@@ -6759,7 +6761,7 @@
       <c r="J131" s="19"/>
       <c r="K131" s="19"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>587</v>
       </c>
@@ -6787,7 +6789,7 @@
       <c r="J132" s="19"/>
       <c r="K132" s="19"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>590</v>
       </c>
@@ -6815,7 +6817,7 @@
       <c r="J133" s="19"/>
       <c r="K133" s="19"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>593</v>
       </c>
@@ -6843,7 +6845,7 @@
       <c r="J134" s="19"/>
       <c r="K134" s="19"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>145</v>
       </c>
@@ -6871,7 +6873,7 @@
       <c r="J135" s="19"/>
       <c r="K135" s="19"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>596</v>
       </c>
@@ -6899,7 +6901,7 @@
       <c r="J136" s="19"/>
       <c r="K136" s="19"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>598</v>
       </c>
@@ -6927,7 +6929,7 @@
       <c r="J137" s="19"/>
       <c r="K137" s="19"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>601</v>
       </c>
@@ -6955,7 +6957,7 @@
       <c r="J138" s="19"/>
       <c r="K138" s="19"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>604</v>
       </c>
@@ -6983,7 +6985,7 @@
       <c r="J139" s="19"/>
       <c r="K139" s="19"/>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>607</v>
       </c>
@@ -7011,7 +7013,7 @@
       <c r="J140" s="19"/>
       <c r="K140" s="19"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>610</v>
       </c>
@@ -7039,7 +7041,7 @@
       <c r="J141" s="19"/>
       <c r="K141" s="19"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>613</v>
       </c>
@@ -7067,7 +7069,7 @@
       <c r="J142" s="19"/>
       <c r="K142" s="19"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>616</v>
       </c>
@@ -7095,7 +7097,7 @@
       <c r="J143" s="19"/>
       <c r="K143" s="19"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>619</v>
       </c>
@@ -7123,7 +7125,7 @@
       <c r="J144" s="19"/>
       <c r="K144" s="19"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>622</v>
       </c>
@@ -7151,7 +7153,7 @@
       <c r="J145" s="19"/>
       <c r="K145" s="19"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>622</v>
       </c>
@@ -7179,7 +7181,7 @@
       <c r="J146" s="19"/>
       <c r="K146" s="19"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>624</v>
       </c>
@@ -7207,7 +7209,7 @@
       <c r="J147" s="19"/>
       <c r="K147" s="19"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>627</v>
       </c>
@@ -7235,7 +7237,7 @@
       <c r="J148" s="19"/>
       <c r="K148" s="19"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>630</v>
       </c>
@@ -7263,7 +7265,7 @@
       <c r="J149" s="19"/>
       <c r="K149" s="19"/>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>633</v>
       </c>
@@ -7291,7 +7293,7 @@
       <c r="J150" s="19"/>
       <c r="K150" s="19"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>636</v>
       </c>
@@ -7319,7 +7321,7 @@
       <c r="J151" s="19"/>
       <c r="K151" s="19"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>639</v>
       </c>
@@ -7351,7 +7353,7 @@
       <c r="J152" s="19"/>
       <c r="K152" s="19"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>202</v>
       </c>
@@ -7379,7 +7381,7 @@
       <c r="J153" s="19"/>
       <c r="K153" s="19"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>122</v>
       </c>
@@ -7407,7 +7409,7 @@
       <c r="J154" s="19"/>
       <c r="K154" s="19"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>122</v>
       </c>
@@ -7435,7 +7437,7 @@
       <c r="J155" s="19"/>
       <c r="K155" s="19"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>103</v>
       </c>
@@ -7463,7 +7465,7 @@
       <c r="J156" s="19"/>
       <c r="K156" s="19"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>105</v>
       </c>
@@ -7491,7 +7493,7 @@
       <c r="J157" s="19"/>
       <c r="K157" s="19"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>107</v>
       </c>
@@ -7519,7 +7521,7 @@
       <c r="J158" s="19"/>
       <c r="K158" s="19"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>111</v>
       </c>
@@ -7547,7 +7549,7 @@
       <c r="J159" s="19"/>
       <c r="K159" s="19"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>651</v>
       </c>
@@ -7575,7 +7577,7 @@
       <c r="J160" s="19"/>
       <c r="K160" s="19"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>654</v>
       </c>
@@ -7603,7 +7605,7 @@
       <c r="J161" s="19"/>
       <c r="K161" s="19"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>148</v>
       </c>
@@ -7631,7 +7633,7 @@
       <c r="J162" s="19"/>
       <c r="K162" s="19"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>134</v>
       </c>
@@ -7657,11 +7659,9 @@
       <c r="H163" s="19"/>
       <c r="I163" s="19"/>
       <c r="J163" s="19"/>
-      <c r="K163" s="19" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K163" s="19"/>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>282</v>
       </c>
@@ -7689,7 +7689,7 @@
       <c r="J164" s="19"/>
       <c r="K164" s="19"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>127</v>
       </c>
@@ -7717,7 +7717,7 @@
       <c r="J165" s="19"/>
       <c r="K165" s="19"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>127</v>
       </c>
@@ -7745,7 +7745,7 @@
       <c r="J166" s="19"/>
       <c r="K166" s="19"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>158</v>
       </c>
@@ -7773,7 +7773,7 @@
       <c r="J167" s="19"/>
       <c r="K167" s="19"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>177</v>
       </c>
@@ -7801,7 +7801,7 @@
       <c r="J168" s="19"/>
       <c r="K168" s="19"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>132</v>
       </c>
@@ -7829,7 +7829,7 @@
       <c r="J169" s="19"/>
       <c r="K169" s="19"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>131</v>
       </c>
@@ -7857,7 +7857,7 @@
       <c r="J170" s="19"/>
       <c r="K170" s="19"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>141</v>
       </c>
@@ -7885,7 +7885,7 @@
       <c r="J171" s="19"/>
       <c r="K171" s="19"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>142</v>
       </c>
@@ -7913,7 +7913,7 @@
       <c r="J172" s="19"/>
       <c r="K172" s="19"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>228</v>
       </c>
@@ -7941,7 +7941,7 @@
       <c r="J173" s="19"/>
       <c r="K173" s="19"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>230</v>
       </c>
@@ -7969,7 +7969,7 @@
       <c r="J174" s="19"/>
       <c r="K174" s="19"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>147</v>
       </c>
@@ -7997,7 +7997,7 @@
       <c r="J175" s="19"/>
       <c r="K175" s="19"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>151</v>
       </c>
@@ -8025,7 +8025,7 @@
       <c r="J176" s="19"/>
       <c r="K176" s="19"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>681</v>
       </c>
@@ -8053,7 +8053,7 @@
       <c r="J177" s="19"/>
       <c r="K177" s="19"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>154</v>
       </c>
@@ -8081,7 +8081,7 @@
       <c r="J178" s="19"/>
       <c r="K178" s="19"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>156</v>
       </c>
@@ -8109,7 +8109,7 @@
       <c r="J179" s="19"/>
       <c r="K179" s="19"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>168</v>
       </c>
@@ -8137,7 +8137,7 @@
       <c r="J180" s="19"/>
       <c r="K180" s="19"/>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>163</v>
       </c>
@@ -8165,7 +8165,7 @@
       <c r="J181" s="19"/>
       <c r="K181" s="19"/>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>374</v>
       </c>
@@ -8193,7 +8193,7 @@
       <c r="J182" s="19"/>
       <c r="K182" s="19"/>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>173</v>
       </c>
@@ -8221,7 +8221,7 @@
       <c r="J183" s="19"/>
       <c r="K183" s="19"/>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>173</v>
       </c>
@@ -8249,7 +8249,7 @@
       <c r="J184" s="19"/>
       <c r="K184" s="19"/>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>175</v>
       </c>
@@ -8277,7 +8277,7 @@
       <c r="J185" s="19"/>
       <c r="K185" s="19"/>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>175</v>
       </c>
@@ -8305,7 +8305,7 @@
       <c r="J186" s="19"/>
       <c r="K186" s="19"/>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>175</v>
       </c>
@@ -8333,7 +8333,7 @@
       <c r="J187" s="19"/>
       <c r="K187" s="19"/>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>179</v>
       </c>
@@ -8361,7 +8361,7 @@
       <c r="J188" s="19"/>
       <c r="K188" s="19"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>696</v>
       </c>
@@ -8387,11 +8387,9 @@
       <c r="H189" s="19"/>
       <c r="I189" s="19"/>
       <c r="J189" s="19"/>
-      <c r="K189" s="19" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K189" s="19"/>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>298</v>
       </c>
@@ -8419,7 +8417,7 @@
       <c r="J190" s="19"/>
       <c r="K190" s="19"/>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>797</v>
       </c>
@@ -8447,7 +8445,7 @@
       <c r="J191" s="19"/>
       <c r="K191" s="19"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>185</v>
       </c>
@@ -8475,7 +8473,7 @@
       <c r="J192" s="19"/>
       <c r="K192" s="19"/>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>185</v>
       </c>
@@ -8503,7 +8501,7 @@
       <c r="J193" s="19"/>
       <c r="K193" s="19"/>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>183</v>
       </c>
@@ -8531,7 +8529,7 @@
       <c r="J194" s="19"/>
       <c r="K194" s="19"/>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>703</v>
       </c>
@@ -8559,7 +8557,7 @@
       <c r="J195" s="19"/>
       <c r="K195" s="19"/>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>705</v>
       </c>
@@ -8587,7 +8585,7 @@
       <c r="J196" s="19"/>
       <c r="K196" s="19"/>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>188</v>
       </c>
@@ -8615,7 +8613,7 @@
       <c r="J197" s="19"/>
       <c r="K197" s="19"/>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>191</v>
       </c>
@@ -8643,7 +8641,7 @@
       <c r="J198" s="19"/>
       <c r="K198" s="19"/>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>711</v>
       </c>
@@ -8671,7 +8669,7 @@
       <c r="J199" s="19"/>
       <c r="K199" s="19"/>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>219</v>
       </c>
@@ -8699,7 +8697,7 @@
       <c r="J200" s="19"/>
       <c r="K200" s="19"/>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>713</v>
       </c>
@@ -8727,7 +8725,7 @@
       <c r="J201" s="19"/>
       <c r="K201" s="19"/>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>716</v>
       </c>
@@ -8757,7 +8755,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>359</v>
       </c>
@@ -8785,7 +8783,7 @@
       <c r="J203" s="19"/>
       <c r="K203" s="19"/>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>204</v>
       </c>
@@ -8813,7 +8811,7 @@
       <c r="J204" s="19"/>
       <c r="K204" s="19"/>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>206</v>
       </c>
@@ -8841,7 +8839,7 @@
       <c r="J205" s="19"/>
       <c r="K205" s="19"/>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>240</v>
       </c>
@@ -8869,7 +8867,7 @@
       <c r="J206" s="19"/>
       <c r="K206" s="19"/>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>212</v>
       </c>
@@ -8897,7 +8895,7 @@
       <c r="J207" s="19"/>
       <c r="K207" s="19"/>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>226</v>
       </c>
@@ -8925,7 +8923,7 @@
       <c r="J208" s="19"/>
       <c r="K208" s="19"/>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>221</v>
       </c>
@@ -8953,7 +8951,7 @@
       <c r="J209" s="19"/>
       <c r="K209" s="19"/>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>221</v>
       </c>
@@ -8981,7 +8979,7 @@
       <c r="J210" s="19"/>
       <c r="K210" s="19"/>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>221</v>
       </c>
@@ -9009,7 +9007,7 @@
       <c r="J211" s="19"/>
       <c r="K211" s="19"/>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>221</v>
       </c>
@@ -9037,7 +9035,7 @@
       <c r="J212" s="19"/>
       <c r="K212" s="19"/>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>221</v>
       </c>
@@ -9065,7 +9063,7 @@
       <c r="J213" s="19"/>
       <c r="K213" s="19"/>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>732</v>
       </c>
@@ -9093,7 +9091,7 @@
       <c r="J214" s="19"/>
       <c r="K214" s="19"/>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>232</v>
       </c>
@@ -9121,7 +9119,7 @@
       <c r="J215" s="19"/>
       <c r="K215" s="19"/>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>242</v>
       </c>
@@ -9149,7 +9147,7 @@
       <c r="J216" s="19"/>
       <c r="K216" s="19"/>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>247</v>
       </c>
@@ -9177,7 +9175,7 @@
       <c r="J217" s="19"/>
       <c r="K217" s="19"/>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>740</v>
       </c>
@@ -9205,7 +9203,7 @@
       <c r="J218" s="19"/>
       <c r="K218" s="19"/>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>251</v>
       </c>
@@ -9233,7 +9231,7 @@
       <c r="J219" s="19"/>
       <c r="K219" s="19"/>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>276</v>
       </c>
@@ -9261,7 +9259,7 @@
       <c r="J220" s="19"/>
       <c r="K220" s="19"/>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>746</v>
       </c>
@@ -9289,7 +9287,7 @@
       <c r="J221" s="19"/>
       <c r="K221" s="19"/>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>257</v>
       </c>
@@ -9317,7 +9315,7 @@
       <c r="J222" s="19"/>
       <c r="K222" s="19"/>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>748</v>
       </c>
@@ -9345,7 +9343,7 @@
       <c r="J223" s="19"/>
       <c r="K223" s="19"/>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>263</v>
       </c>
@@ -9373,7 +9371,7 @@
       <c r="J224" s="19"/>
       <c r="K224" s="19"/>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>260</v>
       </c>
@@ -9401,7 +9399,7 @@
       <c r="J225" s="19"/>
       <c r="K225" s="19"/>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>264</v>
       </c>
@@ -9429,7 +9427,7 @@
       <c r="J226" s="19"/>
       <c r="K226" s="19"/>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>269</v>
       </c>
@@ -9457,7 +9455,7 @@
       <c r="J227" s="19"/>
       <c r="K227" s="19"/>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>270</v>
       </c>
@@ -9485,7 +9483,7 @@
       <c r="J228" s="19"/>
       <c r="K228" s="19"/>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>270</v>
       </c>
@@ -9513,7 +9511,7 @@
       <c r="J229" s="19"/>
       <c r="K229" s="19"/>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>279</v>
       </c>
@@ -9541,7 +9539,7 @@
       <c r="J230" s="19"/>
       <c r="K230" s="19"/>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>278</v>
       </c>
@@ -9569,7 +9567,7 @@
       <c r="J231" s="19"/>
       <c r="K231" s="19"/>
     </row>
-    <row r="232" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>284</v>
       </c>
@@ -9597,7 +9595,7 @@
       <c r="J232" s="20"/>
       <c r="K232" s="20"/>
     </row>
-    <row r="233" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>765</v>
       </c>
@@ -9625,7 +9623,7 @@
       <c r="J233" s="20"/>
       <c r="K233" s="20"/>
     </row>
-    <row r="234" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>288</v>
       </c>
@@ -9653,7 +9651,7 @@
       <c r="J234" s="20"/>
       <c r="K234" s="20"/>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>287</v>
       </c>
@@ -9681,7 +9679,7 @@
       <c r="J235" s="19"/>
       <c r="K235" s="19"/>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>289</v>
       </c>
@@ -9709,7 +9707,7 @@
       <c r="J236" s="19"/>
       <c r="K236" s="19"/>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>290</v>
       </c>
@@ -9737,7 +9735,7 @@
       <c r="J237" s="19"/>
       <c r="K237" s="19"/>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>774</v>
       </c>
@@ -9765,7 +9763,7 @@
       <c r="J238" s="19"/>
       <c r="K238" s="19"/>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>303</v>
       </c>
@@ -9793,7 +9791,7 @@
       <c r="J239" s="19"/>
       <c r="K239" s="19"/>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>304</v>
       </c>
@@ -9821,7 +9819,7 @@
       <c r="J240" s="19"/>
       <c r="K240" s="19"/>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>305</v>
       </c>
@@ -9849,7 +9847,7 @@
       <c r="J241" s="19"/>
       <c r="K241" s="19"/>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>300</v>
       </c>
@@ -9877,7 +9875,7 @@
       <c r="J242" s="19"/>
       <c r="K242" s="19"/>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>348</v>
       </c>
@@ -9905,7 +9903,7 @@
       <c r="J243" s="19"/>
       <c r="K243" s="19"/>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>357</v>
       </c>
@@ -9933,7 +9931,7 @@
       <c r="J244" s="19"/>
       <c r="K244" s="19"/>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>351</v>
       </c>
@@ -9961,7 +9959,7 @@
       <c r="J245" s="19"/>
       <c r="K245" s="19"/>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>361</v>
       </c>
@@ -9989,7 +9987,7 @@
       <c r="J246" s="19"/>
       <c r="K246" s="19"/>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>365</v>
       </c>
@@ -10017,7 +10015,7 @@
       <c r="J247" s="19"/>
       <c r="K247" s="19"/>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>363</v>
       </c>
@@ -10045,7 +10043,7 @@
       <c r="J248" s="19"/>
       <c r="K248" s="19"/>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>355</v>
       </c>
@@ -10073,7 +10071,7 @@
       <c r="J249" s="19"/>
       <c r="K249" s="19"/>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>368</v>
       </c>
@@ -10101,7 +10099,7 @@
       <c r="J250" s="19"/>
       <c r="K250" s="19"/>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>367</v>
       </c>
@@ -10129,7 +10127,7 @@
       <c r="J251" s="19"/>
       <c r="K251" s="19"/>
     </row>
-    <row r="252" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>367</v>
       </c>
@@ -10157,7 +10155,7 @@
       <c r="J252" s="19"/>
       <c r="K252" s="19"/>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>371</v>
       </c>
@@ -10185,7 +10183,7 @@
       <c r="J253" s="19"/>
       <c r="K253" s="19"/>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>816</v>
       </c>
@@ -10223,12 +10221,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100AF0C36E9CBDE43468AAB846756A8BA94" ma:contentTypeVersion="0" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="93c275e25462616b2c1de9b58ec156dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f6edc329ff236629c56e3b879b320d0">
     <xsd:element name="properties">
@@ -10342,16 +10349,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDD49F8-6691-4324-BC0D-0B1E4890A2C6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEFD23-736F-4CE9-81DA-D9D145B9B572}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -10366,7 +10372,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A01C7383-C303-4DC2-9970-99C89A193825}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10380,12 +10386,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDD49F8-6691-4324-BC0D-0B1E4890A2C6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/procesos/inputs/Excel CCC Empresas.xlsx
+++ b/procesos/inputs/Excel CCC Empresas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonza\OneDrive\Nodus\Proyectos\Nodus-app\parche-gestoria\procesos\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43299255-1594-49F4-914F-007F71A18D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8DA043-1D93-4251-915B-6B03C80601E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-14595" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="826">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -3309,7 +3309,9 @@
       <c r="J8" s="19" t="s">
         <v>825</v>
       </c>
-      <c r="K8" s="19"/>
+      <c r="K8" s="19" t="s">
+        <v>825</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
@@ -3423,9 +3425,7 @@
       <c r="H12" s="19"/>
       <c r="I12" s="19"/>
       <c r="J12" s="19"/>
-      <c r="K12" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="K12" s="19"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
@@ -4489,9 +4489,7 @@
       <c r="H50" s="19"/>
       <c r="I50" s="19"/>
       <c r="J50" s="19"/>
-      <c r="K50" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="K50" s="19"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
@@ -4519,9 +4517,7 @@
       <c r="H51" s="19"/>
       <c r="I51" s="19"/>
       <c r="J51" s="19"/>
-      <c r="K51" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="K51" s="19"/>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
@@ -6621,7 +6617,9 @@
       <c r="H126" s="19"/>
       <c r="I126" s="19"/>
       <c r="J126" s="19"/>
-      <c r="K126" s="19"/>
+      <c r="K126" s="19" t="s">
+        <v>825</v>
+      </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
@@ -7661,9 +7659,7 @@
       <c r="H163" s="19"/>
       <c r="I163" s="19"/>
       <c r="J163" s="19"/>
-      <c r="K163" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="K163" s="19"/>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
@@ -8391,9 +8387,7 @@
       <c r="H189" s="19"/>
       <c r="I189" s="19"/>
       <c r="J189" s="19"/>
-      <c r="K189" s="19" t="s">
-        <v>825</v>
-      </c>
+      <c r="K189" s="19"/>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">

--- a/procesos/inputs/Excel CCC Empresas.xlsx
+++ b/procesos/inputs/Excel CCC Empresas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\preprod\Documents\Proyectos\parche-gestoria\procesos\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E9639C-05C2-4436-B1E1-829E28E4BA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46477AE-7687-4240-9241-1A2B24D5572D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/procesos/inputs/Excel CCC Empresas.xlsx
+++ b/procesos/inputs/Excel CCC Empresas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonza\OneDrive\Nodus\Proyectos\Nodus-app\parche-gestoria\procesos\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\preprod\Documents\Proyectos\parche-gestoria\procesos\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8DA043-1D93-4251-915B-6B03C80601E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46477AE-7687-4240-9241-1A2B24D5572D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14595" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE DE DATOS (NO TOCAR)" sheetId="14" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="826">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -3033,20 +3033,20 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:K254"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.54296875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.453125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1796875" style="12" customWidth="1"/>
-    <col min="4" max="4" width="14.1796875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="58.7265625" style="6" customWidth="1"/>
-    <col min="8" max="11" width="10.81640625" style="21"/>
-    <col min="12" max="16384" width="10.81640625" style="6"/>
+    <col min="1" max="1" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="58.7109375" style="6" customWidth="1"/>
+    <col min="8" max="11" width="10.85546875" style="21"/>
+    <col min="12" max="16384" width="10.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>815</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>40</v>
       </c>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="K2" s="19"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K3" s="19"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="K4" s="19"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>40</v>
       </c>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="K5" s="22"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="K6" s="19"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -3279,7 +3279,7 @@
       <c r="J7" s="19"/>
       <c r="K7" s="19"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>215</v>
       </c>
@@ -3309,11 +3309,9 @@
       <c r="J8" s="19" t="s">
         <v>825</v>
       </c>
-      <c r="K8" s="19" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K8" s="19"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
@@ -3341,7 +3339,7 @@
       <c r="J9" s="19"/>
       <c r="K9" s="19"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
@@ -3369,7 +3367,7 @@
       <c r="J10" s="19"/>
       <c r="K10" s="22"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>45</v>
       </c>
@@ -3399,7 +3397,7 @@
       <c r="J11" s="19"/>
       <c r="K11" s="19"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>47</v>
       </c>
@@ -3427,7 +3425,7 @@
       <c r="J12" s="19"/>
       <c r="K12" s="19"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
@@ -3455,7 +3453,7 @@
       <c r="J13" s="19"/>
       <c r="K13" s="19"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>49</v>
       </c>
@@ -3483,7 +3481,7 @@
       <c r="J14" s="19"/>
       <c r="K14" s="19"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>50</v>
       </c>
@@ -3511,7 +3509,7 @@
       <c r="J15" s="19"/>
       <c r="K15" s="19"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -3539,7 +3537,7 @@
       <c r="J16" s="19"/>
       <c r="K16" s="19"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>223</v>
       </c>
@@ -3567,7 +3565,7 @@
       <c r="J17" s="19"/>
       <c r="K17" s="19"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>223</v>
       </c>
@@ -3595,7 +3593,7 @@
       <c r="J18" s="19"/>
       <c r="K18" s="19"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>223</v>
       </c>
@@ -3623,7 +3621,7 @@
       <c r="J19" s="19"/>
       <c r="K19" s="19"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>51</v>
       </c>
@@ -3651,7 +3649,7 @@
       <c r="J20" s="19"/>
       <c r="K20" s="19"/>
     </row>
-    <row r="21" spans="1:11" ht="12.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>112</v>
       </c>
@@ -3679,7 +3677,7 @@
       <c r="J21" s="19"/>
       <c r="K21" s="19"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>52</v>
       </c>
@@ -3707,7 +3705,7 @@
       <c r="J22" s="19"/>
       <c r="K22" s="19"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>52</v>
       </c>
@@ -3735,7 +3733,7 @@
       <c r="J23" s="19"/>
       <c r="K23" s="19"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>236</v>
       </c>
@@ -3763,7 +3761,7 @@
       <c r="J24" s="19"/>
       <c r="K24" s="19"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>54</v>
       </c>
@@ -3791,7 +3789,7 @@
       <c r="J25" s="19"/>
       <c r="K25" s="19"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>55</v>
       </c>
@@ -3819,7 +3817,7 @@
       <c r="J26" s="19"/>
       <c r="K26" s="19"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>57</v>
       </c>
@@ -3847,7 +3845,7 @@
       <c r="J27" s="19"/>
       <c r="K27" s="19"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>59</v>
       </c>
@@ -3875,7 +3873,7 @@
       <c r="J28" s="19"/>
       <c r="K28" s="19"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>61</v>
       </c>
@@ -3903,7 +3901,7 @@
       <c r="J29" s="19"/>
       <c r="K29" s="19"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>61</v>
       </c>
@@ -3931,7 +3929,7 @@
       <c r="J30" s="19"/>
       <c r="K30" s="19"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>62</v>
       </c>
@@ -3959,7 +3957,7 @@
       <c r="J31" s="19"/>
       <c r="K31" s="19"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>63</v>
       </c>
@@ -3987,7 +3985,7 @@
       <c r="J32" s="19"/>
       <c r="K32" s="19"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>208</v>
       </c>
@@ -4015,7 +4013,7 @@
       <c r="J33" s="19"/>
       <c r="K33" s="19"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>65</v>
       </c>
@@ -4043,7 +4041,7 @@
       <c r="J34" s="19"/>
       <c r="K34" s="19"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>238</v>
       </c>
@@ -4071,7 +4069,7 @@
       <c r="J35" s="19"/>
       <c r="K35" s="19"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>113</v>
       </c>
@@ -4099,7 +4097,7 @@
       <c r="J36" s="19"/>
       <c r="K36" s="19"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>113</v>
       </c>
@@ -4127,7 +4125,7 @@
       <c r="J37" s="19"/>
       <c r="K37" s="19"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>67</v>
       </c>
@@ -4155,7 +4153,7 @@
       <c r="J38" s="19"/>
       <c r="K38" s="19"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>69</v>
       </c>
@@ -4183,7 +4181,7 @@
       <c r="J39" s="19"/>
       <c r="K39" s="19"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>71</v>
       </c>
@@ -4211,7 +4209,7 @@
       <c r="J40" s="19"/>
       <c r="K40" s="19"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>72</v>
       </c>
@@ -4239,7 +4237,7 @@
       <c r="J41" s="19"/>
       <c r="K41" s="19"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>431</v>
       </c>
@@ -4267,7 +4265,7 @@
       <c r="J42" s="19"/>
       <c r="K42" s="19"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>434</v>
       </c>
@@ -4295,7 +4293,7 @@
       <c r="J43" s="19"/>
       <c r="K43" s="19"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>436</v>
       </c>
@@ -4323,7 +4321,7 @@
       <c r="J44" s="19"/>
       <c r="K44" s="19"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>439</v>
       </c>
@@ -4351,7 +4349,7 @@
       <c r="J45" s="19"/>
       <c r="K45" s="19"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>442</v>
       </c>
@@ -4379,7 +4377,7 @@
       <c r="J46" s="19"/>
       <c r="K46" s="19"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>164</v>
       </c>
@@ -4407,7 +4405,7 @@
       <c r="J47" s="19"/>
       <c r="K47" s="19"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>214</v>
       </c>
@@ -4435,7 +4433,7 @@
       <c r="J48" s="19"/>
       <c r="K48" s="19"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>449</v>
       </c>
@@ -4463,7 +4461,7 @@
       <c r="J49" s="19"/>
       <c r="K49" s="19"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>262</v>
       </c>
@@ -4491,7 +4489,7 @@
       <c r="J50" s="19"/>
       <c r="K50" s="19"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>262</v>
       </c>
@@ -4519,7 +4517,7 @@
       <c r="J51" s="19"/>
       <c r="K51" s="19"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>451</v>
       </c>
@@ -4547,7 +4545,7 @@
       <c r="J52" s="19"/>
       <c r="K52" s="19"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>217</v>
       </c>
@@ -4575,7 +4573,7 @@
       <c r="J53" s="19"/>
       <c r="K53" s="19"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>217</v>
       </c>
@@ -4603,7 +4601,7 @@
       <c r="J54" s="19"/>
       <c r="K54" s="19"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>217</v>
       </c>
@@ -4631,7 +4629,7 @@
       <c r="J55" s="19"/>
       <c r="K55" s="19"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>217</v>
       </c>
@@ -4659,7 +4657,7 @@
       <c r="J56" s="19"/>
       <c r="K56" s="19"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>217</v>
       </c>
@@ -4687,7 +4685,7 @@
       <c r="J57" s="19"/>
       <c r="K57" s="19"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>217</v>
       </c>
@@ -4715,7 +4713,7 @@
       <c r="J58" s="19"/>
       <c r="K58" s="19"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>458</v>
       </c>
@@ -4743,7 +4741,7 @@
       <c r="J59" s="19"/>
       <c r="K59" s="19"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>461</v>
       </c>
@@ -4771,7 +4769,7 @@
       <c r="J60" s="19"/>
       <c r="K60" s="19"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>464</v>
       </c>
@@ -4799,7 +4797,7 @@
       <c r="J61" s="19"/>
       <c r="K61" s="19"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>467</v>
       </c>
@@ -4827,7 +4825,7 @@
       <c r="J62" s="19"/>
       <c r="K62" s="19"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>198</v>
       </c>
@@ -4855,7 +4853,7 @@
       <c r="J63" s="19"/>
       <c r="K63" s="19"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>198</v>
       </c>
@@ -4883,7 +4881,7 @@
       <c r="J64" s="19"/>
       <c r="K64" s="19"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>472</v>
       </c>
@@ -4911,7 +4909,7 @@
       <c r="J65" s="19"/>
       <c r="K65" s="19"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>474</v>
       </c>
@@ -4939,7 +4937,7 @@
       <c r="J66" s="19"/>
       <c r="K66" s="19"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>196</v>
       </c>
@@ -4967,7 +4965,7 @@
       <c r="J67" s="19"/>
       <c r="K67" s="19"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>478</v>
       </c>
@@ -4995,7 +4993,7 @@
       <c r="J68" s="19"/>
       <c r="K68" s="19"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>480</v>
       </c>
@@ -5023,7 +5021,7 @@
       <c r="J69" s="19"/>
       <c r="K69" s="19"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>480</v>
       </c>
@@ -5051,7 +5049,7 @@
       <c r="J70" s="19"/>
       <c r="K70" s="19"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>115</v>
       </c>
@@ -5079,7 +5077,7 @@
       <c r="J71" s="19"/>
       <c r="K71" s="19"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>485</v>
       </c>
@@ -5107,7 +5105,7 @@
       <c r="J72" s="19"/>
       <c r="K72" s="19"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>488</v>
       </c>
@@ -5135,7 +5133,7 @@
       <c r="J73" s="19"/>
       <c r="K73" s="19"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>491</v>
       </c>
@@ -5163,7 +5161,7 @@
       <c r="J74" s="19"/>
       <c r="K74" s="19"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>494</v>
       </c>
@@ -5191,7 +5189,7 @@
       <c r="J75" s="19"/>
       <c r="K75" s="19"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>494</v>
       </c>
@@ -5219,7 +5217,7 @@
       <c r="J76" s="19"/>
       <c r="K76" s="19"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>170</v>
       </c>
@@ -5247,7 +5245,7 @@
       <c r="J77" s="19"/>
       <c r="K77" s="19"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>130</v>
       </c>
@@ -5275,7 +5273,7 @@
       <c r="J78" s="19"/>
       <c r="K78" s="19"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>161</v>
       </c>
@@ -5303,7 +5301,7 @@
       <c r="J79" s="19"/>
       <c r="K79" s="19"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>137</v>
       </c>
@@ -5331,7 +5329,7 @@
       <c r="J80" s="19"/>
       <c r="K80" s="19"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>503</v>
       </c>
@@ -5359,7 +5357,7 @@
       <c r="J81" s="19"/>
       <c r="K81" s="19"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>506</v>
       </c>
@@ -5387,7 +5385,7 @@
       <c r="J82" s="19"/>
       <c r="K82" s="19"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>509</v>
       </c>
@@ -5415,7 +5413,7 @@
       <c r="J83" s="19"/>
       <c r="K83" s="19"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>512</v>
       </c>
@@ -5443,7 +5441,7 @@
       <c r="J84" s="19"/>
       <c r="K84" s="19"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>116</v>
       </c>
@@ -5471,7 +5469,7 @@
       <c r="J85" s="19"/>
       <c r="K85" s="19"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>516</v>
       </c>
@@ -5499,7 +5497,7 @@
       <c r="J86" s="19"/>
       <c r="K86" s="19"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>519</v>
       </c>
@@ -5527,7 +5525,7 @@
       <c r="J87" s="19"/>
       <c r="K87" s="19"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>519</v>
       </c>
@@ -5555,7 +5553,7 @@
       <c r="J88" s="19"/>
       <c r="K88" s="19"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>519</v>
       </c>
@@ -5583,7 +5581,7 @@
       <c r="J89" s="19"/>
       <c r="K89" s="19"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>522</v>
       </c>
@@ -5611,7 +5609,7 @@
       <c r="J90" s="19"/>
       <c r="K90" s="19"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>525</v>
       </c>
@@ -5639,7 +5637,7 @@
       <c r="J91" s="19"/>
       <c r="K91" s="19"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>117</v>
       </c>
@@ -5667,7 +5665,7 @@
       <c r="J92" s="19"/>
       <c r="K92" s="19"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>529</v>
       </c>
@@ -5695,7 +5693,7 @@
       <c r="J93" s="19"/>
       <c r="K93" s="19"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>529</v>
       </c>
@@ -5723,7 +5721,7 @@
       <c r="J94" s="19"/>
       <c r="K94" s="19"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>529</v>
       </c>
@@ -5751,7 +5749,7 @@
       <c r="J95" s="19"/>
       <c r="K95" s="19"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>531</v>
       </c>
@@ -5779,7 +5777,7 @@
       <c r="J96" s="19"/>
       <c r="K96" s="19"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>536</v>
       </c>
@@ -5807,7 +5805,7 @@
       <c r="J97" s="19"/>
       <c r="K97" s="19"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>536</v>
       </c>
@@ -5835,7 +5833,7 @@
       <c r="J98" s="19"/>
       <c r="K98" s="19"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>534</v>
       </c>
@@ -5863,7 +5861,7 @@
       <c r="J99" s="19"/>
       <c r="K99" s="19"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>267</v>
       </c>
@@ -5891,7 +5889,7 @@
       <c r="J100" s="19"/>
       <c r="K100" s="19"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>267</v>
       </c>
@@ -5919,7 +5917,7 @@
       <c r="J101" s="19"/>
       <c r="K101" s="19"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>540</v>
       </c>
@@ -5947,7 +5945,7 @@
       <c r="J102" s="19"/>
       <c r="K102" s="19"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>540</v>
       </c>
@@ -5975,7 +5973,7 @@
       <c r="J103" s="19"/>
       <c r="K103" s="19"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>540</v>
       </c>
@@ -6003,7 +6001,7 @@
       <c r="J104" s="19"/>
       <c r="K104" s="19"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>543</v>
       </c>
@@ -6031,7 +6029,7 @@
       <c r="J105" s="19"/>
       <c r="K105" s="19"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>543</v>
       </c>
@@ -6059,7 +6057,7 @@
       <c r="J106" s="19"/>
       <c r="K106" s="19"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>545</v>
       </c>
@@ -6087,7 +6085,7 @@
       <c r="J107" s="19"/>
       <c r="K107" s="19"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>548</v>
       </c>
@@ -6115,7 +6113,7 @@
       <c r="J108" s="19"/>
       <c r="K108" s="19"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>805</v>
       </c>
@@ -6143,7 +6141,7 @@
       <c r="J109" s="19"/>
       <c r="K109" s="19"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>167</v>
       </c>
@@ -6171,7 +6169,7 @@
       <c r="J110" s="19"/>
       <c r="K110" s="19"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>554</v>
       </c>
@@ -6199,7 +6197,7 @@
       <c r="J111" s="19"/>
       <c r="K111" s="19"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>295</v>
       </c>
@@ -6227,7 +6225,7 @@
       <c r="J112" s="19"/>
       <c r="K112" s="19"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>558</v>
       </c>
@@ -6255,7 +6253,7 @@
       <c r="J113" s="19"/>
       <c r="K113" s="19"/>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>560</v>
       </c>
@@ -6283,7 +6281,7 @@
       <c r="J114" s="19"/>
       <c r="K114" s="19"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>110</v>
       </c>
@@ -6311,7 +6309,7 @@
       <c r="J115" s="19"/>
       <c r="K115" s="19"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>353</v>
       </c>
@@ -6339,7 +6337,7 @@
       <c r="J116" s="19"/>
       <c r="K116" s="19"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>564</v>
       </c>
@@ -6367,7 +6365,7 @@
       <c r="J117" s="19"/>
       <c r="K117" s="19"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>564</v>
       </c>
@@ -6395,7 +6393,7 @@
       <c r="J118" s="19"/>
       <c r="K118" s="19"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>350</v>
       </c>
@@ -6423,7 +6421,7 @@
       <c r="J119" s="19"/>
       <c r="K119" s="19"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>568</v>
       </c>
@@ -6451,7 +6449,7 @@
       <c r="J120" s="19"/>
       <c r="K120" s="19"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>568</v>
       </c>
@@ -6479,7 +6477,7 @@
       <c r="J121" s="19"/>
       <c r="K121" s="19"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>800</v>
       </c>
@@ -6507,7 +6505,7 @@
       <c r="J122" s="19"/>
       <c r="K122" s="19"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>121</v>
       </c>
@@ -6535,7 +6533,7 @@
       <c r="J123" s="19"/>
       <c r="K123" s="19"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>572</v>
       </c>
@@ -6563,7 +6561,7 @@
       <c r="J124" s="19"/>
       <c r="K124" s="19"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>572</v>
       </c>
@@ -6591,7 +6589,7 @@
       <c r="J125" s="19"/>
       <c r="K125" s="19"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>575</v>
       </c>
@@ -6621,7 +6619,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>135</v>
       </c>
@@ -6649,7 +6647,7 @@
       <c r="J127" s="19"/>
       <c r="K127" s="19"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>231</v>
       </c>
@@ -6677,7 +6675,7 @@
       <c r="J128" s="19"/>
       <c r="K128" s="19"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>581</v>
       </c>
@@ -6705,7 +6703,7 @@
       <c r="J129" s="19"/>
       <c r="K129" s="19"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>581</v>
       </c>
@@ -6733,7 +6731,7 @@
       <c r="J130" s="19"/>
       <c r="K130" s="19"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>584</v>
       </c>
@@ -6761,7 +6759,7 @@
       <c r="J131" s="19"/>
       <c r="K131" s="19"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>587</v>
       </c>
@@ -6789,7 +6787,7 @@
       <c r="J132" s="19"/>
       <c r="K132" s="19"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>590</v>
       </c>
@@ -6817,7 +6815,7 @@
       <c r="J133" s="19"/>
       <c r="K133" s="19"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>593</v>
       </c>
@@ -6845,7 +6843,7 @@
       <c r="J134" s="19"/>
       <c r="K134" s="19"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>145</v>
       </c>
@@ -6873,7 +6871,7 @@
       <c r="J135" s="19"/>
       <c r="K135" s="19"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>596</v>
       </c>
@@ -6901,7 +6899,7 @@
       <c r="J136" s="19"/>
       <c r="K136" s="19"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>598</v>
       </c>
@@ -6929,7 +6927,7 @@
       <c r="J137" s="19"/>
       <c r="K137" s="19"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>601</v>
       </c>
@@ -6957,7 +6955,7 @@
       <c r="J138" s="19"/>
       <c r="K138" s="19"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>604</v>
       </c>
@@ -6985,7 +6983,7 @@
       <c r="J139" s="19"/>
       <c r="K139" s="19"/>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>607</v>
       </c>
@@ -7013,7 +7011,7 @@
       <c r="J140" s="19"/>
       <c r="K140" s="19"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>610</v>
       </c>
@@ -7041,7 +7039,7 @@
       <c r="J141" s="19"/>
       <c r="K141" s="19"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>613</v>
       </c>
@@ -7069,7 +7067,7 @@
       <c r="J142" s="19"/>
       <c r="K142" s="19"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>616</v>
       </c>
@@ -7097,7 +7095,7 @@
       <c r="J143" s="19"/>
       <c r="K143" s="19"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>619</v>
       </c>
@@ -7125,7 +7123,7 @@
       <c r="J144" s="19"/>
       <c r="K144" s="19"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>622</v>
       </c>
@@ -7153,7 +7151,7 @@
       <c r="J145" s="19"/>
       <c r="K145" s="19"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>622</v>
       </c>
@@ -7181,7 +7179,7 @@
       <c r="J146" s="19"/>
       <c r="K146" s="19"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>624</v>
       </c>
@@ -7209,7 +7207,7 @@
       <c r="J147" s="19"/>
       <c r="K147" s="19"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>627</v>
       </c>
@@ -7237,7 +7235,7 @@
       <c r="J148" s="19"/>
       <c r="K148" s="19"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>630</v>
       </c>
@@ -7265,7 +7263,7 @@
       <c r="J149" s="19"/>
       <c r="K149" s="19"/>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>633</v>
       </c>
@@ -7293,7 +7291,7 @@
       <c r="J150" s="19"/>
       <c r="K150" s="19"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>636</v>
       </c>
@@ -7321,7 +7319,7 @@
       <c r="J151" s="19"/>
       <c r="K151" s="19"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>639</v>
       </c>
@@ -7353,7 +7351,7 @@
       <c r="J152" s="19"/>
       <c r="K152" s="19"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>202</v>
       </c>
@@ -7381,7 +7379,7 @@
       <c r="J153" s="19"/>
       <c r="K153" s="19"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>122</v>
       </c>
@@ -7409,7 +7407,7 @@
       <c r="J154" s="19"/>
       <c r="K154" s="19"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>122</v>
       </c>
@@ -7437,7 +7435,7 @@
       <c r="J155" s="19"/>
       <c r="K155" s="19"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>103</v>
       </c>
@@ -7465,7 +7463,7 @@
       <c r="J156" s="19"/>
       <c r="K156" s="19"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>105</v>
       </c>
@@ -7493,7 +7491,7 @@
       <c r="J157" s="19"/>
       <c r="K157" s="19"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>107</v>
       </c>
@@ -7521,7 +7519,7 @@
       <c r="J158" s="19"/>
       <c r="K158" s="19"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>111</v>
       </c>
@@ -7549,7 +7547,7 @@
       <c r="J159" s="19"/>
       <c r="K159" s="19"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>651</v>
       </c>
@@ -7577,7 +7575,7 @@
       <c r="J160" s="19"/>
       <c r="K160" s="19"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>654</v>
       </c>
@@ -7605,7 +7603,7 @@
       <c r="J161" s="19"/>
       <c r="K161" s="19"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>148</v>
       </c>
@@ -7633,7 +7631,7 @@
       <c r="J162" s="19"/>
       <c r="K162" s="19"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>134</v>
       </c>
@@ -7659,9 +7657,11 @@
       <c r="H163" s="19"/>
       <c r="I163" s="19"/>
       <c r="J163" s="19"/>
-      <c r="K163" s="19"/>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K163" s="19" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>282</v>
       </c>
@@ -7689,7 +7689,7 @@
       <c r="J164" s="19"/>
       <c r="K164" s="19"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>127</v>
       </c>
@@ -7717,7 +7717,7 @@
       <c r="J165" s="19"/>
       <c r="K165" s="19"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>127</v>
       </c>
@@ -7745,7 +7745,7 @@
       <c r="J166" s="19"/>
       <c r="K166" s="19"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>158</v>
       </c>
@@ -7773,7 +7773,7 @@
       <c r="J167" s="19"/>
       <c r="K167" s="19"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>177</v>
       </c>
@@ -7801,7 +7801,7 @@
       <c r="J168" s="19"/>
       <c r="K168" s="19"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>132</v>
       </c>
@@ -7829,7 +7829,7 @@
       <c r="J169" s="19"/>
       <c r="K169" s="19"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>131</v>
       </c>
@@ -7857,7 +7857,7 @@
       <c r="J170" s="19"/>
       <c r="K170" s="19"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>141</v>
       </c>
@@ -7885,7 +7885,7 @@
       <c r="J171" s="19"/>
       <c r="K171" s="19"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>142</v>
       </c>
@@ -7913,7 +7913,7 @@
       <c r="J172" s="19"/>
       <c r="K172" s="19"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>228</v>
       </c>
@@ -7941,7 +7941,7 @@
       <c r="J173" s="19"/>
       <c r="K173" s="19"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>230</v>
       </c>
@@ -7969,7 +7969,7 @@
       <c r="J174" s="19"/>
       <c r="K174" s="19"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>147</v>
       </c>
@@ -7997,7 +7997,7 @@
       <c r="J175" s="19"/>
       <c r="K175" s="19"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>151</v>
       </c>
@@ -8025,7 +8025,7 @@
       <c r="J176" s="19"/>
       <c r="K176" s="19"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>681</v>
       </c>
@@ -8053,7 +8053,7 @@
       <c r="J177" s="19"/>
       <c r="K177" s="19"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>154</v>
       </c>
@@ -8081,7 +8081,7 @@
       <c r="J178" s="19"/>
       <c r="K178" s="19"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>156</v>
       </c>
@@ -8109,7 +8109,7 @@
       <c r="J179" s="19"/>
       <c r="K179" s="19"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>168</v>
       </c>
@@ -8137,7 +8137,7 @@
       <c r="J180" s="19"/>
       <c r="K180" s="19"/>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>163</v>
       </c>
@@ -8165,7 +8165,7 @@
       <c r="J181" s="19"/>
       <c r="K181" s="19"/>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>374</v>
       </c>
@@ -8193,7 +8193,7 @@
       <c r="J182" s="19"/>
       <c r="K182" s="19"/>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>173</v>
       </c>
@@ -8221,7 +8221,7 @@
       <c r="J183" s="19"/>
       <c r="K183" s="19"/>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>173</v>
       </c>
@@ -8249,7 +8249,7 @@
       <c r="J184" s="19"/>
       <c r="K184" s="19"/>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>175</v>
       </c>
@@ -8277,7 +8277,7 @@
       <c r="J185" s="19"/>
       <c r="K185" s="19"/>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>175</v>
       </c>
@@ -8305,7 +8305,7 @@
       <c r="J186" s="19"/>
       <c r="K186" s="19"/>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>175</v>
       </c>
@@ -8333,7 +8333,7 @@
       <c r="J187" s="19"/>
       <c r="K187" s="19"/>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>179</v>
       </c>
@@ -8361,7 +8361,7 @@
       <c r="J188" s="19"/>
       <c r="K188" s="19"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>696</v>
       </c>
@@ -8387,9 +8387,11 @@
       <c r="H189" s="19"/>
       <c r="I189" s="19"/>
       <c r="J189" s="19"/>
-      <c r="K189" s="19"/>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K189" s="19" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>298</v>
       </c>
@@ -8417,7 +8419,7 @@
       <c r="J190" s="19"/>
       <c r="K190" s="19"/>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>797</v>
       </c>
@@ -8445,7 +8447,7 @@
       <c r="J191" s="19"/>
       <c r="K191" s="19"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>185</v>
       </c>
@@ -8473,7 +8475,7 @@
       <c r="J192" s="19"/>
       <c r="K192" s="19"/>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>185</v>
       </c>
@@ -8501,7 +8503,7 @@
       <c r="J193" s="19"/>
       <c r="K193" s="19"/>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>183</v>
       </c>
@@ -8529,7 +8531,7 @@
       <c r="J194" s="19"/>
       <c r="K194" s="19"/>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>703</v>
       </c>
@@ -8557,7 +8559,7 @@
       <c r="J195" s="19"/>
       <c r="K195" s="19"/>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>705</v>
       </c>
@@ -8585,7 +8587,7 @@
       <c r="J196" s="19"/>
       <c r="K196" s="19"/>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>188</v>
       </c>
@@ -8613,7 +8615,7 @@
       <c r="J197" s="19"/>
       <c r="K197" s="19"/>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>191</v>
       </c>
@@ -8641,7 +8643,7 @@
       <c r="J198" s="19"/>
       <c r="K198" s="19"/>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>711</v>
       </c>
@@ -8669,7 +8671,7 @@
       <c r="J199" s="19"/>
       <c r="K199" s="19"/>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>219</v>
       </c>
@@ -8697,7 +8699,7 @@
       <c r="J200" s="19"/>
       <c r="K200" s="19"/>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>713</v>
       </c>
@@ -8725,7 +8727,7 @@
       <c r="J201" s="19"/>
       <c r="K201" s="19"/>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>716</v>
       </c>
@@ -8755,7 +8757,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>359</v>
       </c>
@@ -8783,7 +8785,7 @@
       <c r="J203" s="19"/>
       <c r="K203" s="19"/>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>204</v>
       </c>
@@ -8811,7 +8813,7 @@
       <c r="J204" s="19"/>
       <c r="K204" s="19"/>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>206</v>
       </c>
@@ -8839,7 +8841,7 @@
       <c r="J205" s="19"/>
       <c r="K205" s="19"/>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>240</v>
       </c>
@@ -8867,7 +8869,7 @@
       <c r="J206" s="19"/>
       <c r="K206" s="19"/>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>212</v>
       </c>
@@ -8895,7 +8897,7 @@
       <c r="J207" s="19"/>
       <c r="K207" s="19"/>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>226</v>
       </c>
@@ -8923,7 +8925,7 @@
       <c r="J208" s="19"/>
       <c r="K208" s="19"/>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>221</v>
       </c>
@@ -8951,7 +8953,7 @@
       <c r="J209" s="19"/>
       <c r="K209" s="19"/>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>221</v>
       </c>
@@ -8979,7 +8981,7 @@
       <c r="J210" s="19"/>
       <c r="K210" s="19"/>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>221</v>
       </c>
@@ -9007,7 +9009,7 @@
       <c r="J211" s="19"/>
       <c r="K211" s="19"/>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>221</v>
       </c>
@@ -9035,7 +9037,7 @@
       <c r="J212" s="19"/>
       <c r="K212" s="19"/>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>221</v>
       </c>
@@ -9063,7 +9065,7 @@
       <c r="J213" s="19"/>
       <c r="K213" s="19"/>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>732</v>
       </c>
@@ -9091,7 +9093,7 @@
       <c r="J214" s="19"/>
       <c r="K214" s="19"/>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>232</v>
       </c>
@@ -9119,7 +9121,7 @@
       <c r="J215" s="19"/>
       <c r="K215" s="19"/>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>242</v>
       </c>
@@ -9147,7 +9149,7 @@
       <c r="J216" s="19"/>
       <c r="K216" s="19"/>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>247</v>
       </c>
@@ -9175,7 +9177,7 @@
       <c r="J217" s="19"/>
       <c r="K217" s="19"/>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>740</v>
       </c>
@@ -9203,7 +9205,7 @@
       <c r="J218" s="19"/>
       <c r="K218" s="19"/>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>251</v>
       </c>
@@ -9231,7 +9233,7 @@
       <c r="J219" s="19"/>
       <c r="K219" s="19"/>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>276</v>
       </c>
@@ -9259,7 +9261,7 @@
       <c r="J220" s="19"/>
       <c r="K220" s="19"/>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>746</v>
       </c>
@@ -9287,7 +9289,7 @@
       <c r="J221" s="19"/>
       <c r="K221" s="19"/>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>257</v>
       </c>
@@ -9315,7 +9317,7 @@
       <c r="J222" s="19"/>
       <c r="K222" s="19"/>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>748</v>
       </c>
@@ -9343,7 +9345,7 @@
       <c r="J223" s="19"/>
       <c r="K223" s="19"/>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>263</v>
       </c>
@@ -9371,7 +9373,7 @@
       <c r="J224" s="19"/>
       <c r="K224" s="19"/>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>260</v>
       </c>
@@ -9399,7 +9401,7 @@
       <c r="J225" s="19"/>
       <c r="K225" s="19"/>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>264</v>
       </c>
@@ -9427,7 +9429,7 @@
       <c r="J226" s="19"/>
       <c r="K226" s="19"/>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>269</v>
       </c>
@@ -9455,7 +9457,7 @@
       <c r="J227" s="19"/>
       <c r="K227" s="19"/>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>270</v>
       </c>
@@ -9483,7 +9485,7 @@
       <c r="J228" s="19"/>
       <c r="K228" s="19"/>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>270</v>
       </c>
@@ -9511,7 +9513,7 @@
       <c r="J229" s="19"/>
       <c r="K229" s="19"/>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>279</v>
       </c>
@@ -9539,7 +9541,7 @@
       <c r="J230" s="19"/>
       <c r="K230" s="19"/>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>278</v>
       </c>
@@ -9567,7 +9569,7 @@
       <c r="J231" s="19"/>
       <c r="K231" s="19"/>
     </row>
-    <row r="232" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>284</v>
       </c>
@@ -9595,7 +9597,7 @@
       <c r="J232" s="20"/>
       <c r="K232" s="20"/>
     </row>
-    <row r="233" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>765</v>
       </c>
@@ -9623,7 +9625,7 @@
       <c r="J233" s="20"/>
       <c r="K233" s="20"/>
     </row>
-    <row r="234" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>288</v>
       </c>
@@ -9651,7 +9653,7 @@
       <c r="J234" s="20"/>
       <c r="K234" s="20"/>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>287</v>
       </c>
@@ -9679,7 +9681,7 @@
       <c r="J235" s="19"/>
       <c r="K235" s="19"/>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>289</v>
       </c>
@@ -9707,7 +9709,7 @@
       <c r="J236" s="19"/>
       <c r="K236" s="19"/>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>290</v>
       </c>
@@ -9735,7 +9737,7 @@
       <c r="J237" s="19"/>
       <c r="K237" s="19"/>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>774</v>
       </c>
@@ -9763,7 +9765,7 @@
       <c r="J238" s="19"/>
       <c r="K238" s="19"/>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>303</v>
       </c>
@@ -9791,7 +9793,7 @@
       <c r="J239" s="19"/>
       <c r="K239" s="19"/>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>304</v>
       </c>
@@ -9819,7 +9821,7 @@
       <c r="J240" s="19"/>
       <c r="K240" s="19"/>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>305</v>
       </c>
@@ -9847,7 +9849,7 @@
       <c r="J241" s="19"/>
       <c r="K241" s="19"/>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>300</v>
       </c>
@@ -9875,7 +9877,7 @@
       <c r="J242" s="19"/>
       <c r="K242" s="19"/>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>348</v>
       </c>
@@ -9903,7 +9905,7 @@
       <c r="J243" s="19"/>
       <c r="K243" s="19"/>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>357</v>
       </c>
@@ -9931,7 +9933,7 @@
       <c r="J244" s="19"/>
       <c r="K244" s="19"/>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>351</v>
       </c>
@@ -9959,7 +9961,7 @@
       <c r="J245" s="19"/>
       <c r="K245" s="19"/>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>361</v>
       </c>
@@ -9987,7 +9989,7 @@
       <c r="J246" s="19"/>
       <c r="K246" s="19"/>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>365</v>
       </c>
@@ -10015,7 +10017,7 @@
       <c r="J247" s="19"/>
       <c r="K247" s="19"/>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>363</v>
       </c>
@@ -10043,7 +10045,7 @@
       <c r="J248" s="19"/>
       <c r="K248" s="19"/>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>355</v>
       </c>
@@ -10071,7 +10073,7 @@
       <c r="J249" s="19"/>
       <c r="K249" s="19"/>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>368</v>
       </c>
@@ -10099,7 +10101,7 @@
       <c r="J250" s="19"/>
       <c r="K250" s="19"/>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>367</v>
       </c>
@@ -10127,7 +10129,7 @@
       <c r="J251" s="19"/>
       <c r="K251" s="19"/>
     </row>
-    <row r="252" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>367</v>
       </c>
@@ -10155,7 +10157,7 @@
       <c r="J252" s="19"/>
       <c r="K252" s="19"/>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>371</v>
       </c>
@@ -10183,7 +10185,7 @@
       <c r="J253" s="19"/>
       <c r="K253" s="19"/>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>816</v>
       </c>
@@ -10221,21 +10223,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100AF0C36E9CBDE43468AAB846756A8BA94" ma:contentTypeVersion="0" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="93c275e25462616b2c1de9b58ec156dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f6edc329ff236629c56e3b879b320d0">
     <xsd:element name="properties">
@@ -10349,15 +10342,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDD49F8-6691-4324-BC0D-0B1E4890A2C6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEFD23-736F-4CE9-81DA-D9D145B9B572}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -10372,7 +10366,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A01C7383-C303-4DC2-9970-99C89A193825}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10386,4 +10380,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDD49F8-6691-4324-BC0D-0B1E4890A2C6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/procesos/inputs/Excel CCC Empresas.xlsx
+++ b/procesos/inputs/Excel CCC Empresas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\preprod\Documents\Proyectos\parche-gestoria\procesos\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gonza\OneDrive\Nodus\Proyectos\Nodus-app\parche-gestoria\procesos\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46477AE-7687-4240-9241-1A2B24D5572D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8DA043-1D93-4251-915B-6B03C80601E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14595" yWindow="-16350" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE DE DATOS (NO TOCAR)" sheetId="14" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="826">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -3033,20 +3033,20 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:K254"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="12" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="58.7109375" style="6" customWidth="1"/>
-    <col min="8" max="11" width="10.85546875" style="21"/>
-    <col min="12" max="16384" width="10.85546875" style="6"/>
+    <col min="1" max="1" width="10.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.1796875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="14.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="58.7265625" style="6" customWidth="1"/>
+    <col min="8" max="11" width="10.81640625" style="21"/>
+    <col min="12" max="16384" width="10.81640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>815</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>40</v>
       </c>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="K2" s="19"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>40</v>
       </c>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K3" s="19"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="K4" s="19"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>40</v>
       </c>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="K5" s="22"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="K6" s="19"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -3279,7 +3279,7 @@
       <c r="J7" s="19"/>
       <c r="K7" s="19"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>215</v>
       </c>
@@ -3309,9 +3309,11 @@
       <c r="J8" s="19" t="s">
         <v>825</v>
       </c>
-      <c r="K8" s="19"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K8" s="19" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>43</v>
       </c>
@@ -3339,7 +3341,7 @@
       <c r="J9" s="19"/>
       <c r="K9" s="19"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
@@ -3367,7 +3369,7 @@
       <c r="J10" s="19"/>
       <c r="K10" s="22"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>45</v>
       </c>
@@ -3397,7 +3399,7 @@
       <c r="J11" s="19"/>
       <c r="K11" s="19"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>47</v>
       </c>
@@ -3425,7 +3427,7 @@
       <c r="J12" s="19"/>
       <c r="K12" s="19"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
@@ -3453,7 +3455,7 @@
       <c r="J13" s="19"/>
       <c r="K13" s="19"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>49</v>
       </c>
@@ -3481,7 +3483,7 @@
       <c r="J14" s="19"/>
       <c r="K14" s="19"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>50</v>
       </c>
@@ -3509,7 +3511,7 @@
       <c r="J15" s="19"/>
       <c r="K15" s="19"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -3537,7 +3539,7 @@
       <c r="J16" s="19"/>
       <c r="K16" s="19"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>223</v>
       </c>
@@ -3565,7 +3567,7 @@
       <c r="J17" s="19"/>
       <c r="K17" s="19"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>223</v>
       </c>
@@ -3593,7 +3595,7 @@
       <c r="J18" s="19"/>
       <c r="K18" s="19"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>223</v>
       </c>
@@ -3621,7 +3623,7 @@
       <c r="J19" s="19"/>
       <c r="K19" s="19"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>51</v>
       </c>
@@ -3649,7 +3651,7 @@
       <c r="J20" s="19"/>
       <c r="K20" s="19"/>
     </row>
-    <row r="21" spans="1:11" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>112</v>
       </c>
@@ -3677,7 +3679,7 @@
       <c r="J21" s="19"/>
       <c r="K21" s="19"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>52</v>
       </c>
@@ -3705,7 +3707,7 @@
       <c r="J22" s="19"/>
       <c r="K22" s="19"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>52</v>
       </c>
@@ -3733,7 +3735,7 @@
       <c r="J23" s="19"/>
       <c r="K23" s="19"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>236</v>
       </c>
@@ -3761,7 +3763,7 @@
       <c r="J24" s="19"/>
       <c r="K24" s="19"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>54</v>
       </c>
@@ -3789,7 +3791,7 @@
       <c r="J25" s="19"/>
       <c r="K25" s="19"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>55</v>
       </c>
@@ -3817,7 +3819,7 @@
       <c r="J26" s="19"/>
       <c r="K26" s="19"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>57</v>
       </c>
@@ -3845,7 +3847,7 @@
       <c r="J27" s="19"/>
       <c r="K27" s="19"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>59</v>
       </c>
@@ -3873,7 +3875,7 @@
       <c r="J28" s="19"/>
       <c r="K28" s="19"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>61</v>
       </c>
@@ -3901,7 +3903,7 @@
       <c r="J29" s="19"/>
       <c r="K29" s="19"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>61</v>
       </c>
@@ -3929,7 +3931,7 @@
       <c r="J30" s="19"/>
       <c r="K30" s="19"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>62</v>
       </c>
@@ -3957,7 +3959,7 @@
       <c r="J31" s="19"/>
       <c r="K31" s="19"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>63</v>
       </c>
@@ -3985,7 +3987,7 @@
       <c r="J32" s="19"/>
       <c r="K32" s="19"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>208</v>
       </c>
@@ -4013,7 +4015,7 @@
       <c r="J33" s="19"/>
       <c r="K33" s="19"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>65</v>
       </c>
@@ -4041,7 +4043,7 @@
       <c r="J34" s="19"/>
       <c r="K34" s="19"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>238</v>
       </c>
@@ -4069,7 +4071,7 @@
       <c r="J35" s="19"/>
       <c r="K35" s="19"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>113</v>
       </c>
@@ -4097,7 +4099,7 @@
       <c r="J36" s="19"/>
       <c r="K36" s="19"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>113</v>
       </c>
@@ -4125,7 +4127,7 @@
       <c r="J37" s="19"/>
       <c r="K37" s="19"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>67</v>
       </c>
@@ -4153,7 +4155,7 @@
       <c r="J38" s="19"/>
       <c r="K38" s="19"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>69</v>
       </c>
@@ -4181,7 +4183,7 @@
       <c r="J39" s="19"/>
       <c r="K39" s="19"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>71</v>
       </c>
@@ -4209,7 +4211,7 @@
       <c r="J40" s="19"/>
       <c r="K40" s="19"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>72</v>
       </c>
@@ -4237,7 +4239,7 @@
       <c r="J41" s="19"/>
       <c r="K41" s="19"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>431</v>
       </c>
@@ -4265,7 +4267,7 @@
       <c r="J42" s="19"/>
       <c r="K42" s="19"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>434</v>
       </c>
@@ -4293,7 +4295,7 @@
       <c r="J43" s="19"/>
       <c r="K43" s="19"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>436</v>
       </c>
@@ -4321,7 +4323,7 @@
       <c r="J44" s="19"/>
       <c r="K44" s="19"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>439</v>
       </c>
@@ -4349,7 +4351,7 @@
       <c r="J45" s="19"/>
       <c r="K45" s="19"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>442</v>
       </c>
@@ -4377,7 +4379,7 @@
       <c r="J46" s="19"/>
       <c r="K46" s="19"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>164</v>
       </c>
@@ -4405,7 +4407,7 @@
       <c r="J47" s="19"/>
       <c r="K47" s="19"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>214</v>
       </c>
@@ -4433,7 +4435,7 @@
       <c r="J48" s="19"/>
       <c r="K48" s="19"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>449</v>
       </c>
@@ -4461,7 +4463,7 @@
       <c r="J49" s="19"/>
       <c r="K49" s="19"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>262</v>
       </c>
@@ -4489,7 +4491,7 @@
       <c r="J50" s="19"/>
       <c r="K50" s="19"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>262</v>
       </c>
@@ -4517,7 +4519,7 @@
       <c r="J51" s="19"/>
       <c r="K51" s="19"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>451</v>
       </c>
@@ -4545,7 +4547,7 @@
       <c r="J52" s="19"/>
       <c r="K52" s="19"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>217</v>
       </c>
@@ -4573,7 +4575,7 @@
       <c r="J53" s="19"/>
       <c r="K53" s="19"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>217</v>
       </c>
@@ -4601,7 +4603,7 @@
       <c r="J54" s="19"/>
       <c r="K54" s="19"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>217</v>
       </c>
@@ -4629,7 +4631,7 @@
       <c r="J55" s="19"/>
       <c r="K55" s="19"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>217</v>
       </c>
@@ -4657,7 +4659,7 @@
       <c r="J56" s="19"/>
       <c r="K56" s="19"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>217</v>
       </c>
@@ -4685,7 +4687,7 @@
       <c r="J57" s="19"/>
       <c r="K57" s="19"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>217</v>
       </c>
@@ -4713,7 +4715,7 @@
       <c r="J58" s="19"/>
       <c r="K58" s="19"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>458</v>
       </c>
@@ -4741,7 +4743,7 @@
       <c r="J59" s="19"/>
       <c r="K59" s="19"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>461</v>
       </c>
@@ -4769,7 +4771,7 @@
       <c r="J60" s="19"/>
       <c r="K60" s="19"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>464</v>
       </c>
@@ -4797,7 +4799,7 @@
       <c r="J61" s="19"/>
       <c r="K61" s="19"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>467</v>
       </c>
@@ -4825,7 +4827,7 @@
       <c r="J62" s="19"/>
       <c r="K62" s="19"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>198</v>
       </c>
@@ -4853,7 +4855,7 @@
       <c r="J63" s="19"/>
       <c r="K63" s="19"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>198</v>
       </c>
@@ -4881,7 +4883,7 @@
       <c r="J64" s="19"/>
       <c r="K64" s="19"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>472</v>
       </c>
@@ -4909,7 +4911,7 @@
       <c r="J65" s="19"/>
       <c r="K65" s="19"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>474</v>
       </c>
@@ -4937,7 +4939,7 @@
       <c r="J66" s="19"/>
       <c r="K66" s="19"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>196</v>
       </c>
@@ -4965,7 +4967,7 @@
       <c r="J67" s="19"/>
       <c r="K67" s="19"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>478</v>
       </c>
@@ -4993,7 +4995,7 @@
       <c r="J68" s="19"/>
       <c r="K68" s="19"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>480</v>
       </c>
@@ -5021,7 +5023,7 @@
       <c r="J69" s="19"/>
       <c r="K69" s="19"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>480</v>
       </c>
@@ -5049,7 +5051,7 @@
       <c r="J70" s="19"/>
       <c r="K70" s="19"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>115</v>
       </c>
@@ -5077,7 +5079,7 @@
       <c r="J71" s="19"/>
       <c r="K71" s="19"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>485</v>
       </c>
@@ -5105,7 +5107,7 @@
       <c r="J72" s="19"/>
       <c r="K72" s="19"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>488</v>
       </c>
@@ -5133,7 +5135,7 @@
       <c r="J73" s="19"/>
       <c r="K73" s="19"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>491</v>
       </c>
@@ -5161,7 +5163,7 @@
       <c r="J74" s="19"/>
       <c r="K74" s="19"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>494</v>
       </c>
@@ -5189,7 +5191,7 @@
       <c r="J75" s="19"/>
       <c r="K75" s="19"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>494</v>
       </c>
@@ -5217,7 +5219,7 @@
       <c r="J76" s="19"/>
       <c r="K76" s="19"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>170</v>
       </c>
@@ -5245,7 +5247,7 @@
       <c r="J77" s="19"/>
       <c r="K77" s="19"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>130</v>
       </c>
@@ -5273,7 +5275,7 @@
       <c r="J78" s="19"/>
       <c r="K78" s="19"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>161</v>
       </c>
@@ -5301,7 +5303,7 @@
       <c r="J79" s="19"/>
       <c r="K79" s="19"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>137</v>
       </c>
@@ -5329,7 +5331,7 @@
       <c r="J80" s="19"/>
       <c r="K80" s="19"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>503</v>
       </c>
@@ -5357,7 +5359,7 @@
       <c r="J81" s="19"/>
       <c r="K81" s="19"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>506</v>
       </c>
@@ -5385,7 +5387,7 @@
       <c r="J82" s="19"/>
       <c r="K82" s="19"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>509</v>
       </c>
@@ -5413,7 +5415,7 @@
       <c r="J83" s="19"/>
       <c r="K83" s="19"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>512</v>
       </c>
@@ -5441,7 +5443,7 @@
       <c r="J84" s="19"/>
       <c r="K84" s="19"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>116</v>
       </c>
@@ -5469,7 +5471,7 @@
       <c r="J85" s="19"/>
       <c r="K85" s="19"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>516</v>
       </c>
@@ -5497,7 +5499,7 @@
       <c r="J86" s="19"/>
       <c r="K86" s="19"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>519</v>
       </c>
@@ -5525,7 +5527,7 @@
       <c r="J87" s="19"/>
       <c r="K87" s="19"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>519</v>
       </c>
@@ -5553,7 +5555,7 @@
       <c r="J88" s="19"/>
       <c r="K88" s="19"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>519</v>
       </c>
@@ -5581,7 +5583,7 @@
       <c r="J89" s="19"/>
       <c r="K89" s="19"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>522</v>
       </c>
@@ -5609,7 +5611,7 @@
       <c r="J90" s="19"/>
       <c r="K90" s="19"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>525</v>
       </c>
@@ -5637,7 +5639,7 @@
       <c r="J91" s="19"/>
       <c r="K91" s="19"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>117</v>
       </c>
@@ -5665,7 +5667,7 @@
       <c r="J92" s="19"/>
       <c r="K92" s="19"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>529</v>
       </c>
@@ -5693,7 +5695,7 @@
       <c r="J93" s="19"/>
       <c r="K93" s="19"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>529</v>
       </c>
@@ -5721,7 +5723,7 @@
       <c r="J94" s="19"/>
       <c r="K94" s="19"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>529</v>
       </c>
@@ -5749,7 +5751,7 @@
       <c r="J95" s="19"/>
       <c r="K95" s="19"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>531</v>
       </c>
@@ -5777,7 +5779,7 @@
       <c r="J96" s="19"/>
       <c r="K96" s="19"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>536</v>
       </c>
@@ -5805,7 +5807,7 @@
       <c r="J97" s="19"/>
       <c r="K97" s="19"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>536</v>
       </c>
@@ -5833,7 +5835,7 @@
       <c r="J98" s="19"/>
       <c r="K98" s="19"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>534</v>
       </c>
@@ -5861,7 +5863,7 @@
       <c r="J99" s="19"/>
       <c r="K99" s="19"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>267</v>
       </c>
@@ -5889,7 +5891,7 @@
       <c r="J100" s="19"/>
       <c r="K100" s="19"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>267</v>
       </c>
@@ -5917,7 +5919,7 @@
       <c r="J101" s="19"/>
       <c r="K101" s="19"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>540</v>
       </c>
@@ -5945,7 +5947,7 @@
       <c r="J102" s="19"/>
       <c r="K102" s="19"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>540</v>
       </c>
@@ -5973,7 +5975,7 @@
       <c r="J103" s="19"/>
       <c r="K103" s="19"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>540</v>
       </c>
@@ -6001,7 +6003,7 @@
       <c r="J104" s="19"/>
       <c r="K104" s="19"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>543</v>
       </c>
@@ -6029,7 +6031,7 @@
       <c r="J105" s="19"/>
       <c r="K105" s="19"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>543</v>
       </c>
@@ -6057,7 +6059,7 @@
       <c r="J106" s="19"/>
       <c r="K106" s="19"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>545</v>
       </c>
@@ -6085,7 +6087,7 @@
       <c r="J107" s="19"/>
       <c r="K107" s="19"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>548</v>
       </c>
@@ -6113,7 +6115,7 @@
       <c r="J108" s="19"/>
       <c r="K108" s="19"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>805</v>
       </c>
@@ -6141,7 +6143,7 @@
       <c r="J109" s="19"/>
       <c r="K109" s="19"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>167</v>
       </c>
@@ -6169,7 +6171,7 @@
       <c r="J110" s="19"/>
       <c r="K110" s="19"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>554</v>
       </c>
@@ -6197,7 +6199,7 @@
       <c r="J111" s="19"/>
       <c r="K111" s="19"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>295</v>
       </c>
@@ -6225,7 +6227,7 @@
       <c r="J112" s="19"/>
       <c r="K112" s="19"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>558</v>
       </c>
@@ -6253,7 +6255,7 @@
       <c r="J113" s="19"/>
       <c r="K113" s="19"/>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>560</v>
       </c>
@@ -6281,7 +6283,7 @@
       <c r="J114" s="19"/>
       <c r="K114" s="19"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>110</v>
       </c>
@@ -6309,7 +6311,7 @@
       <c r="J115" s="19"/>
       <c r="K115" s="19"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>353</v>
       </c>
@@ -6337,7 +6339,7 @@
       <c r="J116" s="19"/>
       <c r="K116" s="19"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>564</v>
       </c>
@@ -6365,7 +6367,7 @@
       <c r="J117" s="19"/>
       <c r="K117" s="19"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>564</v>
       </c>
@@ -6393,7 +6395,7 @@
       <c r="J118" s="19"/>
       <c r="K118" s="19"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>350</v>
       </c>
@@ -6421,7 +6423,7 @@
       <c r="J119" s="19"/>
       <c r="K119" s="19"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>568</v>
       </c>
@@ -6449,7 +6451,7 @@
       <c r="J120" s="19"/>
       <c r="K120" s="19"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>568</v>
       </c>
@@ -6477,7 +6479,7 @@
       <c r="J121" s="19"/>
       <c r="K121" s="19"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>800</v>
       </c>
@@ -6505,7 +6507,7 @@
       <c r="J122" s="19"/>
       <c r="K122" s="19"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>121</v>
       </c>
@@ -6533,7 +6535,7 @@
       <c r="J123" s="19"/>
       <c r="K123" s="19"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>572</v>
       </c>
@@ -6561,7 +6563,7 @@
       <c r="J124" s="19"/>
       <c r="K124" s="19"/>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>572</v>
       </c>
@@ -6589,7 +6591,7 @@
       <c r="J125" s="19"/>
       <c r="K125" s="19"/>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>575</v>
       </c>
@@ -6619,7 +6621,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>135</v>
       </c>
@@ -6647,7 +6649,7 @@
       <c r="J127" s="19"/>
       <c r="K127" s="19"/>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>231</v>
       </c>
@@ -6675,7 +6677,7 @@
       <c r="J128" s="19"/>
       <c r="K128" s="19"/>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>581</v>
       </c>
@@ -6703,7 +6705,7 @@
       <c r="J129" s="19"/>
       <c r="K129" s="19"/>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>581</v>
       </c>
@@ -6731,7 +6733,7 @@
       <c r="J130" s="19"/>
       <c r="K130" s="19"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>584</v>
       </c>
@@ -6759,7 +6761,7 @@
       <c r="J131" s="19"/>
       <c r="K131" s="19"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>587</v>
       </c>
@@ -6787,7 +6789,7 @@
       <c r="J132" s="19"/>
       <c r="K132" s="19"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>590</v>
       </c>
@@ -6815,7 +6817,7 @@
       <c r="J133" s="19"/>
       <c r="K133" s="19"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>593</v>
       </c>
@@ -6843,7 +6845,7 @@
       <c r="J134" s="19"/>
       <c r="K134" s="19"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>145</v>
       </c>
@@ -6871,7 +6873,7 @@
       <c r="J135" s="19"/>
       <c r="K135" s="19"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>596</v>
       </c>
@@ -6899,7 +6901,7 @@
       <c r="J136" s="19"/>
       <c r="K136" s="19"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>598</v>
       </c>
@@ -6927,7 +6929,7 @@
       <c r="J137" s="19"/>
       <c r="K137" s="19"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>601</v>
       </c>
@@ -6955,7 +6957,7 @@
       <c r="J138" s="19"/>
       <c r="K138" s="19"/>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>604</v>
       </c>
@@ -6983,7 +6985,7 @@
       <c r="J139" s="19"/>
       <c r="K139" s="19"/>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>607</v>
       </c>
@@ -7011,7 +7013,7 @@
       <c r="J140" s="19"/>
       <c r="K140" s="19"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>610</v>
       </c>
@@ -7039,7 +7041,7 @@
       <c r="J141" s="19"/>
       <c r="K141" s="19"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>613</v>
       </c>
@@ -7067,7 +7069,7 @@
       <c r="J142" s="19"/>
       <c r="K142" s="19"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>616</v>
       </c>
@@ -7095,7 +7097,7 @@
       <c r="J143" s="19"/>
       <c r="K143" s="19"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>619</v>
       </c>
@@ -7123,7 +7125,7 @@
       <c r="J144" s="19"/>
       <c r="K144" s="19"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>622</v>
       </c>
@@ -7151,7 +7153,7 @@
       <c r="J145" s="19"/>
       <c r="K145" s="19"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>622</v>
       </c>
@@ -7179,7 +7181,7 @@
       <c r="J146" s="19"/>
       <c r="K146" s="19"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>624</v>
       </c>
@@ -7207,7 +7209,7 @@
       <c r="J147" s="19"/>
       <c r="K147" s="19"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>627</v>
       </c>
@@ -7235,7 +7237,7 @@
       <c r="J148" s="19"/>
       <c r="K148" s="19"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>630</v>
       </c>
@@ -7263,7 +7265,7 @@
       <c r="J149" s="19"/>
       <c r="K149" s="19"/>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>633</v>
       </c>
@@ -7291,7 +7293,7 @@
       <c r="J150" s="19"/>
       <c r="K150" s="19"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>636</v>
       </c>
@@ -7319,7 +7321,7 @@
       <c r="J151" s="19"/>
       <c r="K151" s="19"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>639</v>
       </c>
@@ -7351,7 +7353,7 @@
       <c r="J152" s="19"/>
       <c r="K152" s="19"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>202</v>
       </c>
@@ -7379,7 +7381,7 @@
       <c r="J153" s="19"/>
       <c r="K153" s="19"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>122</v>
       </c>
@@ -7407,7 +7409,7 @@
       <c r="J154" s="19"/>
       <c r="K154" s="19"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>122</v>
       </c>
@@ -7435,7 +7437,7 @@
       <c r="J155" s="19"/>
       <c r="K155" s="19"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>103</v>
       </c>
@@ -7463,7 +7465,7 @@
       <c r="J156" s="19"/>
       <c r="K156" s="19"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>105</v>
       </c>
@@ -7491,7 +7493,7 @@
       <c r="J157" s="19"/>
       <c r="K157" s="19"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>107</v>
       </c>
@@ -7519,7 +7521,7 @@
       <c r="J158" s="19"/>
       <c r="K158" s="19"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>111</v>
       </c>
@@ -7547,7 +7549,7 @@
       <c r="J159" s="19"/>
       <c r="K159" s="19"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>651</v>
       </c>
@@ -7575,7 +7577,7 @@
       <c r="J160" s="19"/>
       <c r="K160" s="19"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>654</v>
       </c>
@@ -7603,7 +7605,7 @@
       <c r="J161" s="19"/>
       <c r="K161" s="19"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>148</v>
       </c>
@@ -7631,7 +7633,7 @@
       <c r="J162" s="19"/>
       <c r="K162" s="19"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>134</v>
       </c>
@@ -7657,11 +7659,9 @@
       <c r="H163" s="19"/>
       <c r="I163" s="19"/>
       <c r="J163" s="19"/>
-      <c r="K163" s="19" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K163" s="19"/>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>282</v>
       </c>
@@ -7689,7 +7689,7 @@
       <c r="J164" s="19"/>
       <c r="K164" s="19"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>127</v>
       </c>
@@ -7717,7 +7717,7 @@
       <c r="J165" s="19"/>
       <c r="K165" s="19"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>127</v>
       </c>
@@ -7745,7 +7745,7 @@
       <c r="J166" s="19"/>
       <c r="K166" s="19"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>158</v>
       </c>
@@ -7773,7 +7773,7 @@
       <c r="J167" s="19"/>
       <c r="K167" s="19"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>177</v>
       </c>
@@ -7801,7 +7801,7 @@
       <c r="J168" s="19"/>
       <c r="K168" s="19"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>132</v>
       </c>
@@ -7829,7 +7829,7 @@
       <c r="J169" s="19"/>
       <c r="K169" s="19"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>131</v>
       </c>
@@ -7857,7 +7857,7 @@
       <c r="J170" s="19"/>
       <c r="K170" s="19"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>141</v>
       </c>
@@ -7885,7 +7885,7 @@
       <c r="J171" s="19"/>
       <c r="K171" s="19"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>142</v>
       </c>
@@ -7913,7 +7913,7 @@
       <c r="J172" s="19"/>
       <c r="K172" s="19"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>228</v>
       </c>
@@ -7941,7 +7941,7 @@
       <c r="J173" s="19"/>
       <c r="K173" s="19"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>230</v>
       </c>
@@ -7969,7 +7969,7 @@
       <c r="J174" s="19"/>
       <c r="K174" s="19"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>147</v>
       </c>
@@ -7997,7 +7997,7 @@
       <c r="J175" s="19"/>
       <c r="K175" s="19"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>151</v>
       </c>
@@ -8025,7 +8025,7 @@
       <c r="J176" s="19"/>
       <c r="K176" s="19"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>681</v>
       </c>
@@ -8053,7 +8053,7 @@
       <c r="J177" s="19"/>
       <c r="K177" s="19"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>154</v>
       </c>
@@ -8081,7 +8081,7 @@
       <c r="J178" s="19"/>
       <c r="K178" s="19"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>156</v>
       </c>
@@ -8109,7 +8109,7 @@
       <c r="J179" s="19"/>
       <c r="K179" s="19"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>168</v>
       </c>
@@ -8137,7 +8137,7 @@
       <c r="J180" s="19"/>
       <c r="K180" s="19"/>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>163</v>
       </c>
@@ -8165,7 +8165,7 @@
       <c r="J181" s="19"/>
       <c r="K181" s="19"/>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>374</v>
       </c>
@@ -8193,7 +8193,7 @@
       <c r="J182" s="19"/>
       <c r="K182" s="19"/>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>173</v>
       </c>
@@ -8221,7 +8221,7 @@
       <c r="J183" s="19"/>
       <c r="K183" s="19"/>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>173</v>
       </c>
@@ -8249,7 +8249,7 @@
       <c r="J184" s="19"/>
       <c r="K184" s="19"/>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>175</v>
       </c>
@@ -8277,7 +8277,7 @@
       <c r="J185" s="19"/>
       <c r="K185" s="19"/>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>175</v>
       </c>
@@ -8305,7 +8305,7 @@
       <c r="J186" s="19"/>
       <c r="K186" s="19"/>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>175</v>
       </c>
@@ -8333,7 +8333,7 @@
       <c r="J187" s="19"/>
       <c r="K187" s="19"/>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>179</v>
       </c>
@@ -8361,7 +8361,7 @@
       <c r="J188" s="19"/>
       <c r="K188" s="19"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>696</v>
       </c>
@@ -8387,11 +8387,9 @@
       <c r="H189" s="19"/>
       <c r="I189" s="19"/>
       <c r="J189" s="19"/>
-      <c r="K189" s="19" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K189" s="19"/>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>298</v>
       </c>
@@ -8419,7 +8417,7 @@
       <c r="J190" s="19"/>
       <c r="K190" s="19"/>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>797</v>
       </c>
@@ -8447,7 +8445,7 @@
       <c r="J191" s="19"/>
       <c r="K191" s="19"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>185</v>
       </c>
@@ -8475,7 +8473,7 @@
       <c r="J192" s="19"/>
       <c r="K192" s="19"/>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>185</v>
       </c>
@@ -8503,7 +8501,7 @@
       <c r="J193" s="19"/>
       <c r="K193" s="19"/>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>183</v>
       </c>
@@ -8531,7 +8529,7 @@
       <c r="J194" s="19"/>
       <c r="K194" s="19"/>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>703</v>
       </c>
@@ -8559,7 +8557,7 @@
       <c r="J195" s="19"/>
       <c r="K195" s="19"/>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>705</v>
       </c>
@@ -8587,7 +8585,7 @@
       <c r="J196" s="19"/>
       <c r="K196" s="19"/>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>188</v>
       </c>
@@ -8615,7 +8613,7 @@
       <c r="J197" s="19"/>
       <c r="K197" s="19"/>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>191</v>
       </c>
@@ -8643,7 +8641,7 @@
       <c r="J198" s="19"/>
       <c r="K198" s="19"/>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>711</v>
       </c>
@@ -8671,7 +8669,7 @@
       <c r="J199" s="19"/>
       <c r="K199" s="19"/>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>219</v>
       </c>
@@ -8699,7 +8697,7 @@
       <c r="J200" s="19"/>
       <c r="K200" s="19"/>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>713</v>
       </c>
@@ -8727,7 +8725,7 @@
       <c r="J201" s="19"/>
       <c r="K201" s="19"/>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>716</v>
       </c>
@@ -8757,7 +8755,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>359</v>
       </c>
@@ -8785,7 +8783,7 @@
       <c r="J203" s="19"/>
       <c r="K203" s="19"/>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>204</v>
       </c>
@@ -8813,7 +8811,7 @@
       <c r="J204" s="19"/>
       <c r="K204" s="19"/>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>206</v>
       </c>
@@ -8841,7 +8839,7 @@
       <c r="J205" s="19"/>
       <c r="K205" s="19"/>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>240</v>
       </c>
@@ -8869,7 +8867,7 @@
       <c r="J206" s="19"/>
       <c r="K206" s="19"/>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>212</v>
       </c>
@@ -8897,7 +8895,7 @@
       <c r="J207" s="19"/>
       <c r="K207" s="19"/>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>226</v>
       </c>
@@ -8925,7 +8923,7 @@
       <c r="J208" s="19"/>
       <c r="K208" s="19"/>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>221</v>
       </c>
@@ -8953,7 +8951,7 @@
       <c r="J209" s="19"/>
       <c r="K209" s="19"/>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>221</v>
       </c>
@@ -8981,7 +8979,7 @@
       <c r="J210" s="19"/>
       <c r="K210" s="19"/>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>221</v>
       </c>
@@ -9009,7 +9007,7 @@
       <c r="J211" s="19"/>
       <c r="K211" s="19"/>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>221</v>
       </c>
@@ -9037,7 +9035,7 @@
       <c r="J212" s="19"/>
       <c r="K212" s="19"/>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>221</v>
       </c>
@@ -9065,7 +9063,7 @@
       <c r="J213" s="19"/>
       <c r="K213" s="19"/>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>732</v>
       </c>
@@ -9093,7 +9091,7 @@
       <c r="J214" s="19"/>
       <c r="K214" s="19"/>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>232</v>
       </c>
@@ -9121,7 +9119,7 @@
       <c r="J215" s="19"/>
       <c r="K215" s="19"/>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>242</v>
       </c>
@@ -9149,7 +9147,7 @@
       <c r="J216" s="19"/>
       <c r="K216" s="19"/>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>247</v>
       </c>
@@ -9177,7 +9175,7 @@
       <c r="J217" s="19"/>
       <c r="K217" s="19"/>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>740</v>
       </c>
@@ -9205,7 +9203,7 @@
       <c r="J218" s="19"/>
       <c r="K218" s="19"/>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>251</v>
       </c>
@@ -9233,7 +9231,7 @@
       <c r="J219" s="19"/>
       <c r="K219" s="19"/>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>276</v>
       </c>
@@ -9261,7 +9259,7 @@
       <c r="J220" s="19"/>
       <c r="K220" s="19"/>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>746</v>
       </c>
@@ -9289,7 +9287,7 @@
       <c r="J221" s="19"/>
       <c r="K221" s="19"/>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>257</v>
       </c>
@@ -9317,7 +9315,7 @@
       <c r="J222" s="19"/>
       <c r="K222" s="19"/>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>748</v>
       </c>
@@ -9345,7 +9343,7 @@
       <c r="J223" s="19"/>
       <c r="K223" s="19"/>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>263</v>
       </c>
@@ -9373,7 +9371,7 @@
       <c r="J224" s="19"/>
       <c r="K224" s="19"/>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>260</v>
       </c>
@@ -9401,7 +9399,7 @@
       <c r="J225" s="19"/>
       <c r="K225" s="19"/>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>264</v>
       </c>
@@ -9429,7 +9427,7 @@
       <c r="J226" s="19"/>
       <c r="K226" s="19"/>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>269</v>
       </c>
@@ -9457,7 +9455,7 @@
       <c r="J227" s="19"/>
       <c r="K227" s="19"/>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>270</v>
       </c>
@@ -9485,7 +9483,7 @@
       <c r="J228" s="19"/>
       <c r="K228" s="19"/>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>270</v>
       </c>
@@ -9513,7 +9511,7 @@
       <c r="J229" s="19"/>
       <c r="K229" s="19"/>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>279</v>
       </c>
@@ -9541,7 +9539,7 @@
       <c r="J230" s="19"/>
       <c r="K230" s="19"/>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>278</v>
       </c>
@@ -9569,7 +9567,7 @@
       <c r="J231" s="19"/>
       <c r="K231" s="19"/>
     </row>
-    <row r="232" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>284</v>
       </c>
@@ -9597,7 +9595,7 @@
       <c r="J232" s="20"/>
       <c r="K232" s="20"/>
     </row>
-    <row r="233" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>765</v>
       </c>
@@ -9625,7 +9623,7 @@
       <c r="J233" s="20"/>
       <c r="K233" s="20"/>
     </row>
-    <row r="234" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:11" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>288</v>
       </c>
@@ -9653,7 +9651,7 @@
       <c r="J234" s="20"/>
       <c r="K234" s="20"/>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>287</v>
       </c>
@@ -9681,7 +9679,7 @@
       <c r="J235" s="19"/>
       <c r="K235" s="19"/>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>289</v>
       </c>
@@ -9709,7 +9707,7 @@
       <c r="J236" s="19"/>
       <c r="K236" s="19"/>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>290</v>
       </c>
@@ -9737,7 +9735,7 @@
       <c r="J237" s="19"/>
       <c r="K237" s="19"/>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>774</v>
       </c>
@@ -9765,7 +9763,7 @@
       <c r="J238" s="19"/>
       <c r="K238" s="19"/>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>303</v>
       </c>
@@ -9793,7 +9791,7 @@
       <c r="J239" s="19"/>
       <c r="K239" s="19"/>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>304</v>
       </c>
@@ -9821,7 +9819,7 @@
       <c r="J240" s="19"/>
       <c r="K240" s="19"/>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>305</v>
       </c>
@@ -9849,7 +9847,7 @@
       <c r="J241" s="19"/>
       <c r="K241" s="19"/>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>300</v>
       </c>
@@ -9877,7 +9875,7 @@
       <c r="J242" s="19"/>
       <c r="K242" s="19"/>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>348</v>
       </c>
@@ -9905,7 +9903,7 @@
       <c r="J243" s="19"/>
       <c r="K243" s="19"/>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>357</v>
       </c>
@@ -9933,7 +9931,7 @@
       <c r="J244" s="19"/>
       <c r="K244" s="19"/>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>351</v>
       </c>
@@ -9961,7 +9959,7 @@
       <c r="J245" s="19"/>
       <c r="K245" s="19"/>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>361</v>
       </c>
@@ -9989,7 +9987,7 @@
       <c r="J246" s="19"/>
       <c r="K246" s="19"/>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>365</v>
       </c>
@@ -10017,7 +10015,7 @@
       <c r="J247" s="19"/>
       <c r="K247" s="19"/>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>363</v>
       </c>
@@ -10045,7 +10043,7 @@
       <c r="J248" s="19"/>
       <c r="K248" s="19"/>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>355</v>
       </c>
@@ -10073,7 +10071,7 @@
       <c r="J249" s="19"/>
       <c r="K249" s="19"/>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>368</v>
       </c>
@@ -10101,7 +10099,7 @@
       <c r="J250" s="19"/>
       <c r="K250" s="19"/>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>367</v>
       </c>
@@ -10129,7 +10127,7 @@
       <c r="J251" s="19"/>
       <c r="K251" s="19"/>
     </row>
-    <row r="252" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>367</v>
       </c>
@@ -10157,7 +10155,7 @@
       <c r="J252" s="19"/>
       <c r="K252" s="19"/>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>371</v>
       </c>
@@ -10185,7 +10183,7 @@
       <c r="J253" s="19"/>
       <c r="K253" s="19"/>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>816</v>
       </c>
@@ -10223,12 +10221,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100AF0C36E9CBDE43468AAB846756A8BA94" ma:contentTypeVersion="0" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="93c275e25462616b2c1de9b58ec156dd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f6edc329ff236629c56e3b879b320d0">
     <xsd:element name="properties">
@@ -10342,16 +10349,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDD49F8-6691-4324-BC0D-0B1E4890A2C6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FEFD23-736F-4CE9-81DA-D9D145B9B572}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -10366,7 +10372,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A01C7383-C303-4DC2-9970-99C89A193825}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10380,12 +10386,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DDD49F8-6691-4324-BC0D-0B1E4890A2C6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>